--- a/formats/formato_SOP.xlsx
+++ b/formats/formato_SOP.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\analistadatos\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gmhcol-my.sharepoint.com/personal/analistadatos_turinza_com/Documents/proyectos/SOP/formats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4C81DFA-2F42-43D1-A45D-C4F01C3237E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{B4C81DFA-2F42-43D1-A45D-C4F01C3237E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87C2E396-1B2D-4515-935F-A4BA13CCC027}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">SOP!$B$1:$O$125</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">SOP!$1:$5</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -943,7 +943,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="192">
   <si>
     <t>Versión</t>
   </si>
@@ -2442,6 +2442,461 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2450,14 +2905,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -2474,154 +2921,12 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
@@ -2631,295 +2936,6 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -2927,22 +2943,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -3041,6 +3041,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3492,60 +3496,60 @@
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="2:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="74" t="e" vm="1">
+      <c r="B2" s="116" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C2" s="74"/>
-      <c r="D2" s="75" t="s">
+      <c r="C2" s="116"/>
+      <c r="D2" s="117" t="s">
         <v>164</v>
       </c>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-      <c r="J2" s="76"/>
-      <c r="K2" s="76"/>
-      <c r="L2" s="76"/>
-      <c r="M2" s="76"/>
-      <c r="N2" s="77" t="s">
+      <c r="E2" s="118"/>
+      <c r="F2" s="118"/>
+      <c r="G2" s="118"/>
+      <c r="H2" s="118"/>
+      <c r="I2" s="118"/>
+      <c r="J2" s="118"/>
+      <c r="K2" s="118"/>
+      <c r="L2" s="118"/>
+      <c r="M2" s="118"/>
+      <c r="N2" s="119" t="s">
         <v>102</v>
       </c>
-      <c r="O2" s="78"/>
+      <c r="O2" s="120"/>
     </row>
     <row r="3" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="79"/>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-      <c r="I3" s="79"/>
-      <c r="J3" s="79"/>
-      <c r="K3" s="79"/>
-      <c r="L3" s="79"/>
-      <c r="M3" s="79"/>
-      <c r="N3" s="79"/>
-      <c r="O3" s="79"/>
+      <c r="B3" s="121"/>
+      <c r="C3" s="121"/>
+      <c r="D3" s="121"/>
+      <c r="E3" s="121"/>
+      <c r="F3" s="121"/>
+      <c r="G3" s="121"/>
+      <c r="H3" s="121"/>
+      <c r="I3" s="121"/>
+      <c r="J3" s="121"/>
+      <c r="K3" s="121"/>
+      <c r="L3" s="121"/>
+      <c r="M3" s="121"/>
+      <c r="N3" s="121"/>
+      <c r="O3" s="121"/>
     </row>
     <row r="4" spans="2:15" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="43" t="s">
+      <c r="B4" s="67" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="44"/>
-      <c r="M4" s="44"/>
-      <c r="N4" s="44"/>
-      <c r="O4" s="45"/>
+      <c r="C4" s="68"/>
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="68"/>
+      <c r="G4" s="68"/>
+      <c r="H4" s="68"/>
+      <c r="I4" s="68"/>
+      <c r="J4" s="68"/>
+      <c r="K4" s="68"/>
+      <c r="L4" s="68"/>
+      <c r="M4" s="68"/>
+      <c r="N4" s="68"/>
+      <c r="O4" s="69"/>
     </row>
     <row r="5" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
@@ -3554,251 +3558,249 @@
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
-      <c r="F5" s="113" t="s">
+      <c r="F5" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="114"/>
-      <c r="H5" s="115"/>
-      <c r="I5" s="116" t="s">
+      <c r="G5" s="88"/>
+      <c r="H5" s="89"/>
+      <c r="I5" s="90" t="s">
         <v>137</v>
       </c>
-      <c r="J5" s="117"/>
-      <c r="K5" s="118"/>
-      <c r="L5" s="32" t="s">
+      <c r="J5" s="91"/>
+      <c r="K5" s="92"/>
+      <c r="L5" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="33"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="47"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="6" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="153"/>
-      <c r="C6" s="154"/>
-      <c r="D6" s="154"/>
-      <c r="E6" s="155"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="99"/>
-      <c r="J6" s="100"/>
-      <c r="K6" s="132"/>
-      <c r="L6" s="87" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="44"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="47" t="s">
         <v>189</v>
       </c>
-      <c r="M6" s="33"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="47"/>
+      <c r="M6" s="23"/>
+      <c r="N6" s="23"/>
+      <c r="O6" s="24"/>
     </row>
     <row r="7" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="47"/>
-      <c r="F7" s="28" t="s">
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="29"/>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="131"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="43"/>
     </row>
     <row r="8" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="87"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="47"/>
-      <c r="F8" s="148" t="s">
-        <v>179</v>
-      </c>
-      <c r="G8" s="149"/>
-      <c r="H8" s="148"/>
-      <c r="I8" s="149"/>
-      <c r="J8" s="148"/>
-      <c r="K8" s="149"/>
-      <c r="L8" s="148"/>
-      <c r="M8" s="149"/>
-      <c r="N8" s="148"/>
-      <c r="O8" s="156"/>
+      <c r="B8" s="47"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="37"/>
+      <c r="G8" s="38"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="38"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="38"/>
+      <c r="N8" s="37"/>
+      <c r="O8" s="39"/>
     </row>
     <row r="9" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="33"/>
-      <c r="G9" s="33"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="47"/>
-      <c r="J9" s="32" t="s">
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="K9" s="33"/>
-      <c r="L9" s="47"/>
-      <c r="M9" s="32" t="s">
+      <c r="K9" s="23"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="40" t="s">
         <v>126</v>
       </c>
-      <c r="N9" s="33"/>
-      <c r="O9" s="47"/>
+      <c r="N9" s="23"/>
+      <c r="O9" s="24"/>
     </row>
     <row r="10" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="87"/>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="33"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="87"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="47"/>
-      <c r="M10" s="87"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="47"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="47"/>
+      <c r="K10" s="23"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="47"/>
+      <c r="N10" s="23"/>
+      <c r="O10" s="24"/>
     </row>
     <row r="11" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B11" s="88" t="s">
+      <c r="B11" s="104" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="89"/>
-      <c r="D11" s="89"/>
-      <c r="E11" s="89"/>
-      <c r="F11" s="89"/>
-      <c r="G11" s="89"/>
-      <c r="H11" s="90"/>
-      <c r="I11" s="91" t="s">
+      <c r="C11" s="105"/>
+      <c r="D11" s="105"/>
+      <c r="E11" s="105"/>
+      <c r="F11" s="105"/>
+      <c r="G11" s="105"/>
+      <c r="H11" s="106"/>
+      <c r="I11" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="J11" s="89"/>
-      <c r="K11" s="89"/>
-      <c r="L11" s="89"/>
-      <c r="M11" s="89"/>
-      <c r="N11" s="89"/>
-      <c r="O11" s="92"/>
+      <c r="J11" s="105"/>
+      <c r="K11" s="105"/>
+      <c r="L11" s="105"/>
+      <c r="M11" s="105"/>
+      <c r="N11" s="105"/>
+      <c r="O11" s="108"/>
     </row>
     <row r="12" spans="2:15" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="134" t="s">
+      <c r="B12" s="48" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="135"/>
-      <c r="D12" s="135"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="136"/>
-      <c r="I12" s="143" t="s">
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="57" t="s">
         <v>178</v>
       </c>
-      <c r="J12" s="135"/>
-      <c r="K12" s="135"/>
-      <c r="L12" s="135"/>
-      <c r="M12" s="135"/>
-      <c r="N12" s="135"/>
-      <c r="O12" s="144"/>
+      <c r="J12" s="49"/>
+      <c r="K12" s="49"/>
+      <c r="L12" s="49"/>
+      <c r="M12" s="49"/>
+      <c r="N12" s="49"/>
+      <c r="O12" s="58"/>
     </row>
     <row r="13" spans="2:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="137"/>
-      <c r="C13" s="138"/>
-      <c r="D13" s="138"/>
-      <c r="E13" s="138"/>
-      <c r="F13" s="138"/>
-      <c r="G13" s="138"/>
-      <c r="H13" s="139"/>
-      <c r="I13" s="145" t="str">
+      <c r="B13" s="51"/>
+      <c r="C13" s="52"/>
+      <c r="D13" s="52"/>
+      <c r="E13" s="52"/>
+      <c r="F13" s="52"/>
+      <c r="G13" s="52"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="34" t="str">
         <f>IFERROR(VLOOKUP(F8,Listas!$C$12:$D$17, 2, FALSE), "")</f>
-        <v>DTA/OTM: Cubre desde la recepción de solicitud del cliente hasta el descargue de la mercancía y liberación de documentos del embarque en el deposito indicado en el documento de transporte.</v>
-      </c>
-      <c r="J13" s="146"/>
-      <c r="K13" s="146"/>
-      <c r="L13" s="146"/>
-      <c r="M13" s="146"/>
-      <c r="N13" s="146"/>
-      <c r="O13" s="147"/>
+        <v/>
+      </c>
+      <c r="J13" s="35"/>
+      <c r="K13" s="35"/>
+      <c r="L13" s="35"/>
+      <c r="M13" s="35"/>
+      <c r="N13" s="35"/>
+      <c r="O13" s="36"/>
     </row>
     <row r="14" spans="2:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="137"/>
-      <c r="C14" s="138"/>
-      <c r="D14" s="138"/>
-      <c r="E14" s="138"/>
-      <c r="F14" s="138"/>
-      <c r="G14" s="138"/>
-      <c r="H14" s="139"/>
-      <c r="I14" s="145" t="str">
+      <c r="B14" s="51"/>
+      <c r="C14" s="52"/>
+      <c r="D14" s="52"/>
+      <c r="E14" s="52"/>
+      <c r="F14" s="52"/>
+      <c r="G14" s="52"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="34" t="str">
         <f>IFERROR(VLOOKUP(H8,Listas!$C$12:$D$17, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="J14" s="146"/>
-      <c r="K14" s="146"/>
-      <c r="L14" s="146"/>
-      <c r="M14" s="146"/>
-      <c r="N14" s="146"/>
-      <c r="O14" s="147"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="35"/>
+      <c r="L14" s="35"/>
+      <c r="M14" s="35"/>
+      <c r="N14" s="35"/>
+      <c r="O14" s="36"/>
     </row>
     <row r="15" spans="2:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="137"/>
-      <c r="C15" s="138"/>
-      <c r="D15" s="138"/>
-      <c r="E15" s="138"/>
-      <c r="F15" s="138"/>
-      <c r="G15" s="138"/>
-      <c r="H15" s="139"/>
-      <c r="I15" s="145" t="str">
+      <c r="B15" s="51"/>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52"/>
+      <c r="E15" s="52"/>
+      <c r="F15" s="52"/>
+      <c r="G15" s="52"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="34" t="str">
         <f>IFERROR(VLOOKUP(J8,Listas!$C$12:$D$17, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="J15" s="146"/>
-      <c r="K15" s="146"/>
-      <c r="L15" s="146"/>
-      <c r="M15" s="146"/>
-      <c r="N15" s="146"/>
-      <c r="O15" s="147"/>
+      <c r="J15" s="35"/>
+      <c r="K15" s="35"/>
+      <c r="L15" s="35"/>
+      <c r="M15" s="35"/>
+      <c r="N15" s="35"/>
+      <c r="O15" s="36"/>
     </row>
     <row r="16" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="137"/>
-      <c r="C16" s="138"/>
-      <c r="D16" s="138"/>
-      <c r="E16" s="138"/>
-      <c r="F16" s="138"/>
-      <c r="G16" s="138"/>
-      <c r="H16" s="139"/>
-      <c r="I16" s="145" t="str">
+      <c r="B16" s="51"/>
+      <c r="C16" s="52"/>
+      <c r="D16" s="52"/>
+      <c r="E16" s="52"/>
+      <c r="F16" s="52"/>
+      <c r="G16" s="52"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="34" t="str">
         <f>IFERROR(VLOOKUP(L8,Listas!$C$12:$D$17, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="J16" s="146"/>
-      <c r="K16" s="146"/>
-      <c r="L16" s="146"/>
-      <c r="M16" s="146"/>
-      <c r="N16" s="146"/>
-      <c r="O16" s="147"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="35"/>
+      <c r="M16" s="35"/>
+      <c r="N16" s="35"/>
+      <c r="O16" s="36"/>
     </row>
     <row r="17" spans="2:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="140"/>
-      <c r="C17" s="141"/>
-      <c r="D17" s="141"/>
-      <c r="E17" s="141"/>
-      <c r="F17" s="141"/>
-      <c r="G17" s="141"/>
-      <c r="H17" s="142"/>
-      <c r="I17" s="80" t="str">
+      <c r="B17" s="54"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="55"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="112" t="str">
         <f>IFERROR(VLOOKUP(N8,Listas!$C$12:$D$17, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="J17" s="81"/>
-      <c r="K17" s="81"/>
-      <c r="L17" s="81"/>
-      <c r="M17" s="81"/>
-      <c r="N17" s="81"/>
-      <c r="O17" s="82"/>
+      <c r="J17" s="113"/>
+      <c r="K17" s="113"/>
+      <c r="L17" s="113"/>
+      <c r="M17" s="113"/>
+      <c r="N17" s="113"/>
+      <c r="O17" s="114"/>
     </row>
     <row r="18" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="5"/>
@@ -3817,150 +3819,150 @@
       <c r="O18" s="5"/>
     </row>
     <row r="19" spans="2:15" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="43" t="s">
+      <c r="B19" s="67" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
-      <c r="M19" s="44"/>
-      <c r="N19" s="44"/>
-      <c r="O19" s="45"/>
+      <c r="C19" s="68"/>
+      <c r="D19" s="68"/>
+      <c r="E19" s="68"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="68"/>
+      <c r="H19" s="68"/>
+      <c r="I19" s="68"/>
+      <c r="J19" s="68"/>
+      <c r="K19" s="68"/>
+      <c r="L19" s="68"/>
+      <c r="M19" s="68"/>
+      <c r="N19" s="68"/>
+      <c r="O19" s="69"/>
     </row>
     <row r="20" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="32" t="s">
+      <c r="B20" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="47"/>
-      <c r="I20" s="32" t="s">
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="40" t="s">
         <v>19</v>
       </c>
-      <c r="J20" s="33"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="N20" s="33"/>
-      <c r="O20" s="47"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+      <c r="L20" s="23"/>
+      <c r="M20" s="23"/>
+      <c r="N20" s="23"/>
+      <c r="O20" s="24"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="49"/>
-      <c r="C21" s="102"/>
-      <c r="D21" s="102"/>
-      <c r="E21" s="102"/>
-      <c r="F21" s="102"/>
-      <c r="G21" s="102"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="49"/>
-      <c r="J21" s="102"/>
-      <c r="K21" s="102"/>
-      <c r="L21" s="102"/>
-      <c r="M21" s="102"/>
-      <c r="N21" s="102"/>
-      <c r="O21" s="103"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="22"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="26"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="106"/>
-      <c r="C22" s="107"/>
-      <c r="D22" s="107"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="107"/>
-      <c r="H22" s="108"/>
-      <c r="I22" s="106"/>
-      <c r="J22" s="107"/>
-      <c r="K22" s="107"/>
-      <c r="L22" s="107"/>
-      <c r="M22" s="107"/>
-      <c r="N22" s="107"/>
-      <c r="O22" s="108"/>
+      <c r="B22" s="62"/>
+      <c r="C22" s="76"/>
+      <c r="D22" s="76"/>
+      <c r="E22" s="76"/>
+      <c r="F22" s="76"/>
+      <c r="G22" s="76"/>
+      <c r="H22" s="63"/>
+      <c r="I22" s="62"/>
+      <c r="J22" s="76"/>
+      <c r="K22" s="76"/>
+      <c r="L22" s="76"/>
+      <c r="M22" s="76"/>
+      <c r="N22" s="76"/>
+      <c r="O22" s="63"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="106"/>
-      <c r="C23" s="107"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="107"/>
-      <c r="G23" s="107"/>
-      <c r="H23" s="108"/>
-      <c r="I23" s="106"/>
-      <c r="J23" s="107"/>
-      <c r="K23" s="107"/>
-      <c r="L23" s="107"/>
-      <c r="M23" s="107"/>
-      <c r="N23" s="107"/>
-      <c r="O23" s="108"/>
+      <c r="B23" s="62"/>
+      <c r="C23" s="76"/>
+      <c r="D23" s="76"/>
+      <c r="E23" s="76"/>
+      <c r="F23" s="76"/>
+      <c r="G23" s="76"/>
+      <c r="H23" s="63"/>
+      <c r="I23" s="62"/>
+      <c r="J23" s="76"/>
+      <c r="K23" s="76"/>
+      <c r="L23" s="76"/>
+      <c r="M23" s="76"/>
+      <c r="N23" s="76"/>
+      <c r="O23" s="63"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="104"/>
-      <c r="C24" s="105"/>
-      <c r="D24" s="105"/>
-      <c r="E24" s="105"/>
-      <c r="F24" s="105"/>
-      <c r="G24" s="105"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="104"/>
-      <c r="J24" s="105"/>
-      <c r="K24" s="105"/>
-      <c r="L24" s="105"/>
-      <c r="M24" s="105"/>
-      <c r="N24" s="105"/>
-      <c r="O24" s="68"/>
+      <c r="B24" s="27"/>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="29"/>
+      <c r="I24" s="27"/>
+      <c r="J24" s="28"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="28"/>
+      <c r="N24" s="28"/>
+      <c r="O24" s="29"/>
     </row>
     <row r="25" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="32" t="s">
+      <c r="B25" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="33"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="20" t="s">
+      <c r="C25" s="23"/>
+      <c r="D25" s="24"/>
+      <c r="E25" s="144" t="s">
         <v>167</v>
       </c>
-      <c r="F25" s="21"/>
-      <c r="G25" s="32" t="s">
+      <c r="F25" s="145"/>
+      <c r="G25" s="40" t="s">
         <v>166</v>
       </c>
-      <c r="H25" s="33"/>
-      <c r="I25" s="32" t="s">
+      <c r="H25" s="23"/>
+      <c r="I25" s="40" t="s">
         <v>168</v>
       </c>
-      <c r="J25" s="33"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="28" t="s">
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+      <c r="L25" s="41" t="s">
         <v>142</v>
       </c>
-      <c r="M25" s="29"/>
-      <c r="N25" s="28" t="s">
+      <c r="M25" s="42"/>
+      <c r="N25" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="O25" s="30"/>
+      <c r="O25" s="150"/>
     </row>
     <row r="26" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B26" s="49"/>
-      <c r="C26" s="33"/>
-      <c r="D26" s="47"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="22"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="24"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="26"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="25"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="26"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="24"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="146"/>
+      <c r="J26" s="147"/>
+      <c r="K26" s="148"/>
+      <c r="L26" s="146"/>
+      <c r="M26" s="147"/>
+      <c r="N26" s="149"/>
+      <c r="O26" s="148"/>
     </row>
     <row r="27" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="5"/>
@@ -3997,356 +3999,356 @@
       <c r="O28" s="111"/>
     </row>
     <row r="29" spans="2:15" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="34" t="s">
+      <c r="B29" s="131" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="35"/>
-      <c r="D29" s="35"/>
-      <c r="E29" s="35"/>
-      <c r="F29" s="35"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="35"/>
-      <c r="I29" s="35"/>
-      <c r="J29" s="35"/>
-      <c r="K29" s="35"/>
-      <c r="L29" s="35"/>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
-      <c r="O29" s="36"/>
+      <c r="C29" s="132"/>
+      <c r="D29" s="132"/>
+      <c r="E29" s="132"/>
+      <c r="F29" s="132"/>
+      <c r="G29" s="132"/>
+      <c r="H29" s="132"/>
+      <c r="I29" s="132"/>
+      <c r="J29" s="132"/>
+      <c r="K29" s="132"/>
+      <c r="L29" s="132"/>
+      <c r="M29" s="132"/>
+      <c r="N29" s="132"/>
+      <c r="O29" s="133"/>
     </row>
     <row r="30" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="142" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="62"/>
-      <c r="K30" s="58" t="s">
+      <c r="C30" s="142"/>
+      <c r="D30" s="142"/>
+      <c r="E30" s="142"/>
+      <c r="F30" s="142"/>
+      <c r="G30" s="142"/>
+      <c r="H30" s="142"/>
+      <c r="I30" s="142"/>
+      <c r="J30" s="143"/>
+      <c r="K30" s="139" t="s">
         <v>140</v>
       </c>
-      <c r="L30" s="59"/>
-      <c r="M30" s="59"/>
-      <c r="N30" s="59"/>
-      <c r="O30" s="60"/>
+      <c r="L30" s="140"/>
+      <c r="M30" s="140"/>
+      <c r="N30" s="140"/>
+      <c r="O30" s="141"/>
     </row>
     <row r="31" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B31" s="119" t="s">
+      <c r="B31" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="120"/>
-      <c r="D31" s="119" t="s">
+      <c r="C31" s="21"/>
+      <c r="D31" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="E31" s="120"/>
+      <c r="E31" s="21"/>
       <c r="F31" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G31" s="119" t="s">
+      <c r="G31" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="H31" s="120"/>
-      <c r="I31" s="119" t="s">
+      <c r="H31" s="21"/>
+      <c r="I31" s="20" t="s">
         <v>169</v>
       </c>
-      <c r="J31" s="133"/>
-      <c r="K31" s="121" t="s">
+      <c r="J31" s="103"/>
+      <c r="K31" s="151" t="s">
         <v>28</v>
       </c>
-      <c r="L31" s="71"/>
+      <c r="L31" s="123"/>
       <c r="M31" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="N31" s="72" t="s">
+      <c r="N31" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="O31" s="71"/>
+      <c r="O31" s="123"/>
     </row>
     <row r="32" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B32" s="64" t="s">
+      <c r="B32" s="99" t="s">
         <v>170</v>
       </c>
-      <c r="C32" s="64"/>
-      <c r="D32" s="63"/>
-      <c r="E32" s="64"/>
+      <c r="C32" s="99"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="99"/>
       <c r="F32" s="16"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="63"/>
-      <c r="J32" s="130"/>
-      <c r="K32" s="52"/>
-      <c r="L32" s="47"/>
+      <c r="G32" s="64"/>
+      <c r="H32" s="99"/>
+      <c r="I32" s="64"/>
+      <c r="J32" s="65"/>
+      <c r="K32" s="66"/>
+      <c r="L32" s="24"/>
       <c r="M32" s="4"/>
-      <c r="N32" s="49"/>
-      <c r="O32" s="47"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="24"/>
     </row>
     <row r="33" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B33" s="64" t="s">
+      <c r="B33" s="99" t="s">
         <v>171</v>
       </c>
-      <c r="C33" s="64"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="64"/>
+      <c r="C33" s="99"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="99"/>
       <c r="F33" s="16"/>
-      <c r="G33" s="63"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="63"/>
-      <c r="J33" s="65"/>
-      <c r="K33" s="66"/>
-      <c r="L33" s="47"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="99"/>
+      <c r="I33" s="64"/>
+      <c r="J33" s="70"/>
+      <c r="K33" s="71"/>
+      <c r="L33" s="24"/>
       <c r="M33" s="4"/>
-      <c r="N33" s="49"/>
-      <c r="O33" s="47"/>
+      <c r="N33" s="22"/>
+      <c r="O33" s="24"/>
     </row>
     <row r="34" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B34" s="64" t="s">
+      <c r="B34" s="99" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="64"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="64"/>
+      <c r="C34" s="99"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="99"/>
       <c r="F34" s="16"/>
-      <c r="G34" s="63"/>
-      <c r="H34" s="64"/>
-      <c r="I34" s="63"/>
-      <c r="J34" s="130"/>
-      <c r="K34" s="52"/>
-      <c r="L34" s="47"/>
+      <c r="G34" s="64"/>
+      <c r="H34" s="99"/>
+      <c r="I34" s="64"/>
+      <c r="J34" s="65"/>
+      <c r="K34" s="66"/>
+      <c r="L34" s="24"/>
       <c r="M34" s="4"/>
-      <c r="N34" s="49"/>
-      <c r="O34" s="47"/>
+      <c r="N34" s="22"/>
+      <c r="O34" s="24"/>
     </row>
     <row r="35" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B35" s="64" t="s">
+      <c r="B35" s="99" t="s">
         <v>117</v>
       </c>
-      <c r="C35" s="64"/>
-      <c r="D35" s="63"/>
-      <c r="E35" s="64"/>
+      <c r="C35" s="99"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="99"/>
       <c r="F35" s="16"/>
-      <c r="G35" s="63"/>
-      <c r="H35" s="64"/>
-      <c r="I35" s="63"/>
-      <c r="J35" s="65"/>
-      <c r="K35" s="66"/>
-      <c r="L35" s="47"/>
+      <c r="G35" s="64"/>
+      <c r="H35" s="99"/>
+      <c r="I35" s="64"/>
+      <c r="J35" s="70"/>
+      <c r="K35" s="71"/>
+      <c r="L35" s="24"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="49"/>
-      <c r="O35" s="47"/>
+      <c r="N35" s="22"/>
+      <c r="O35" s="24"/>
     </row>
     <row r="36" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B36" s="15" t="s">
         <v>118</v>
       </c>
       <c r="C36" s="15"/>
-      <c r="D36" s="63"/>
-      <c r="E36" s="64"/>
+      <c r="D36" s="64"/>
+      <c r="E36" s="99"/>
       <c r="F36" s="16"/>
-      <c r="G36" s="63"/>
-      <c r="H36" s="64"/>
-      <c r="I36" s="63"/>
-      <c r="J36" s="65"/>
-      <c r="K36" s="66"/>
-      <c r="L36" s="47"/>
+      <c r="G36" s="64"/>
+      <c r="H36" s="99"/>
+      <c r="I36" s="64"/>
+      <c r="J36" s="70"/>
+      <c r="K36" s="71"/>
+      <c r="L36" s="24"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="49"/>
-      <c r="O36" s="47"/>
+      <c r="N36" s="22"/>
+      <c r="O36" s="24"/>
     </row>
     <row r="37" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B37" s="15" t="s">
         <v>119</v>
       </c>
       <c r="C37" s="15"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="64"/>
+      <c r="D37" s="64"/>
+      <c r="E37" s="99"/>
       <c r="F37" s="16"/>
-      <c r="G37" s="63"/>
-      <c r="H37" s="64"/>
-      <c r="I37" s="63"/>
-      <c r="J37" s="65"/>
-      <c r="K37" s="66"/>
-      <c r="L37" s="47"/>
+      <c r="G37" s="64"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="64"/>
+      <c r="J37" s="70"/>
+      <c r="K37" s="71"/>
+      <c r="L37" s="24"/>
       <c r="M37" s="4"/>
-      <c r="N37" s="49"/>
-      <c r="O37" s="47"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="24"/>
     </row>
     <row r="38" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="53" t="s">
+      <c r="B38" s="134" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="54"/>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="54"/>
-      <c r="H38" s="54"/>
-      <c r="I38" s="54"/>
-      <c r="J38" s="54"/>
-      <c r="K38" s="35"/>
-      <c r="L38" s="35"/>
-      <c r="M38" s="35"/>
-      <c r="N38" s="35"/>
-      <c r="O38" s="36"/>
+      <c r="C38" s="135"/>
+      <c r="D38" s="135"/>
+      <c r="E38" s="135"/>
+      <c r="F38" s="135"/>
+      <c r="G38" s="135"/>
+      <c r="H38" s="135"/>
+      <c r="I38" s="135"/>
+      <c r="J38" s="135"/>
+      <c r="K38" s="132"/>
+      <c r="L38" s="132"/>
+      <c r="M38" s="132"/>
+      <c r="N38" s="132"/>
+      <c r="O38" s="133"/>
     </row>
     <row r="39" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="55" t="s">
+      <c r="B39" s="136" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="56"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="56"/>
-      <c r="F39" s="56"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="56"/>
-      <c r="I39" s="56"/>
-      <c r="J39" s="57"/>
-      <c r="K39" s="58" t="s">
+      <c r="C39" s="137"/>
+      <c r="D39" s="137"/>
+      <c r="E39" s="137"/>
+      <c r="F39" s="137"/>
+      <c r="G39" s="137"/>
+      <c r="H39" s="137"/>
+      <c r="I39" s="137"/>
+      <c r="J39" s="138"/>
+      <c r="K39" s="139" t="s">
         <v>140</v>
       </c>
-      <c r="L39" s="59"/>
-      <c r="M39" s="59"/>
-      <c r="N39" s="59"/>
-      <c r="O39" s="60"/>
+      <c r="L39" s="140"/>
+      <c r="M39" s="140"/>
+      <c r="N39" s="140"/>
+      <c r="O39" s="141"/>
     </row>
     <row r="40" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B40" s="67" t="s">
+      <c r="B40" s="102" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="68"/>
-      <c r="D40" s="67" t="s">
+      <c r="C40" s="29"/>
+      <c r="D40" s="102" t="s">
         <v>28</v>
       </c>
-      <c r="E40" s="68"/>
+      <c r="E40" s="29"/>
       <c r="F40" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G40" s="67" t="s">
+      <c r="G40" s="102" t="s">
         <v>30</v>
       </c>
-      <c r="H40" s="68"/>
-      <c r="I40" s="67" t="s">
+      <c r="H40" s="29"/>
+      <c r="I40" s="102" t="s">
         <v>169</v>
       </c>
-      <c r="J40" s="69"/>
-      <c r="K40" s="70" t="s">
+      <c r="J40" s="152"/>
+      <c r="K40" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="L40" s="71"/>
+      <c r="L40" s="123"/>
       <c r="M40" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="N40" s="72" t="s">
+      <c r="N40" s="122" t="s">
         <v>30</v>
       </c>
-      <c r="O40" s="71"/>
+      <c r="O40" s="123"/>
     </row>
     <row r="41" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B41" s="50" t="s">
+      <c r="B41" s="101" t="s">
         <v>116</v>
       </c>
-      <c r="C41" s="47"/>
-      <c r="D41" s="49"/>
-      <c r="E41" s="47"/>
+      <c r="C41" s="24"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="24"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="49"/>
-      <c r="H41" s="47"/>
-      <c r="I41" s="49"/>
-      <c r="J41" s="51"/>
-      <c r="K41" s="52"/>
-      <c r="L41" s="47"/>
+      <c r="G41" s="22"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="22"/>
+      <c r="J41" s="100"/>
+      <c r="K41" s="66"/>
+      <c r="L41" s="24"/>
       <c r="M41" s="4"/>
-      <c r="N41" s="49"/>
-      <c r="O41" s="47"/>
+      <c r="N41" s="22"/>
+      <c r="O41" s="24"/>
     </row>
     <row r="42" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B42" s="50" t="s">
+      <c r="B42" s="101" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="47"/>
-      <c r="D42" s="49"/>
-      <c r="E42" s="47"/>
+      <c r="C42" s="24"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="24"/>
       <c r="F42" s="4"/>
-      <c r="G42" s="49"/>
-      <c r="H42" s="47"/>
-      <c r="I42" s="49"/>
-      <c r="J42" s="51"/>
-      <c r="K42" s="52"/>
-      <c r="L42" s="47"/>
+      <c r="G42" s="22"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="22"/>
+      <c r="J42" s="100"/>
+      <c r="K42" s="66"/>
+      <c r="L42" s="24"/>
       <c r="M42" s="4"/>
-      <c r="N42" s="49"/>
-      <c r="O42" s="47"/>
+      <c r="N42" s="22"/>
+      <c r="O42" s="24"/>
     </row>
     <row r="43" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B43" s="50" t="s">
+      <c r="B43" s="101" t="s">
         <v>118</v>
       </c>
-      <c r="C43" s="47"/>
-      <c r="D43" s="49"/>
-      <c r="E43" s="47"/>
+      <c r="C43" s="24"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="24"/>
       <c r="F43" s="4"/>
-      <c r="G43" s="49"/>
-      <c r="H43" s="47"/>
-      <c r="I43" s="49"/>
-      <c r="J43" s="51"/>
-      <c r="K43" s="52"/>
-      <c r="L43" s="47"/>
+      <c r="G43" s="22"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="22"/>
+      <c r="J43" s="100"/>
+      <c r="K43" s="66"/>
+      <c r="L43" s="24"/>
       <c r="M43" s="4"/>
-      <c r="N43" s="49"/>
-      <c r="O43" s="47"/>
+      <c r="N43" s="22"/>
+      <c r="O43" s="24"/>
     </row>
     <row r="44" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B44" s="50" t="s">
+      <c r="B44" s="101" t="s">
         <v>119</v>
       </c>
-      <c r="C44" s="47"/>
-      <c r="D44" s="49"/>
-      <c r="E44" s="47"/>
+      <c r="C44" s="24"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="24"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="49"/>
-      <c r="H44" s="47"/>
-      <c r="I44" s="49"/>
-      <c r="J44" s="51"/>
-      <c r="K44" s="52"/>
-      <c r="L44" s="47"/>
+      <c r="G44" s="22"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="22"/>
+      <c r="J44" s="100"/>
+      <c r="K44" s="66"/>
+      <c r="L44" s="24"/>
       <c r="M44" s="4"/>
-      <c r="N44" s="49"/>
-      <c r="O44" s="47"/>
+      <c r="N44" s="22"/>
+      <c r="O44" s="24"/>
     </row>
     <row r="45" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B45" s="50"/>
-      <c r="C45" s="47"/>
-      <c r="D45" s="49"/>
-      <c r="E45" s="47"/>
+      <c r="B45" s="101"/>
+      <c r="C45" s="24"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="24"/>
       <c r="F45" s="4"/>
-      <c r="G45" s="49"/>
-      <c r="H45" s="47"/>
-      <c r="I45" s="49"/>
-      <c r="J45" s="51"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="47"/>
+      <c r="G45" s="22"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="22"/>
+      <c r="J45" s="100"/>
+      <c r="K45" s="66"/>
+      <c r="L45" s="24"/>
       <c r="M45" s="4"/>
-      <c r="N45" s="49"/>
-      <c r="O45" s="47"/>
+      <c r="N45" s="22"/>
+      <c r="O45" s="24"/>
     </row>
     <row r="46" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B46" s="50"/>
-      <c r="C46" s="47"/>
-      <c r="D46" s="49"/>
-      <c r="E46" s="47"/>
+      <c r="B46" s="101"/>
+      <c r="C46" s="24"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="24"/>
       <c r="F46" s="4"/>
-      <c r="G46" s="49"/>
-      <c r="H46" s="47"/>
-      <c r="I46" s="49"/>
-      <c r="J46" s="51"/>
-      <c r="K46" s="52"/>
-      <c r="L46" s="47"/>
+      <c r="G46" s="22"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="22"/>
+      <c r="J46" s="100"/>
+      <c r="K46" s="66"/>
+      <c r="L46" s="24"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="49"/>
-      <c r="O46" s="47"/>
+      <c r="N46" s="22"/>
+      <c r="O46" s="24"/>
     </row>
     <row r="47" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="5"/>
@@ -4365,96 +4367,96 @@
       <c r="O47" s="5"/>
     </row>
     <row r="48" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="43" t="s">
+      <c r="B48" s="67" t="s">
         <v>31</v>
       </c>
-      <c r="C48" s="44"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="44"/>
-      <c r="F48" s="44"/>
-      <c r="G48" s="44"/>
-      <c r="H48" s="44"/>
-      <c r="I48" s="44"/>
-      <c r="J48" s="44"/>
-      <c r="K48" s="44"/>
-      <c r="L48" s="44"/>
-      <c r="M48" s="44"/>
-      <c r="N48" s="44"/>
-      <c r="O48" s="45"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="68"/>
+      <c r="G48" s="68"/>
+      <c r="H48" s="68"/>
+      <c r="I48" s="68"/>
+      <c r="J48" s="68"/>
+      <c r="K48" s="68"/>
+      <c r="L48" s="68"/>
+      <c r="M48" s="68"/>
+      <c r="N48" s="68"/>
+      <c r="O48" s="69"/>
     </row>
     <row r="49" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B49" s="123" t="s">
+      <c r="B49" s="86" t="s">
         <v>32</v>
       </c>
-      <c r="C49" s="33"/>
-      <c r="D49" s="33"/>
-      <c r="E49" s="33"/>
-      <c r="F49" s="33"/>
-      <c r="G49" s="33"/>
-      <c r="H49" s="33"/>
-      <c r="I49" s="33"/>
-      <c r="J49" s="33"/>
-      <c r="K49" s="33"/>
-      <c r="L49" s="33"/>
-      <c r="M49" s="33"/>
-      <c r="N49" s="33"/>
-      <c r="O49" s="47"/>
+      <c r="C49" s="23"/>
+      <c r="D49" s="23"/>
+      <c r="E49" s="23"/>
+      <c r="F49" s="23"/>
+      <c r="G49" s="23"/>
+      <c r="H49" s="23"/>
+      <c r="I49" s="23"/>
+      <c r="J49" s="23"/>
+      <c r="K49" s="23"/>
+      <c r="L49" s="23"/>
+      <c r="M49" s="23"/>
+      <c r="N49" s="23"/>
+      <c r="O49" s="24"/>
     </row>
     <row r="50" spans="2:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="32" t="s">
+      <c r="B50" s="40" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="33"/>
-      <c r="D50" s="47"/>
-      <c r="E50" s="32" t="s">
+      <c r="C50" s="23"/>
+      <c r="D50" s="24"/>
+      <c r="E50" s="40" t="s">
         <v>33</v>
       </c>
-      <c r="F50" s="33"/>
-      <c r="G50" s="47"/>
-      <c r="H50" s="32" t="s">
+      <c r="F50" s="23"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="47"/>
-      <c r="L50" s="32" t="s">
+      <c r="I50" s="23"/>
+      <c r="J50" s="23"/>
+      <c r="K50" s="24"/>
+      <c r="L50" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="M50" s="33"/>
-      <c r="N50" s="33"/>
-      <c r="O50" s="47"/>
+      <c r="M50" s="23"/>
+      <c r="N50" s="23"/>
+      <c r="O50" s="24"/>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B51" s="49"/>
-      <c r="C51" s="102"/>
-      <c r="D51" s="103"/>
-      <c r="E51" s="49"/>
-      <c r="F51" s="102"/>
-      <c r="G51" s="103"/>
-      <c r="H51" s="49"/>
-      <c r="I51" s="102"/>
-      <c r="J51" s="102"/>
-      <c r="K51" s="103"/>
-      <c r="L51" s="49"/>
-      <c r="M51" s="102"/>
-      <c r="N51" s="102"/>
-      <c r="O51" s="103"/>
+      <c r="B51" s="22"/>
+      <c r="C51" s="25"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="22"/>
+      <c r="F51" s="25"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="22"/>
+      <c r="I51" s="25"/>
+      <c r="J51" s="25"/>
+      <c r="K51" s="26"/>
+      <c r="L51" s="22"/>
+      <c r="M51" s="25"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="26"/>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B52" s="104"/>
-      <c r="C52" s="105"/>
-      <c r="D52" s="68"/>
-      <c r="E52" s="104"/>
-      <c r="F52" s="105"/>
-      <c r="G52" s="68"/>
-      <c r="H52" s="104"/>
-      <c r="I52" s="105"/>
-      <c r="J52" s="105"/>
-      <c r="K52" s="68"/>
-      <c r="L52" s="104"/>
-      <c r="M52" s="105"/>
-      <c r="N52" s="105"/>
-      <c r="O52" s="68"/>
+      <c r="B52" s="27"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="27"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="27"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="27"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="29"/>
     </row>
     <row r="53" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B53" s="5"/>
@@ -4473,46 +4475,46 @@
       <c r="O53" s="5"/>
     </row>
     <row r="54" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B54" s="123" t="s">
+      <c r="B54" s="86" t="s">
         <v>35</v>
       </c>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="33"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="33"/>
-      <c r="L54" s="33"/>
-      <c r="M54" s="33"/>
-      <c r="N54" s="33"/>
-      <c r="O54" s="47"/>
+      <c r="C54" s="23"/>
+      <c r="D54" s="23"/>
+      <c r="E54" s="23"/>
+      <c r="F54" s="23"/>
+      <c r="G54" s="23"/>
+      <c r="H54" s="23"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="23"/>
+      <c r="K54" s="23"/>
+      <c r="L54" s="23"/>
+      <c r="M54" s="23"/>
+      <c r="N54" s="23"/>
+      <c r="O54" s="24"/>
     </row>
     <row r="55" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B55" s="32" t="s">
+      <c r="B55" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="C55" s="33"/>
-      <c r="D55" s="47"/>
-      <c r="E55" s="32" t="s">
+      <c r="C55" s="23"/>
+      <c r="D55" s="24"/>
+      <c r="E55" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="F55" s="33"/>
-      <c r="G55" s="47"/>
-      <c r="H55" s="32" t="s">
+      <c r="F55" s="23"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="I55" s="33"/>
-      <c r="J55" s="33"/>
-      <c r="K55" s="47"/>
-      <c r="L55" s="32" t="s">
+      <c r="I55" s="23"/>
+      <c r="J55" s="23"/>
+      <c r="K55" s="24"/>
+      <c r="L55" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="M55" s="33"/>
-      <c r="N55" s="33"/>
-      <c r="O55" s="47"/>
+      <c r="M55" s="23"/>
+      <c r="N55" s="23"/>
+      <c r="O55" s="24"/>
     </row>
     <row r="56" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="93" t="s">
@@ -4520,155 +4522,155 @@
       </c>
       <c r="C56" s="94"/>
       <c r="D56" s="95"/>
-      <c r="E56" s="49" t="s">
+      <c r="E56" s="22" t="s">
         <v>154</v>
       </c>
-      <c r="F56" s="102"/>
-      <c r="G56" s="103"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="102"/>
-      <c r="J56" s="102"/>
-      <c r="K56" s="103"/>
-      <c r="L56" s="49"/>
-      <c r="M56" s="102"/>
-      <c r="N56" s="102"/>
-      <c r="O56" s="103"/>
+      <c r="F56" s="25"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="22"/>
+      <c r="I56" s="25"/>
+      <c r="J56" s="25"/>
+      <c r="K56" s="26"/>
+      <c r="L56" s="22"/>
+      <c r="M56" s="25"/>
+      <c r="N56" s="25"/>
+      <c r="O56" s="26"/>
     </row>
     <row r="57" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="96"/>
       <c r="C57" s="97"/>
       <c r="D57" s="98"/>
-      <c r="E57" s="104"/>
-      <c r="F57" s="105"/>
-      <c r="G57" s="68"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105"/>
-      <c r="J57" s="105"/>
-      <c r="K57" s="68"/>
-      <c r="L57" s="104"/>
-      <c r="M57" s="105"/>
-      <c r="N57" s="105"/>
-      <c r="O57" s="68"/>
+      <c r="E57" s="27"/>
+      <c r="F57" s="28"/>
+      <c r="G57" s="29"/>
+      <c r="H57" s="27"/>
+      <c r="I57" s="28"/>
+      <c r="J57" s="28"/>
+      <c r="K57" s="29"/>
+      <c r="L57" s="27"/>
+      <c r="M57" s="28"/>
+      <c r="N57" s="28"/>
+      <c r="O57" s="29"/>
     </row>
     <row r="58" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B58" s="32" t="s">
+      <c r="B58" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="C58" s="33"/>
-      <c r="D58" s="47"/>
-      <c r="E58" s="32" t="s">
+      <c r="C58" s="23"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="F58" s="33"/>
-      <c r="G58" s="47"/>
-      <c r="H58" s="32" t="s">
+      <c r="F58" s="23"/>
+      <c r="G58" s="24"/>
+      <c r="H58" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="I58" s="33"/>
-      <c r="J58" s="33"/>
-      <c r="K58" s="47"/>
-      <c r="L58" s="32" t="s">
+      <c r="I58" s="23"/>
+      <c r="J58" s="23"/>
+      <c r="K58" s="24"/>
+      <c r="L58" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="M58" s="33"/>
-      <c r="N58" s="33"/>
-      <c r="O58" s="47"/>
-    </row>
-    <row r="59" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M58" s="23"/>
+      <c r="N58" s="23"/>
+      <c r="O58" s="24"/>
+    </row>
+    <row r="59" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="93" t="s">
         <v>134</v>
       </c>
       <c r="C59" s="94"/>
       <c r="D59" s="95"/>
-      <c r="E59" s="49" t="s">
+      <c r="E59" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="F59" s="102"/>
-      <c r="G59" s="103"/>
-      <c r="H59" s="49"/>
-      <c r="I59" s="102"/>
-      <c r="J59" s="102"/>
-      <c r="K59" s="103"/>
-      <c r="L59" s="49"/>
-      <c r="M59" s="102"/>
-      <c r="N59" s="102"/>
-      <c r="O59" s="103"/>
-    </row>
-    <row r="60" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F59" s="25"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="22"/>
+      <c r="I59" s="25"/>
+      <c r="J59" s="25"/>
+      <c r="K59" s="26"/>
+      <c r="L59" s="22"/>
+      <c r="M59" s="25"/>
+      <c r="N59" s="25"/>
+      <c r="O59" s="26"/>
+    </row>
+    <row r="60" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="96"/>
       <c r="C60" s="97"/>
       <c r="D60" s="98"/>
-      <c r="E60" s="104"/>
-      <c r="F60" s="105"/>
-      <c r="G60" s="68"/>
-      <c r="H60" s="104"/>
-      <c r="I60" s="105"/>
-      <c r="J60" s="105"/>
-      <c r="K60" s="68"/>
-      <c r="L60" s="104"/>
-      <c r="M60" s="105"/>
-      <c r="N60" s="105"/>
-      <c r="O60" s="68"/>
+      <c r="E60" s="27"/>
+      <c r="F60" s="28"/>
+      <c r="G60" s="29"/>
+      <c r="H60" s="27"/>
+      <c r="I60" s="28"/>
+      <c r="J60" s="28"/>
+      <c r="K60" s="29"/>
+      <c r="L60" s="27"/>
+      <c r="M60" s="28"/>
+      <c r="N60" s="28"/>
+      <c r="O60" s="29"/>
     </row>
     <row r="61" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B61" s="32" t="s">
+      <c r="B61" s="40" t="s">
         <v>136</v>
       </c>
-      <c r="C61" s="33"/>
-      <c r="D61" s="47"/>
-      <c r="E61" s="32" t="s">
+      <c r="C61" s="23"/>
+      <c r="D61" s="24"/>
+      <c r="E61" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="F61" s="33"/>
-      <c r="G61" s="47"/>
-      <c r="H61" s="32" t="s">
+      <c r="F61" s="23"/>
+      <c r="G61" s="24"/>
+      <c r="H61" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="I61" s="33"/>
-      <c r="J61" s="33"/>
-      <c r="K61" s="47"/>
-      <c r="L61" s="32" t="s">
+      <c r="I61" s="23"/>
+      <c r="J61" s="23"/>
+      <c r="K61" s="24"/>
+      <c r="L61" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="M61" s="33"/>
-      <c r="N61" s="33"/>
-      <c r="O61" s="47"/>
-    </row>
-    <row r="62" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M61" s="23"/>
+      <c r="N61" s="23"/>
+      <c r="O61" s="24"/>
+    </row>
+    <row r="62" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="93" t="s">
         <v>172</v>
       </c>
       <c r="C62" s="94"/>
       <c r="D62" s="95"/>
-      <c r="E62" s="49" t="s">
+      <c r="E62" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="F62" s="102"/>
-      <c r="G62" s="103"/>
-      <c r="H62" s="49"/>
-      <c r="I62" s="102"/>
-      <c r="J62" s="102"/>
-      <c r="K62" s="103"/>
-      <c r="L62" s="49"/>
-      <c r="M62" s="102"/>
-      <c r="N62" s="102"/>
-      <c r="O62" s="103"/>
-    </row>
-    <row r="63" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F62" s="25"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="25"/>
+      <c r="J62" s="25"/>
+      <c r="K62" s="26"/>
+      <c r="L62" s="22"/>
+      <c r="M62" s="25"/>
+      <c r="N62" s="25"/>
+      <c r="O62" s="26"/>
+    </row>
+    <row r="63" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="96"/>
       <c r="C63" s="97"/>
       <c r="D63" s="98"/>
-      <c r="E63" s="104"/>
-      <c r="F63" s="105"/>
-      <c r="G63" s="68"/>
-      <c r="H63" s="104"/>
-      <c r="I63" s="105"/>
-      <c r="J63" s="105"/>
-      <c r="K63" s="68"/>
-      <c r="L63" s="104"/>
-      <c r="M63" s="105"/>
-      <c r="N63" s="105"/>
-      <c r="O63" s="68"/>
+      <c r="E63" s="27"/>
+      <c r="F63" s="28"/>
+      <c r="G63" s="29"/>
+      <c r="H63" s="27"/>
+      <c r="I63" s="28"/>
+      <c r="J63" s="28"/>
+      <c r="K63" s="29"/>
+      <c r="L63" s="27"/>
+      <c r="M63" s="28"/>
+      <c r="N63" s="28"/>
+      <c r="O63" s="29"/>
     </row>
     <row r="64" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B64" s="5"/>
@@ -4687,41 +4689,41 @@
       <c r="O64" s="5"/>
     </row>
     <row r="65" spans="2:15" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="43" t="s">
+      <c r="B65" s="67" t="s">
         <v>157</v>
       </c>
-      <c r="C65" s="44"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="44"/>
-      <c r="F65" s="44"/>
-      <c r="G65" s="44"/>
-      <c r="H65" s="44"/>
-      <c r="I65" s="44"/>
-      <c r="J65" s="44"/>
-      <c r="K65" s="44"/>
-      <c r="L65" s="44"/>
-      <c r="M65" s="44"/>
-      <c r="N65" s="44"/>
-      <c r="O65" s="45"/>
+      <c r="C65" s="68"/>
+      <c r="D65" s="68"/>
+      <c r="E65" s="68"/>
+      <c r="F65" s="68"/>
+      <c r="G65" s="68"/>
+      <c r="H65" s="68"/>
+      <c r="I65" s="68"/>
+      <c r="J65" s="68"/>
+      <c r="K65" s="68"/>
+      <c r="L65" s="68"/>
+      <c r="M65" s="68"/>
+      <c r="N65" s="68"/>
+      <c r="O65" s="69"/>
     </row>
     <row r="66" spans="2:15" ht="33" x14ac:dyDescent="0.3">
-      <c r="B66" s="122" t="s">
+      <c r="B66" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="C66" s="47"/>
+      <c r="C66" s="24"/>
       <c r="D66" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E66" s="122" t="s">
+      <c r="E66" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="F66" s="33"/>
-      <c r="G66" s="47"/>
-      <c r="H66" s="122" t="s">
+      <c r="F66" s="23"/>
+      <c r="G66" s="24"/>
+      <c r="H66" s="30" t="s">
         <v>42</v>
       </c>
-      <c r="I66" s="33"/>
-      <c r="J66" s="47"/>
+      <c r="I66" s="23"/>
+      <c r="J66" s="24"/>
       <c r="K66" s="6" t="s">
         <v>43</v>
       </c>
@@ -4731,340 +4733,340 @@
       <c r="M66" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N66" s="122" t="s">
+      <c r="N66" s="30" t="s">
         <v>46</v>
       </c>
-      <c r="O66" s="47"/>
+      <c r="O66" s="24"/>
     </row>
     <row r="67" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B67" s="112" t="s">
+      <c r="B67" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="C67" s="103"/>
+      <c r="C67" s="26"/>
       <c r="D67" s="4"/>
-      <c r="E67" s="49"/>
-      <c r="F67" s="33"/>
-      <c r="G67" s="47"/>
-      <c r="H67" s="49"/>
-      <c r="I67" s="33"/>
-      <c r="J67" s="47"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="23"/>
+      <c r="G67" s="24"/>
+      <c r="H67" s="22"/>
+      <c r="I67" s="23"/>
+      <c r="J67" s="24"/>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="49"/>
-      <c r="O67" s="47"/>
+      <c r="N67" s="22"/>
+      <c r="O67" s="24"/>
     </row>
     <row r="68" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B68" s="106"/>
-      <c r="C68" s="108"/>
+      <c r="B68" s="62"/>
+      <c r="C68" s="63"/>
       <c r="D68" s="4"/>
-      <c r="E68" s="49"/>
-      <c r="F68" s="33"/>
-      <c r="G68" s="47"/>
-      <c r="H68" s="49"/>
-      <c r="I68" s="33"/>
-      <c r="J68" s="47"/>
+      <c r="E68" s="22"/>
+      <c r="F68" s="23"/>
+      <c r="G68" s="24"/>
+      <c r="H68" s="22"/>
+      <c r="I68" s="23"/>
+      <c r="J68" s="24"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="49"/>
-      <c r="O68" s="47"/>
+      <c r="N68" s="22"/>
+      <c r="O68" s="24"/>
     </row>
     <row r="69" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B69" s="106"/>
-      <c r="C69" s="108"/>
+      <c r="B69" s="62"/>
+      <c r="C69" s="63"/>
       <c r="D69" s="4"/>
-      <c r="E69" s="49"/>
-      <c r="F69" s="33"/>
-      <c r="G69" s="47"/>
-      <c r="H69" s="49"/>
-      <c r="I69" s="33"/>
-      <c r="J69" s="47"/>
+      <c r="E69" s="22"/>
+      <c r="F69" s="23"/>
+      <c r="G69" s="24"/>
+      <c r="H69" s="22"/>
+      <c r="I69" s="23"/>
+      <c r="J69" s="24"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="49"/>
-      <c r="O69" s="47"/>
+      <c r="N69" s="22"/>
+      <c r="O69" s="24"/>
     </row>
     <row r="70" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B70" s="104"/>
-      <c r="C70" s="68"/>
+      <c r="B70" s="27"/>
+      <c r="C70" s="29"/>
       <c r="D70" s="4"/>
-      <c r="E70" s="49"/>
-      <c r="F70" s="33"/>
-      <c r="G70" s="47"/>
-      <c r="H70" s="49"/>
-      <c r="I70" s="33"/>
-      <c r="J70" s="47"/>
+      <c r="E70" s="22"/>
+      <c r="F70" s="23"/>
+      <c r="G70" s="24"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="23"/>
+      <c r="J70" s="24"/>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
-      <c r="N70" s="49"/>
-      <c r="O70" s="47"/>
+      <c r="N70" s="22"/>
+      <c r="O70" s="24"/>
     </row>
     <row r="71" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B71" s="112" t="s">
+      <c r="B71" s="61" t="s">
         <v>48</v>
       </c>
-      <c r="C71" s="103"/>
+      <c r="C71" s="26"/>
       <c r="D71" s="4"/>
-      <c r="E71" s="49"/>
-      <c r="F71" s="33"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="49"/>
-      <c r="I71" s="33"/>
-      <c r="J71" s="47"/>
+      <c r="E71" s="22"/>
+      <c r="F71" s="23"/>
+      <c r="G71" s="24"/>
+      <c r="H71" s="22"/>
+      <c r="I71" s="23"/>
+      <c r="J71" s="24"/>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
-      <c r="N71" s="49"/>
-      <c r="O71" s="47"/>
+      <c r="N71" s="22"/>
+      <c r="O71" s="24"/>
     </row>
     <row r="72" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B72" s="106"/>
-      <c r="C72" s="108"/>
+      <c r="B72" s="62"/>
+      <c r="C72" s="63"/>
       <c r="D72" s="4"/>
-      <c r="E72" s="49"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="47"/>
-      <c r="H72" s="49"/>
-      <c r="I72" s="33"/>
-      <c r="J72" s="47"/>
+      <c r="E72" s="22"/>
+      <c r="F72" s="23"/>
+      <c r="G72" s="24"/>
+      <c r="H72" s="22"/>
+      <c r="I72" s="23"/>
+      <c r="J72" s="24"/>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
-      <c r="N72" s="49"/>
-      <c r="O72" s="47"/>
+      <c r="N72" s="22"/>
+      <c r="O72" s="24"/>
     </row>
     <row r="73" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B73" s="106"/>
-      <c r="C73" s="108"/>
+      <c r="B73" s="62"/>
+      <c r="C73" s="63"/>
       <c r="D73" s="4"/>
-      <c r="E73" s="49"/>
-      <c r="F73" s="33"/>
-      <c r="G73" s="47"/>
-      <c r="H73" s="49"/>
-      <c r="I73" s="33"/>
-      <c r="J73" s="47"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="23"/>
+      <c r="G73" s="24"/>
+      <c r="H73" s="22"/>
+      <c r="I73" s="23"/>
+      <c r="J73" s="24"/>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
-      <c r="N73" s="49"/>
-      <c r="O73" s="47"/>
+      <c r="N73" s="22"/>
+      <c r="O73" s="24"/>
     </row>
     <row r="74" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B74" s="104"/>
-      <c r="C74" s="68"/>
+      <c r="B74" s="27"/>
+      <c r="C74" s="29"/>
       <c r="D74" s="4"/>
-      <c r="E74" s="49"/>
-      <c r="F74" s="33"/>
-      <c r="G74" s="47"/>
-      <c r="H74" s="49"/>
-      <c r="I74" s="33"/>
-      <c r="J74" s="47"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="23"/>
+      <c r="G74" s="24"/>
+      <c r="H74" s="22"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="24"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
-      <c r="N74" s="49"/>
-      <c r="O74" s="47"/>
+      <c r="N74" s="22"/>
+      <c r="O74" s="24"/>
     </row>
     <row r="75" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B75" s="112" t="s">
+      <c r="B75" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="C75" s="103"/>
+      <c r="C75" s="26"/>
       <c r="D75" s="4"/>
-      <c r="E75" s="49"/>
-      <c r="F75" s="33"/>
-      <c r="G75" s="47"/>
-      <c r="H75" s="49"/>
-      <c r="I75" s="33"/>
-      <c r="J75" s="47"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="23"/>
+      <c r="G75" s="24"/>
+      <c r="H75" s="22"/>
+      <c r="I75" s="23"/>
+      <c r="J75" s="24"/>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
-      <c r="N75" s="49"/>
-      <c r="O75" s="47"/>
+      <c r="N75" s="22"/>
+      <c r="O75" s="24"/>
     </row>
     <row r="76" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B76" s="106"/>
-      <c r="C76" s="108"/>
+      <c r="B76" s="62"/>
+      <c r="C76" s="63"/>
       <c r="D76" s="4"/>
-      <c r="E76" s="49"/>
-      <c r="F76" s="33"/>
-      <c r="G76" s="47"/>
-      <c r="H76" s="49"/>
-      <c r="I76" s="33"/>
-      <c r="J76" s="47"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="23"/>
+      <c r="G76" s="24"/>
+      <c r="H76" s="22"/>
+      <c r="I76" s="23"/>
+      <c r="J76" s="24"/>
       <c r="K76" s="4"/>
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="49"/>
-      <c r="O76" s="47"/>
+      <c r="N76" s="22"/>
+      <c r="O76" s="24"/>
     </row>
     <row r="77" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B77" s="106"/>
-      <c r="C77" s="108"/>
+      <c r="B77" s="62"/>
+      <c r="C77" s="63"/>
       <c r="D77" s="4"/>
-      <c r="E77" s="49"/>
-      <c r="F77" s="33"/>
-      <c r="G77" s="47"/>
-      <c r="H77" s="49"/>
-      <c r="I77" s="33"/>
-      <c r="J77" s="47"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="23"/>
+      <c r="G77" s="24"/>
+      <c r="H77" s="22"/>
+      <c r="I77" s="23"/>
+      <c r="J77" s="24"/>
       <c r="K77" s="4"/>
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="49"/>
-      <c r="O77" s="47"/>
+      <c r="N77" s="22"/>
+      <c r="O77" s="24"/>
     </row>
     <row r="78" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B78" s="104"/>
-      <c r="C78" s="68"/>
+      <c r="B78" s="27"/>
+      <c r="C78" s="29"/>
       <c r="D78" s="4"/>
-      <c r="E78" s="49"/>
-      <c r="F78" s="33"/>
-      <c r="G78" s="47"/>
-      <c r="H78" s="49"/>
-      <c r="I78" s="33"/>
-      <c r="J78" s="47"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="23"/>
+      <c r="G78" s="24"/>
+      <c r="H78" s="22"/>
+      <c r="I78" s="23"/>
+      <c r="J78" s="24"/>
       <c r="K78" s="4"/>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
-      <c r="N78" s="49"/>
-      <c r="O78" s="47"/>
+      <c r="N78" s="22"/>
+      <c r="O78" s="24"/>
     </row>
     <row r="79" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B79" s="112" t="s">
+      <c r="B79" s="61" t="s">
         <v>124</v>
       </c>
-      <c r="C79" s="103"/>
+      <c r="C79" s="26"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="49"/>
-      <c r="F79" s="33"/>
-      <c r="G79" s="47"/>
-      <c r="H79" s="49"/>
-      <c r="I79" s="33"/>
-      <c r="J79" s="47"/>
+      <c r="E79" s="22"/>
+      <c r="F79" s="23"/>
+      <c r="G79" s="24"/>
+      <c r="H79" s="22"/>
+      <c r="I79" s="23"/>
+      <c r="J79" s="24"/>
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
-      <c r="N79" s="49"/>
-      <c r="O79" s="47"/>
+      <c r="N79" s="22"/>
+      <c r="O79" s="24"/>
     </row>
     <row r="80" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B80" s="106"/>
-      <c r="C80" s="108"/>
+      <c r="B80" s="62"/>
+      <c r="C80" s="63"/>
       <c r="D80" s="4"/>
-      <c r="E80" s="49"/>
-      <c r="F80" s="33"/>
-      <c r="G80" s="47"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="33"/>
-      <c r="J80" s="47"/>
+      <c r="E80" s="22"/>
+      <c r="F80" s="23"/>
+      <c r="G80" s="24"/>
+      <c r="H80" s="22"/>
+      <c r="I80" s="23"/>
+      <c r="J80" s="24"/>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
-      <c r="N80" s="49"/>
-      <c r="O80" s="47"/>
+      <c r="N80" s="22"/>
+      <c r="O80" s="24"/>
     </row>
     <row r="81" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B81" s="106"/>
-      <c r="C81" s="108"/>
+      <c r="B81" s="62"/>
+      <c r="C81" s="63"/>
       <c r="D81" s="4"/>
-      <c r="E81" s="49"/>
-      <c r="F81" s="33"/>
-      <c r="G81" s="47"/>
-      <c r="H81" s="49"/>
-      <c r="I81" s="33"/>
-      <c r="J81" s="47"/>
+      <c r="E81" s="22"/>
+      <c r="F81" s="23"/>
+      <c r="G81" s="24"/>
+      <c r="H81" s="22"/>
+      <c r="I81" s="23"/>
+      <c r="J81" s="24"/>
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
-      <c r="N81" s="49"/>
-      <c r="O81" s="47"/>
+      <c r="N81" s="22"/>
+      <c r="O81" s="24"/>
     </row>
     <row r="82" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B82" s="104"/>
-      <c r="C82" s="68"/>
+      <c r="B82" s="27"/>
+      <c r="C82" s="29"/>
       <c r="D82" s="4"/>
-      <c r="E82" s="49"/>
-      <c r="F82" s="33"/>
-      <c r="G82" s="47"/>
-      <c r="H82" s="49"/>
-      <c r="I82" s="33"/>
-      <c r="J82" s="47"/>
+      <c r="E82" s="22"/>
+      <c r="F82" s="23"/>
+      <c r="G82" s="24"/>
+      <c r="H82" s="22"/>
+      <c r="I82" s="23"/>
+      <c r="J82" s="24"/>
       <c r="K82" s="4"/>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
-      <c r="N82" s="49"/>
-      <c r="O82" s="47"/>
+      <c r="N82" s="22"/>
+      <c r="O82" s="24"/>
     </row>
     <row r="83" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B83" s="112" t="s">
+      <c r="B83" s="61" t="s">
         <v>49</v>
       </c>
-      <c r="C83" s="103"/>
+      <c r="C83" s="26"/>
       <c r="D83" s="4"/>
-      <c r="E83" s="49"/>
-      <c r="F83" s="33"/>
-      <c r="G83" s="47"/>
-      <c r="H83" s="49"/>
-      <c r="I83" s="33"/>
-      <c r="J83" s="47"/>
+      <c r="E83" s="22"/>
+      <c r="F83" s="23"/>
+      <c r="G83" s="24"/>
+      <c r="H83" s="22"/>
+      <c r="I83" s="23"/>
+      <c r="J83" s="24"/>
       <c r="K83" s="4"/>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
-      <c r="N83" s="49"/>
-      <c r="O83" s="47"/>
+      <c r="N83" s="22"/>
+      <c r="O83" s="24"/>
     </row>
     <row r="84" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B84" s="106"/>
-      <c r="C84" s="108"/>
+      <c r="B84" s="62"/>
+      <c r="C84" s="63"/>
       <c r="D84" s="4"/>
-      <c r="E84" s="49"/>
-      <c r="F84" s="33"/>
-      <c r="G84" s="47"/>
-      <c r="H84" s="49"/>
-      <c r="I84" s="33"/>
-      <c r="J84" s="47"/>
+      <c r="E84" s="22"/>
+      <c r="F84" s="23"/>
+      <c r="G84" s="24"/>
+      <c r="H84" s="22"/>
+      <c r="I84" s="23"/>
+      <c r="J84" s="24"/>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
-      <c r="N84" s="49"/>
-      <c r="O84" s="47"/>
+      <c r="N84" s="22"/>
+      <c r="O84" s="24"/>
     </row>
     <row r="85" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B85" s="106"/>
-      <c r="C85" s="108"/>
+      <c r="B85" s="62"/>
+      <c r="C85" s="63"/>
       <c r="D85" s="4"/>
-      <c r="E85" s="49"/>
-      <c r="F85" s="33"/>
-      <c r="G85" s="47"/>
-      <c r="H85" s="49"/>
-      <c r="I85" s="33"/>
-      <c r="J85" s="47"/>
+      <c r="E85" s="22"/>
+      <c r="F85" s="23"/>
+      <c r="G85" s="24"/>
+      <c r="H85" s="22"/>
+      <c r="I85" s="23"/>
+      <c r="J85" s="24"/>
       <c r="K85" s="4"/>
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
-      <c r="N85" s="49"/>
-      <c r="O85" s="47"/>
+      <c r="N85" s="22"/>
+      <c r="O85" s="24"/>
     </row>
     <row r="86" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B86" s="104"/>
-      <c r="C86" s="68"/>
+      <c r="B86" s="27"/>
+      <c r="C86" s="29"/>
       <c r="D86" s="4"/>
-      <c r="E86" s="49"/>
-      <c r="F86" s="33"/>
-      <c r="G86" s="47"/>
-      <c r="H86" s="49"/>
-      <c r="I86" s="33"/>
-      <c r="J86" s="47"/>
+      <c r="E86" s="22"/>
+      <c r="F86" s="23"/>
+      <c r="G86" s="24"/>
+      <c r="H86" s="22"/>
+      <c r="I86" s="23"/>
+      <c r="J86" s="24"/>
       <c r="K86" s="4"/>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
-      <c r="N86" s="49"/>
-      <c r="O86" s="47"/>
+      <c r="N86" s="22"/>
+      <c r="O86" s="24"/>
     </row>
     <row r="87" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B87" s="5"/>
@@ -5083,118 +5085,118 @@
       <c r="O87" s="5"/>
     </row>
     <row r="88" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="43" t="s">
+      <c r="B88" s="67" t="s">
         <v>158</v>
       </c>
-      <c r="C88" s="44"/>
-      <c r="D88" s="44"/>
-      <c r="E88" s="44"/>
-      <c r="F88" s="44"/>
-      <c r="G88" s="44"/>
-      <c r="H88" s="44"/>
-      <c r="I88" s="44"/>
-      <c r="J88" s="44"/>
-      <c r="K88" s="44"/>
-      <c r="L88" s="44"/>
-      <c r="M88" s="44"/>
-      <c r="N88" s="44"/>
-      <c r="O88" s="45"/>
+      <c r="C88" s="68"/>
+      <c r="D88" s="68"/>
+      <c r="E88" s="68"/>
+      <c r="F88" s="68"/>
+      <c r="G88" s="68"/>
+      <c r="H88" s="68"/>
+      <c r="I88" s="68"/>
+      <c r="J88" s="68"/>
+      <c r="K88" s="68"/>
+      <c r="L88" s="68"/>
+      <c r="M88" s="68"/>
+      <c r="N88" s="68"/>
+      <c r="O88" s="69"/>
     </row>
     <row r="89" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B89" s="46" t="s">
+      <c r="B89" s="85" t="s">
         <v>27</v>
       </c>
-      <c r="C89" s="47"/>
-      <c r="D89" s="46" t="s">
+      <c r="C89" s="24"/>
+      <c r="D89" s="85" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="33"/>
-      <c r="F89" s="33"/>
-      <c r="G89" s="33"/>
-      <c r="H89" s="33"/>
-      <c r="I89" s="47"/>
-      <c r="J89" s="46" t="s">
+      <c r="E89" s="23"/>
+      <c r="F89" s="23"/>
+      <c r="G89" s="23"/>
+      <c r="H89" s="23"/>
+      <c r="I89" s="24"/>
+      <c r="J89" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="K89" s="33"/>
-      <c r="L89" s="47"/>
-      <c r="M89" s="46" t="s">
+      <c r="K89" s="23"/>
+      <c r="L89" s="24"/>
+      <c r="M89" s="85" t="s">
         <v>62</v>
       </c>
-      <c r="N89" s="33"/>
-      <c r="O89" s="47"/>
+      <c r="N89" s="23"/>
+      <c r="O89" s="24"/>
     </row>
     <row r="90" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B90" s="48" t="s">
+      <c r="B90" s="72" t="s">
         <v>63</v>
       </c>
-      <c r="C90" s="47"/>
-      <c r="D90" s="49"/>
-      <c r="E90" s="33"/>
-      <c r="F90" s="33"/>
-      <c r="G90" s="33"/>
-      <c r="H90" s="33"/>
-      <c r="I90" s="47"/>
-      <c r="J90" s="49"/>
-      <c r="K90" s="33"/>
-      <c r="L90" s="47"/>
-      <c r="M90" s="49"/>
-      <c r="N90" s="33"/>
-      <c r="O90" s="47"/>
+      <c r="C90" s="24"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="23"/>
+      <c r="F90" s="23"/>
+      <c r="G90" s="23"/>
+      <c r="H90" s="23"/>
+      <c r="I90" s="24"/>
+      <c r="J90" s="22"/>
+      <c r="K90" s="23"/>
+      <c r="L90" s="24"/>
+      <c r="M90" s="22"/>
+      <c r="N90" s="23"/>
+      <c r="O90" s="24"/>
     </row>
     <row r="91" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B91" s="48" t="s">
+      <c r="B91" s="72" t="s">
         <v>37</v>
       </c>
-      <c r="C91" s="47"/>
-      <c r="D91" s="49"/>
-      <c r="E91" s="33"/>
-      <c r="F91" s="33"/>
-      <c r="G91" s="33"/>
-      <c r="H91" s="33"/>
-      <c r="I91" s="47"/>
-      <c r="J91" s="49"/>
-      <c r="K91" s="33"/>
-      <c r="L91" s="47"/>
-      <c r="M91" s="49"/>
-      <c r="N91" s="33"/>
-      <c r="O91" s="47"/>
+      <c r="C91" s="24"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="23"/>
+      <c r="F91" s="23"/>
+      <c r="G91" s="23"/>
+      <c r="H91" s="23"/>
+      <c r="I91" s="24"/>
+      <c r="J91" s="22"/>
+      <c r="K91" s="23"/>
+      <c r="L91" s="24"/>
+      <c r="M91" s="22"/>
+      <c r="N91" s="23"/>
+      <c r="O91" s="24"/>
     </row>
     <row r="92" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B92" s="48" t="s">
+      <c r="B92" s="72" t="s">
         <v>64</v>
       </c>
-      <c r="C92" s="47"/>
-      <c r="D92" s="49"/>
-      <c r="E92" s="33"/>
-      <c r="F92" s="33"/>
-      <c r="G92" s="33"/>
-      <c r="H92" s="33"/>
-      <c r="I92" s="47"/>
-      <c r="J92" s="49"/>
-      <c r="K92" s="33"/>
-      <c r="L92" s="47"/>
-      <c r="M92" s="49"/>
-      <c r="N92" s="33"/>
-      <c r="O92" s="47"/>
+      <c r="C92" s="24"/>
+      <c r="D92" s="22"/>
+      <c r="E92" s="23"/>
+      <c r="F92" s="23"/>
+      <c r="G92" s="23"/>
+      <c r="H92" s="23"/>
+      <c r="I92" s="24"/>
+      <c r="J92" s="22"/>
+      <c r="K92" s="23"/>
+      <c r="L92" s="24"/>
+      <c r="M92" s="22"/>
+      <c r="N92" s="23"/>
+      <c r="O92" s="24"/>
     </row>
     <row r="93" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B93" s="48" t="s">
+      <c r="B93" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="C93" s="47"/>
-      <c r="D93" s="49"/>
-      <c r="E93" s="33"/>
-      <c r="F93" s="33"/>
-      <c r="G93" s="33"/>
-      <c r="H93" s="33"/>
-      <c r="I93" s="47"/>
-      <c r="J93" s="49"/>
-      <c r="K93" s="33"/>
-      <c r="L93" s="47"/>
-      <c r="M93" s="49"/>
-      <c r="N93" s="33"/>
-      <c r="O93" s="47"/>
+      <c r="C93" s="24"/>
+      <c r="D93" s="22"/>
+      <c r="E93" s="23"/>
+      <c r="F93" s="23"/>
+      <c r="G93" s="23"/>
+      <c r="H93" s="23"/>
+      <c r="I93" s="24"/>
+      <c r="J93" s="22"/>
+      <c r="K93" s="23"/>
+      <c r="L93" s="24"/>
+      <c r="M93" s="22"/>
+      <c r="N93" s="23"/>
+      <c r="O93" s="24"/>
     </row>
     <row r="94" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B94" s="5"/>
@@ -5213,154 +5215,154 @@
       <c r="O94" s="5"/>
     </row>
     <row r="95" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="43" t="s">
+      <c r="B95" s="67" t="s">
         <v>50</v>
       </c>
-      <c r="C95" s="44"/>
-      <c r="D95" s="44"/>
-      <c r="E95" s="44"/>
-      <c r="F95" s="44"/>
-      <c r="G95" s="44"/>
-      <c r="H95" s="44"/>
-      <c r="I95" s="44"/>
-      <c r="J95" s="44"/>
-      <c r="K95" s="44"/>
-      <c r="L95" s="44"/>
-      <c r="M95" s="44"/>
-      <c r="N95" s="44"/>
-      <c r="O95" s="45"/>
+      <c r="C95" s="68"/>
+      <c r="D95" s="68"/>
+      <c r="E95" s="68"/>
+      <c r="F95" s="68"/>
+      <c r="G95" s="68"/>
+      <c r="H95" s="68"/>
+      <c r="I95" s="68"/>
+      <c r="J95" s="68"/>
+      <c r="K95" s="68"/>
+      <c r="L95" s="68"/>
+      <c r="M95" s="68"/>
+      <c r="N95" s="68"/>
+      <c r="O95" s="69"/>
     </row>
     <row r="96" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B96" s="46" t="s">
+      <c r="B96" s="85" t="s">
         <v>51</v>
       </c>
-      <c r="C96" s="33"/>
-      <c r="D96" s="33"/>
-      <c r="E96" s="47"/>
-      <c r="F96" s="46" t="s">
+      <c r="C96" s="23"/>
+      <c r="D96" s="23"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="G96" s="47"/>
-      <c r="H96" s="46" t="s">
+      <c r="G96" s="24"/>
+      <c r="H96" s="85" t="s">
         <v>53</v>
       </c>
-      <c r="I96" s="33"/>
-      <c r="J96" s="33"/>
-      <c r="K96" s="33"/>
-      <c r="L96" s="33"/>
-      <c r="M96" s="47"/>
-      <c r="N96" s="46" t="s">
+      <c r="I96" s="23"/>
+      <c r="J96" s="23"/>
+      <c r="K96" s="23"/>
+      <c r="L96" s="23"/>
+      <c r="M96" s="24"/>
+      <c r="N96" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="O96" s="47"/>
+      <c r="O96" s="24"/>
     </row>
     <row r="97" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B97" s="48" t="s">
+      <c r="B97" s="72" t="s">
         <v>54</v>
       </c>
-      <c r="C97" s="33"/>
-      <c r="D97" s="33"/>
-      <c r="E97" s="47"/>
-      <c r="F97" s="49"/>
-      <c r="G97" s="47"/>
-      <c r="H97" s="49"/>
-      <c r="I97" s="33"/>
-      <c r="J97" s="33"/>
-      <c r="K97" s="33"/>
-      <c r="L97" s="33"/>
-      <c r="M97" s="47"/>
-      <c r="N97" s="49"/>
-      <c r="O97" s="47"/>
+      <c r="C97" s="23"/>
+      <c r="D97" s="23"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="22"/>
+      <c r="G97" s="24"/>
+      <c r="H97" s="22"/>
+      <c r="I97" s="23"/>
+      <c r="J97" s="23"/>
+      <c r="K97" s="23"/>
+      <c r="L97" s="23"/>
+      <c r="M97" s="24"/>
+      <c r="N97" s="22"/>
+      <c r="O97" s="24"/>
     </row>
     <row r="98" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B98" s="48" t="s">
+      <c r="B98" s="72" t="s">
         <v>55</v>
       </c>
-      <c r="C98" s="33"/>
-      <c r="D98" s="33"/>
-      <c r="E98" s="47"/>
-      <c r="F98" s="49"/>
-      <c r="G98" s="47"/>
-      <c r="H98" s="49"/>
-      <c r="I98" s="33"/>
-      <c r="J98" s="33"/>
-      <c r="K98" s="33"/>
-      <c r="L98" s="33"/>
-      <c r="M98" s="47"/>
-      <c r="N98" s="49"/>
-      <c r="O98" s="47"/>
+      <c r="C98" s="23"/>
+      <c r="D98" s="23"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="22"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="22"/>
+      <c r="I98" s="23"/>
+      <c r="J98" s="23"/>
+      <c r="K98" s="23"/>
+      <c r="L98" s="23"/>
+      <c r="M98" s="24"/>
+      <c r="N98" s="22"/>
+      <c r="O98" s="24"/>
     </row>
     <row r="99" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B99" s="48" t="s">
+      <c r="B99" s="72" t="s">
         <v>56</v>
       </c>
-      <c r="C99" s="33"/>
-      <c r="D99" s="33"/>
-      <c r="E99" s="47"/>
-      <c r="F99" s="49"/>
-      <c r="G99" s="47"/>
-      <c r="H99" s="49"/>
-      <c r="I99" s="33"/>
-      <c r="J99" s="33"/>
-      <c r="K99" s="33"/>
-      <c r="L99" s="33"/>
-      <c r="M99" s="47"/>
-      <c r="N99" s="49"/>
-      <c r="O99" s="47"/>
+      <c r="C99" s="23"/>
+      <c r="D99" s="23"/>
+      <c r="E99" s="24"/>
+      <c r="F99" s="22"/>
+      <c r="G99" s="24"/>
+      <c r="H99" s="22"/>
+      <c r="I99" s="23"/>
+      <c r="J99" s="23"/>
+      <c r="K99" s="23"/>
+      <c r="L99" s="23"/>
+      <c r="M99" s="24"/>
+      <c r="N99" s="22"/>
+      <c r="O99" s="24"/>
     </row>
     <row r="100" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B100" s="48" t="s">
+      <c r="B100" s="72" t="s">
         <v>57</v>
       </c>
-      <c r="C100" s="33"/>
-      <c r="D100" s="33"/>
-      <c r="E100" s="47"/>
-      <c r="F100" s="49"/>
-      <c r="G100" s="47"/>
-      <c r="H100" s="49"/>
-      <c r="I100" s="33"/>
-      <c r="J100" s="33"/>
-      <c r="K100" s="33"/>
-      <c r="L100" s="33"/>
-      <c r="M100" s="47"/>
-      <c r="N100" s="49"/>
-      <c r="O100" s="47"/>
+      <c r="C100" s="23"/>
+      <c r="D100" s="23"/>
+      <c r="E100" s="24"/>
+      <c r="F100" s="22"/>
+      <c r="G100" s="24"/>
+      <c r="H100" s="22"/>
+      <c r="I100" s="23"/>
+      <c r="J100" s="23"/>
+      <c r="K100" s="23"/>
+      <c r="L100" s="23"/>
+      <c r="M100" s="24"/>
+      <c r="N100" s="22"/>
+      <c r="O100" s="24"/>
     </row>
     <row r="101" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B101" s="48" t="s">
+      <c r="B101" s="72" t="s">
         <v>58</v>
       </c>
-      <c r="C101" s="33"/>
-      <c r="D101" s="33"/>
-      <c r="E101" s="47"/>
-      <c r="F101" s="49"/>
-      <c r="G101" s="47"/>
-      <c r="H101" s="49"/>
-      <c r="I101" s="33"/>
-      <c r="J101" s="33"/>
-      <c r="K101" s="33"/>
-      <c r="L101" s="33"/>
-      <c r="M101" s="47"/>
-      <c r="N101" s="49"/>
-      <c r="O101" s="47"/>
+      <c r="C101" s="23"/>
+      <c r="D101" s="23"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="22"/>
+      <c r="G101" s="24"/>
+      <c r="H101" s="22"/>
+      <c r="I101" s="23"/>
+      <c r="J101" s="23"/>
+      <c r="K101" s="23"/>
+      <c r="L101" s="23"/>
+      <c r="M101" s="24"/>
+      <c r="N101" s="22"/>
+      <c r="O101" s="24"/>
     </row>
     <row r="102" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B102" s="48" t="s">
+      <c r="B102" s="72" t="s">
         <v>59</v>
       </c>
-      <c r="C102" s="33"/>
-      <c r="D102" s="33"/>
-      <c r="E102" s="47"/>
-      <c r="F102" s="49"/>
-      <c r="G102" s="47"/>
-      <c r="H102" s="49"/>
-      <c r="I102" s="33"/>
-      <c r="J102" s="33"/>
-      <c r="K102" s="33"/>
-      <c r="L102" s="33"/>
-      <c r="M102" s="47"/>
-      <c r="N102" s="49"/>
-      <c r="O102" s="47"/>
+      <c r="C102" s="23"/>
+      <c r="D102" s="23"/>
+      <c r="E102" s="24"/>
+      <c r="F102" s="22"/>
+      <c r="G102" s="24"/>
+      <c r="H102" s="22"/>
+      <c r="I102" s="23"/>
+      <c r="J102" s="23"/>
+      <c r="K102" s="23"/>
+      <c r="L102" s="23"/>
+      <c r="M102" s="24"/>
+      <c r="N102" s="22"/>
+      <c r="O102" s="24"/>
     </row>
     <row r="103" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B103" s="5"/>
@@ -5379,145 +5381,145 @@
       <c r="O103" s="5"/>
     </row>
     <row r="104" spans="2:15" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="43" t="s">
+      <c r="B104" s="67" t="s">
         <v>159</v>
       </c>
-      <c r="C104" s="44"/>
-      <c r="D104" s="44"/>
-      <c r="E104" s="44"/>
-      <c r="F104" s="44"/>
-      <c r="G104" s="44"/>
-      <c r="H104" s="44"/>
-      <c r="I104" s="44"/>
-      <c r="J104" s="44"/>
-      <c r="K104" s="44"/>
-      <c r="L104" s="44"/>
-      <c r="M104" s="44"/>
-      <c r="N104" s="44"/>
-      <c r="O104" s="45"/>
+      <c r="C104" s="68"/>
+      <c r="D104" s="68"/>
+      <c r="E104" s="68"/>
+      <c r="F104" s="68"/>
+      <c r="G104" s="68"/>
+      <c r="H104" s="68"/>
+      <c r="I104" s="68"/>
+      <c r="J104" s="68"/>
+      <c r="K104" s="68"/>
+      <c r="L104" s="68"/>
+      <c r="M104" s="68"/>
+      <c r="N104" s="68"/>
+      <c r="O104" s="69"/>
     </row>
     <row r="105" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="127" t="s">
+      <c r="B105" s="73" t="s">
         <v>163</v>
       </c>
-      <c r="C105" s="128"/>
-      <c r="D105" s="128"/>
-      <c r="E105" s="128"/>
-      <c r="F105" s="128"/>
-      <c r="G105" s="128"/>
-      <c r="H105" s="128"/>
-      <c r="I105" s="128"/>
-      <c r="J105" s="128"/>
-      <c r="K105" s="128"/>
-      <c r="L105" s="128"/>
-      <c r="M105" s="128"/>
-      <c r="N105" s="128"/>
-      <c r="O105" s="128"/>
+      <c r="C105" s="74"/>
+      <c r="D105" s="74"/>
+      <c r="E105" s="74"/>
+      <c r="F105" s="74"/>
+      <c r="G105" s="74"/>
+      <c r="H105" s="74"/>
+      <c r="I105" s="74"/>
+      <c r="J105" s="74"/>
+      <c r="K105" s="74"/>
+      <c r="L105" s="74"/>
+      <c r="M105" s="74"/>
+      <c r="N105" s="74"/>
+      <c r="O105" s="74"/>
     </row>
     <row r="106" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B106" s="46" t="s">
+      <c r="B106" s="85" t="s">
         <v>66</v>
       </c>
-      <c r="C106" s="33"/>
-      <c r="D106" s="33"/>
-      <c r="E106" s="33"/>
-      <c r="F106" s="47"/>
-      <c r="G106" s="46" t="s">
+      <c r="C106" s="23"/>
+      <c r="D106" s="23"/>
+      <c r="E106" s="23"/>
+      <c r="F106" s="24"/>
+      <c r="G106" s="85" t="s">
         <v>67</v>
       </c>
-      <c r="H106" s="33"/>
-      <c r="I106" s="47"/>
-      <c r="J106" s="124" t="s">
+      <c r="H106" s="23"/>
+      <c r="I106" s="24"/>
+      <c r="J106" s="77" t="s">
         <v>161</v>
       </c>
-      <c r="K106" s="125"/>
-      <c r="L106" s="126"/>
-      <c r="M106" s="46" t="s">
+      <c r="K106" s="78"/>
+      <c r="L106" s="79"/>
+      <c r="M106" s="85" t="s">
         <v>43</v>
       </c>
-      <c r="N106" s="47"/>
+      <c r="N106" s="24"/>
       <c r="O106" s="6" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="107" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B107" s="49"/>
-      <c r="C107" s="33"/>
-      <c r="D107" s="33"/>
-      <c r="E107" s="33"/>
-      <c r="F107" s="47"/>
-      <c r="G107" s="49"/>
-      <c r="H107" s="33"/>
-      <c r="I107" s="47"/>
-      <c r="J107" s="22"/>
-      <c r="K107" s="23"/>
-      <c r="L107" s="23"/>
-      <c r="M107" s="22"/>
-      <c r="N107" s="31"/>
+      <c r="B107" s="22"/>
+      <c r="C107" s="23"/>
+      <c r="D107" s="23"/>
+      <c r="E107" s="23"/>
+      <c r="F107" s="24"/>
+      <c r="G107" s="22"/>
+      <c r="H107" s="23"/>
+      <c r="I107" s="24"/>
+      <c r="J107" s="80"/>
+      <c r="K107" s="81"/>
+      <c r="L107" s="81"/>
+      <c r="M107" s="80"/>
+      <c r="N107" s="130"/>
       <c r="O107" s="4"/>
     </row>
     <row r="108" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B108" s="49"/>
-      <c r="C108" s="33"/>
-      <c r="D108" s="33"/>
-      <c r="E108" s="33"/>
-      <c r="F108" s="47"/>
-      <c r="G108" s="49"/>
-      <c r="H108" s="33"/>
-      <c r="I108" s="47"/>
-      <c r="J108" s="22"/>
-      <c r="K108" s="23"/>
-      <c r="L108" s="23"/>
-      <c r="M108" s="22"/>
-      <c r="N108" s="31"/>
+      <c r="B108" s="22"/>
+      <c r="C108" s="23"/>
+      <c r="D108" s="23"/>
+      <c r="E108" s="23"/>
+      <c r="F108" s="24"/>
+      <c r="G108" s="22"/>
+      <c r="H108" s="23"/>
+      <c r="I108" s="24"/>
+      <c r="J108" s="80"/>
+      <c r="K108" s="81"/>
+      <c r="L108" s="81"/>
+      <c r="M108" s="80"/>
+      <c r="N108" s="130"/>
       <c r="O108" s="4"/>
     </row>
     <row r="109" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B109" s="49"/>
-      <c r="C109" s="33"/>
-      <c r="D109" s="33"/>
-      <c r="E109" s="33"/>
-      <c r="F109" s="47"/>
-      <c r="G109" s="49"/>
-      <c r="H109" s="33"/>
-      <c r="I109" s="47"/>
-      <c r="J109" s="22"/>
-      <c r="K109" s="23"/>
-      <c r="L109" s="23"/>
-      <c r="M109" s="22"/>
-      <c r="N109" s="31"/>
+      <c r="B109" s="22"/>
+      <c r="C109" s="23"/>
+      <c r="D109" s="23"/>
+      <c r="E109" s="23"/>
+      <c r="F109" s="24"/>
+      <c r="G109" s="22"/>
+      <c r="H109" s="23"/>
+      <c r="I109" s="24"/>
+      <c r="J109" s="80"/>
+      <c r="K109" s="81"/>
+      <c r="L109" s="81"/>
+      <c r="M109" s="80"/>
+      <c r="N109" s="130"/>
       <c r="O109" s="4"/>
     </row>
     <row r="110" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B110" s="49"/>
-      <c r="C110" s="33"/>
-      <c r="D110" s="33"/>
-      <c r="E110" s="33"/>
-      <c r="F110" s="47"/>
-      <c r="G110" s="49"/>
-      <c r="H110" s="33"/>
-      <c r="I110" s="47"/>
-      <c r="J110" s="22"/>
-      <c r="K110" s="23"/>
-      <c r="L110" s="23"/>
-      <c r="M110" s="22"/>
-      <c r="N110" s="31"/>
+      <c r="B110" s="22"/>
+      <c r="C110" s="23"/>
+      <c r="D110" s="23"/>
+      <c r="E110" s="23"/>
+      <c r="F110" s="24"/>
+      <c r="G110" s="22"/>
+      <c r="H110" s="23"/>
+      <c r="I110" s="24"/>
+      <c r="J110" s="80"/>
+      <c r="K110" s="81"/>
+      <c r="L110" s="81"/>
+      <c r="M110" s="80"/>
+      <c r="N110" s="130"/>
       <c r="O110" s="4"/>
     </row>
     <row r="111" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B111" s="49"/>
-      <c r="C111" s="33"/>
-      <c r="D111" s="33"/>
-      <c r="E111" s="33"/>
-      <c r="F111" s="47"/>
-      <c r="G111" s="49"/>
-      <c r="H111" s="33"/>
-      <c r="I111" s="47"/>
-      <c r="J111" s="22"/>
-      <c r="K111" s="23"/>
-      <c r="L111" s="23"/>
-      <c r="M111" s="22"/>
-      <c r="N111" s="31"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="23"/>
+      <c r="D111" s="23"/>
+      <c r="E111" s="23"/>
+      <c r="F111" s="24"/>
+      <c r="G111" s="22"/>
+      <c r="H111" s="23"/>
+      <c r="I111" s="24"/>
+      <c r="J111" s="80"/>
+      <c r="K111" s="81"/>
+      <c r="L111" s="81"/>
+      <c r="M111" s="80"/>
+      <c r="N111" s="130"/>
       <c r="O111" s="4"/>
     </row>
     <row r="112" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5537,120 +5539,120 @@
       <c r="O112" s="5"/>
     </row>
     <row r="113" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="43" t="s">
+      <c r="B113" s="67" t="s">
         <v>160</v>
       </c>
-      <c r="C113" s="44"/>
-      <c r="D113" s="44"/>
-      <c r="E113" s="44"/>
-      <c r="F113" s="44"/>
-      <c r="G113" s="44"/>
-      <c r="H113" s="44"/>
-      <c r="I113" s="44"/>
-      <c r="J113" s="44"/>
-      <c r="K113" s="44"/>
-      <c r="L113" s="44"/>
-      <c r="M113" s="44"/>
-      <c r="N113" s="44"/>
-      <c r="O113" s="45"/>
+      <c r="C113" s="68"/>
+      <c r="D113" s="68"/>
+      <c r="E113" s="68"/>
+      <c r="F113" s="68"/>
+      <c r="G113" s="68"/>
+      <c r="H113" s="68"/>
+      <c r="I113" s="68"/>
+      <c r="J113" s="68"/>
+      <c r="K113" s="68"/>
+      <c r="L113" s="68"/>
+      <c r="M113" s="68"/>
+      <c r="N113" s="68"/>
+      <c r="O113" s="69"/>
     </row>
     <row r="114" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B114" s="129" t="s">
+      <c r="B114" s="60" t="s">
         <v>120</v>
       </c>
-      <c r="C114" s="33"/>
-      <c r="D114" s="33"/>
-      <c r="E114" s="33"/>
-      <c r="F114" s="33"/>
-      <c r="G114" s="33"/>
-      <c r="H114" s="33"/>
-      <c r="I114" s="33"/>
-      <c r="J114" s="33"/>
-      <c r="K114" s="33"/>
-      <c r="L114" s="33"/>
-      <c r="M114" s="33"/>
-      <c r="N114" s="33"/>
-      <c r="O114" s="47"/>
+      <c r="C114" s="23"/>
+      <c r="D114" s="23"/>
+      <c r="E114" s="23"/>
+      <c r="F114" s="23"/>
+      <c r="G114" s="23"/>
+      <c r="H114" s="23"/>
+      <c r="I114" s="23"/>
+      <c r="J114" s="23"/>
+      <c r="K114" s="23"/>
+      <c r="L114" s="23"/>
+      <c r="M114" s="23"/>
+      <c r="N114" s="23"/>
+      <c r="O114" s="24"/>
     </row>
     <row r="115" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B115" s="49"/>
-      <c r="C115" s="102"/>
-      <c r="D115" s="102"/>
-      <c r="E115" s="102"/>
-      <c r="F115" s="102"/>
-      <c r="G115" s="102"/>
-      <c r="H115" s="102"/>
-      <c r="I115" s="102"/>
-      <c r="J115" s="102"/>
-      <c r="K115" s="102"/>
-      <c r="L115" s="102"/>
-      <c r="M115" s="102"/>
-      <c r="N115" s="102"/>
-      <c r="O115" s="103"/>
+      <c r="B115" s="22"/>
+      <c r="C115" s="25"/>
+      <c r="D115" s="25"/>
+      <c r="E115" s="25"/>
+      <c r="F115" s="25"/>
+      <c r="G115" s="25"/>
+      <c r="H115" s="25"/>
+      <c r="I115" s="25"/>
+      <c r="J115" s="25"/>
+      <c r="K115" s="25"/>
+      <c r="L115" s="25"/>
+      <c r="M115" s="25"/>
+      <c r="N115" s="25"/>
+      <c r="O115" s="26"/>
     </row>
     <row r="116" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B116" s="106"/>
-      <c r="C116" s="107"/>
-      <c r="D116" s="107"/>
-      <c r="E116" s="107"/>
-      <c r="F116" s="107"/>
-      <c r="G116" s="107"/>
-      <c r="H116" s="107"/>
-      <c r="I116" s="107"/>
-      <c r="J116" s="107"/>
-      <c r="K116" s="107"/>
-      <c r="L116" s="107"/>
-      <c r="M116" s="107"/>
-      <c r="N116" s="107"/>
-      <c r="O116" s="108"/>
+      <c r="B116" s="62"/>
+      <c r="C116" s="76"/>
+      <c r="D116" s="76"/>
+      <c r="E116" s="76"/>
+      <c r="F116" s="76"/>
+      <c r="G116" s="76"/>
+      <c r="H116" s="76"/>
+      <c r="I116" s="76"/>
+      <c r="J116" s="76"/>
+      <c r="K116" s="76"/>
+      <c r="L116" s="76"/>
+      <c r="M116" s="76"/>
+      <c r="N116" s="76"/>
+      <c r="O116" s="63"/>
     </row>
     <row r="117" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B117" s="106"/>
-      <c r="C117" s="107"/>
-      <c r="D117" s="107"/>
-      <c r="E117" s="107"/>
-      <c r="F117" s="107"/>
-      <c r="G117" s="107"/>
-      <c r="H117" s="107"/>
-      <c r="I117" s="107"/>
-      <c r="J117" s="107"/>
-      <c r="K117" s="107"/>
-      <c r="L117" s="107"/>
-      <c r="M117" s="107"/>
-      <c r="N117" s="107"/>
-      <c r="O117" s="108"/>
+      <c r="B117" s="62"/>
+      <c r="C117" s="76"/>
+      <c r="D117" s="76"/>
+      <c r="E117" s="76"/>
+      <c r="F117" s="76"/>
+      <c r="G117" s="76"/>
+      <c r="H117" s="76"/>
+      <c r="I117" s="76"/>
+      <c r="J117" s="76"/>
+      <c r="K117" s="76"/>
+      <c r="L117" s="76"/>
+      <c r="M117" s="76"/>
+      <c r="N117" s="76"/>
+      <c r="O117" s="63"/>
     </row>
     <row r="118" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B118" s="106"/>
-      <c r="C118" s="107"/>
-      <c r="D118" s="107"/>
-      <c r="E118" s="107"/>
-      <c r="F118" s="107"/>
-      <c r="G118" s="107"/>
-      <c r="H118" s="107"/>
-      <c r="I118" s="107"/>
-      <c r="J118" s="107"/>
-      <c r="K118" s="107"/>
-      <c r="L118" s="107"/>
-      <c r="M118" s="107"/>
-      <c r="N118" s="107"/>
-      <c r="O118" s="108"/>
+      <c r="B118" s="62"/>
+      <c r="C118" s="76"/>
+      <c r="D118" s="76"/>
+      <c r="E118" s="76"/>
+      <c r="F118" s="76"/>
+      <c r="G118" s="76"/>
+      <c r="H118" s="76"/>
+      <c r="I118" s="76"/>
+      <c r="J118" s="76"/>
+      <c r="K118" s="76"/>
+      <c r="L118" s="76"/>
+      <c r="M118" s="76"/>
+      <c r="N118" s="76"/>
+      <c r="O118" s="63"/>
     </row>
     <row r="119" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B119" s="104"/>
-      <c r="C119" s="105"/>
-      <c r="D119" s="105"/>
-      <c r="E119" s="105"/>
-      <c r="F119" s="105"/>
-      <c r="G119" s="105"/>
-      <c r="H119" s="105"/>
-      <c r="I119" s="105"/>
-      <c r="J119" s="105"/>
-      <c r="K119" s="105"/>
-      <c r="L119" s="105"/>
-      <c r="M119" s="105"/>
-      <c r="N119" s="105"/>
-      <c r="O119" s="68"/>
+      <c r="B119" s="27"/>
+      <c r="C119" s="28"/>
+      <c r="D119" s="28"/>
+      <c r="E119" s="28"/>
+      <c r="F119" s="28"/>
+      <c r="G119" s="28"/>
+      <c r="H119" s="28"/>
+      <c r="I119" s="28"/>
+      <c r="J119" s="28"/>
+      <c r="K119" s="28"/>
+      <c r="L119" s="28"/>
+      <c r="M119" s="28"/>
+      <c r="N119" s="28"/>
+      <c r="O119" s="29"/>
     </row>
     <row r="120" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B120" s="8"/>
@@ -5669,146 +5671,399 @@
       <c r="O120" s="10"/>
     </row>
     <row r="121" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B121" s="39" t="s">
+      <c r="B121" s="126" t="s">
         <v>151</v>
       </c>
-      <c r="C121" s="40"/>
-      <c r="D121" s="40"/>
-      <c r="E121" s="40"/>
-      <c r="F121" s="40"/>
-      <c r="G121" s="40"/>
-      <c r="H121" s="41"/>
-      <c r="I121" s="39" t="s">
+      <c r="C121" s="127"/>
+      <c r="D121" s="127"/>
+      <c r="E121" s="127"/>
+      <c r="F121" s="127"/>
+      <c r="G121" s="127"/>
+      <c r="H121" s="128"/>
+      <c r="I121" s="126" t="s">
         <v>152</v>
       </c>
-      <c r="J121" s="40"/>
-      <c r="K121" s="40"/>
-      <c r="L121" s="40"/>
-      <c r="M121" s="40"/>
-      <c r="N121" s="40"/>
-      <c r="O121" s="42"/>
+      <c r="J121" s="127"/>
+      <c r="K121" s="127"/>
+      <c r="L121" s="127"/>
+      <c r="M121" s="127"/>
+      <c r="N121" s="127"/>
+      <c r="O121" s="129"/>
       <c r="P121" s="19"/>
     </row>
     <row r="122" spans="2:16" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="37" t="s">
+      <c r="B122" s="124" t="s">
         <v>121</v>
       </c>
-      <c r="C122" s="38"/>
-      <c r="D122" s="38"/>
-      <c r="E122" s="38"/>
-      <c r="F122" s="38"/>
-      <c r="G122" s="38"/>
-      <c r="H122" s="38"/>
-      <c r="I122" s="37" t="s">
+      <c r="C122" s="125"/>
+      <c r="D122" s="125"/>
+      <c r="E122" s="125"/>
+      <c r="F122" s="125"/>
+      <c r="G122" s="125"/>
+      <c r="H122" s="125"/>
+      <c r="I122" s="124" t="s">
         <v>121</v>
       </c>
-      <c r="J122" s="38"/>
-      <c r="K122" s="38"/>
-      <c r="L122" s="38"/>
-      <c r="M122" s="38"/>
-      <c r="N122" s="38"/>
-      <c r="O122" s="38"/>
+      <c r="J122" s="125"/>
+      <c r="K122" s="125"/>
+      <c r="L122" s="125"/>
+      <c r="M122" s="125"/>
+      <c r="N122" s="125"/>
+      <c r="O122" s="125"/>
       <c r="P122" s="19"/>
     </row>
     <row r="123" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B123" s="86" t="s">
+      <c r="B123" s="75" t="s">
         <v>149</v>
       </c>
-      <c r="C123" s="33"/>
-      <c r="D123" s="33"/>
-      <c r="E123" s="47"/>
-      <c r="F123" s="86" t="s">
+      <c r="C123" s="23"/>
+      <c r="D123" s="23"/>
+      <c r="E123" s="24"/>
+      <c r="F123" s="75" t="s">
         <v>149</v>
       </c>
-      <c r="G123" s="33"/>
-      <c r="H123" s="33"/>
-      <c r="I123" s="33"/>
-      <c r="J123" s="47"/>
-      <c r="K123" s="86" t="s">
+      <c r="G123" s="23"/>
+      <c r="H123" s="23"/>
+      <c r="I123" s="23"/>
+      <c r="J123" s="24"/>
+      <c r="K123" s="75" t="s">
         <v>150</v>
       </c>
-      <c r="L123" s="33"/>
-      <c r="M123" s="33"/>
-      <c r="N123" s="33"/>
-      <c r="O123" s="47"/>
+      <c r="L123" s="23"/>
+      <c r="M123" s="23"/>
+      <c r="N123" s="23"/>
+      <c r="O123" s="24"/>
     </row>
     <row r="124" spans="2:16" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="83" t="s">
+      <c r="B124" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="C124" s="84"/>
-      <c r="D124" s="84"/>
-      <c r="E124" s="85"/>
-      <c r="F124" s="83" t="s">
+      <c r="C124" s="83"/>
+      <c r="D124" s="83"/>
+      <c r="E124" s="84"/>
+      <c r="F124" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="G124" s="84"/>
-      <c r="H124" s="84"/>
-      <c r="I124" s="84"/>
-      <c r="J124" s="85"/>
-      <c r="K124" s="83" t="s">
+      <c r="G124" s="83"/>
+      <c r="H124" s="83"/>
+      <c r="I124" s="83"/>
+      <c r="J124" s="84"/>
+      <c r="K124" s="82" t="s">
         <v>121</v>
       </c>
-      <c r="L124" s="84"/>
-      <c r="M124" s="84"/>
-      <c r="N124" s="84"/>
-      <c r="O124" s="85"/>
+      <c r="L124" s="83"/>
+      <c r="M124" s="83"/>
+      <c r="N124" s="83"/>
+      <c r="O124" s="84"/>
     </row>
     <row r="125" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B125" s="73" t="s">
+      <c r="B125" s="115" t="s">
         <v>103</v>
       </c>
-      <c r="C125" s="44"/>
-      <c r="D125" s="44"/>
-      <c r="E125" s="44"/>
-      <c r="F125" s="44"/>
-      <c r="G125" s="44"/>
-      <c r="H125" s="44"/>
-      <c r="I125" s="44"/>
-      <c r="J125" s="44"/>
-      <c r="K125" s="44"/>
-      <c r="L125" s="44"/>
-      <c r="M125" s="44"/>
-      <c r="N125" s="44"/>
-      <c r="O125" s="45"/>
+      <c r="C125" s="68"/>
+      <c r="D125" s="68"/>
+      <c r="E125" s="68"/>
+      <c r="F125" s="68"/>
+      <c r="G125" s="68"/>
+      <c r="H125" s="68"/>
+      <c r="I125" s="68"/>
+      <c r="J125" s="68"/>
+      <c r="K125" s="68"/>
+      <c r="L125" s="68"/>
+      <c r="M125" s="68"/>
+      <c r="N125" s="68"/>
+      <c r="O125" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="336">
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="I13:O13"/>
-    <mergeCell ref="I14:O14"/>
-    <mergeCell ref="I15:O15"/>
-    <mergeCell ref="I16:O16"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="E77:G77"/>
+    <mergeCell ref="L51:O52"/>
+    <mergeCell ref="H75:J75"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="N33:O33"/>
+    <mergeCell ref="N77:O77"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="G45:H45"/>
+    <mergeCell ref="H79:J79"/>
+    <mergeCell ref="E50:G50"/>
+    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="G40:H40"/>
+    <mergeCell ref="E73:G73"/>
+    <mergeCell ref="H62:K63"/>
+    <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="N67:O67"/>
+    <mergeCell ref="N79:O79"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="B65:O65"/>
+    <mergeCell ref="H70:J70"/>
+    <mergeCell ref="K36:L36"/>
+    <mergeCell ref="N71:O71"/>
+    <mergeCell ref="B79:C82"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="J110:L110"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="N98:O98"/>
+    <mergeCell ref="N85:O85"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="B54:O54"/>
+    <mergeCell ref="H76:J76"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="N83:O83"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="H61:K61"/>
+    <mergeCell ref="L61:O61"/>
+    <mergeCell ref="B62:D63"/>
+    <mergeCell ref="E62:G63"/>
+    <mergeCell ref="M111:N111"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B29:O29"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="B38:O38"/>
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="K30:O30"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="B122:H122"/>
+    <mergeCell ref="B121:H121"/>
+    <mergeCell ref="I121:O121"/>
+    <mergeCell ref="I122:O122"/>
+    <mergeCell ref="B88:O88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:I89"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="M89:O89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="D90:I90"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="M90:O90"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="H98:M98"/>
+    <mergeCell ref="H96:M96"/>
+    <mergeCell ref="M106:N106"/>
+    <mergeCell ref="J111:L111"/>
+    <mergeCell ref="M107:N107"/>
+    <mergeCell ref="M108:N108"/>
+    <mergeCell ref="M109:N109"/>
+    <mergeCell ref="M110:N110"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="B125:O125"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="N82:O82"/>
+    <mergeCell ref="N84:O84"/>
+    <mergeCell ref="N78:O78"/>
+    <mergeCell ref="H84:J84"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="I17:O17"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="K124:O124"/>
+    <mergeCell ref="H99:M99"/>
+    <mergeCell ref="F123:J123"/>
+    <mergeCell ref="B113:O113"/>
+    <mergeCell ref="G111:I111"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="N72:O72"/>
+    <mergeCell ref="E79:G79"/>
+    <mergeCell ref="H59:K60"/>
+    <mergeCell ref="L59:O60"/>
+    <mergeCell ref="N70:O70"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="I11:O11"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B56:D57"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="H85:J85"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="L50:O50"/>
+    <mergeCell ref="H69:J69"/>
+    <mergeCell ref="N96:O96"/>
+    <mergeCell ref="B19:O19"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B21:H24"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B51:D52"/>
+    <mergeCell ref="B28:O28"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="N35:O35"/>
     <mergeCell ref="I32:J32"/>
-    <mergeCell ref="B50:D50"/>
     <mergeCell ref="I31:J31"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="N67:O67"/>
-    <mergeCell ref="N79:O79"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="I20:O20"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="B25:D25"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="B65:O65"/>
-    <mergeCell ref="H70:J70"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="K36:L36"/>
-    <mergeCell ref="N71:O71"/>
-    <mergeCell ref="B79:C82"/>
-    <mergeCell ref="B12:H17"/>
-    <mergeCell ref="I12:O12"/>
-    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="H102:M102"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="B83:C86"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="L62:O63"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="H58:K58"/>
+    <mergeCell ref="L58:O58"/>
+    <mergeCell ref="B59:D60"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B48:O48"/>
+    <mergeCell ref="I21:O24"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="F124:J124"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="E76:G76"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="G110:I110"/>
+    <mergeCell ref="H81:J81"/>
+    <mergeCell ref="E85:G85"/>
+    <mergeCell ref="G109:I109"/>
+    <mergeCell ref="H66:J66"/>
+    <mergeCell ref="H97:M97"/>
+    <mergeCell ref="H86:J86"/>
+    <mergeCell ref="G106:I106"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="E78:G78"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="B49:O49"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="L56:O57"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="K123:O123"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B115:O119"/>
+    <mergeCell ref="B104:O104"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="N73:O73"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="N97:O97"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="E84:G84"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="N102:O102"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="N69:O69"/>
+    <mergeCell ref="N76:O76"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="D91:I91"/>
+    <mergeCell ref="J91:L91"/>
+    <mergeCell ref="M91:O91"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="G108:I108"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="L55:O55"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="H56:K57"/>
+    <mergeCell ref="E75:G75"/>
+    <mergeCell ref="G107:I107"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="J92:L92"/>
+    <mergeCell ref="M92:O92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="M93:O93"/>
+    <mergeCell ref="B105:O105"/>
+    <mergeCell ref="B67:C70"/>
+    <mergeCell ref="B71:C74"/>
+    <mergeCell ref="H101:M101"/>
+    <mergeCell ref="E56:G57"/>
+    <mergeCell ref="N101:O101"/>
+    <mergeCell ref="E82:G82"/>
     <mergeCell ref="L5:O5"/>
     <mergeCell ref="B114:O114"/>
     <mergeCell ref="N99:O99"/>
@@ -5833,283 +6088,30 @@
     <mergeCell ref="N100:O100"/>
     <mergeCell ref="F100:G100"/>
     <mergeCell ref="B97:E97"/>
+    <mergeCell ref="G31:H31"/>
     <mergeCell ref="H67:J67"/>
     <mergeCell ref="H51:K52"/>
     <mergeCell ref="E66:G66"/>
     <mergeCell ref="E67:G67"/>
     <mergeCell ref="N43:O43"/>
-    <mergeCell ref="B55:D55"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="G108:I108"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="H71:J71"/>
-    <mergeCell ref="L55:O55"/>
-    <mergeCell ref="H68:J68"/>
-    <mergeCell ref="H56:K57"/>
-    <mergeCell ref="E75:G75"/>
-    <mergeCell ref="G107:I107"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="J92:L92"/>
-    <mergeCell ref="M92:O92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="J93:L93"/>
-    <mergeCell ref="M93:O93"/>
-    <mergeCell ref="B105:O105"/>
-    <mergeCell ref="K123:O123"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B115:O119"/>
-    <mergeCell ref="B104:O104"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="N73:O73"/>
-    <mergeCell ref="E71:G71"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="N97:O97"/>
-    <mergeCell ref="E72:G72"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="E84:G84"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="N102:O102"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="N69:O69"/>
-    <mergeCell ref="N76:O76"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="D91:I91"/>
-    <mergeCell ref="J91:L91"/>
-    <mergeCell ref="M91:O91"/>
-    <mergeCell ref="F124:J124"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="E76:G76"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="G110:I110"/>
-    <mergeCell ref="H81:J81"/>
-    <mergeCell ref="E85:G85"/>
-    <mergeCell ref="G109:I109"/>
-    <mergeCell ref="H66:J66"/>
-    <mergeCell ref="H97:M97"/>
-    <mergeCell ref="H86:J86"/>
-    <mergeCell ref="G106:I106"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="E78:G78"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="B49:O49"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="H55:K55"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="L56:O57"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="B67:C70"/>
-    <mergeCell ref="B71:C74"/>
-    <mergeCell ref="H101:M101"/>
-    <mergeCell ref="E56:G57"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="N72:O72"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="E79:G79"/>
-    <mergeCell ref="H59:K60"/>
-    <mergeCell ref="L59:O60"/>
-    <mergeCell ref="N70:O70"/>
-    <mergeCell ref="N98:O98"/>
-    <mergeCell ref="N85:O85"/>
-    <mergeCell ref="N101:O101"/>
-    <mergeCell ref="H78:J78"/>
-    <mergeCell ref="E73:G73"/>
-    <mergeCell ref="B54:O54"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="H76:J76"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="N83:O83"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="H102:M102"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="B83:C86"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="L62:O63"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="H58:K58"/>
-    <mergeCell ref="L58:O58"/>
-    <mergeCell ref="B59:D60"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="E81:G81"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B48:O48"/>
-    <mergeCell ref="I21:O24"/>
-    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="I13:O13"/>
+    <mergeCell ref="I14:O14"/>
+    <mergeCell ref="I15:O15"/>
+    <mergeCell ref="I16:O16"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="F7:O7"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B12:H17"/>
+    <mergeCell ref="I12:O12"/>
     <mergeCell ref="F6:H6"/>
-    <mergeCell ref="H61:K61"/>
-    <mergeCell ref="L61:O61"/>
-    <mergeCell ref="B62:D63"/>
-    <mergeCell ref="E62:G63"/>
-    <mergeCell ref="H62:K63"/>
     <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B21:H24"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B51:D52"/>
-    <mergeCell ref="B28:O28"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="K124:O124"/>
-    <mergeCell ref="H99:M99"/>
-    <mergeCell ref="F123:J123"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="I11:O11"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B56:D57"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="H85:J85"/>
-    <mergeCell ref="B113:O113"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="G111:I111"/>
-    <mergeCell ref="L50:O50"/>
-    <mergeCell ref="H69:J69"/>
-    <mergeCell ref="N96:O96"/>
-    <mergeCell ref="B19:O19"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B125:O125"/>
-    <mergeCell ref="B109:F109"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="E68:G68"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="N82:O82"/>
-    <mergeCell ref="N84:O84"/>
-    <mergeCell ref="N78:O78"/>
-    <mergeCell ref="H84:J84"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="I17:O17"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="D40:E40"/>
-    <mergeCell ref="G40:H40"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="B122:H122"/>
-    <mergeCell ref="B121:H121"/>
-    <mergeCell ref="I121:O121"/>
-    <mergeCell ref="I122:O122"/>
-    <mergeCell ref="B88:O88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:I89"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="M89:O89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="D90:I90"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="M90:O90"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="H98:M98"/>
-    <mergeCell ref="H96:M96"/>
-    <mergeCell ref="M106:N106"/>
-    <mergeCell ref="J111:L111"/>
-    <mergeCell ref="M107:N107"/>
-    <mergeCell ref="M108:N108"/>
-    <mergeCell ref="M109:N109"/>
-    <mergeCell ref="M110:N110"/>
-    <mergeCell ref="M111:N111"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B29:O29"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="B38:O38"/>
-    <mergeCell ref="B39:J39"/>
-    <mergeCell ref="K39:O39"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="K30:O30"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="J110:L110"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="E77:G77"/>
-    <mergeCell ref="L51:O52"/>
-    <mergeCell ref="H75:J75"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="N33:O33"/>
-    <mergeCell ref="N77:O77"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="G45:H45"/>
-    <mergeCell ref="H79:J79"/>
-    <mergeCell ref="E50:G50"/>
   </mergeCells>
   <conditionalFormatting sqref="D67:D87">
     <cfRule type="expression" dxfId="3" priority="1">
@@ -6577,16 +6579,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="154" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="152"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="156"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -6779,17 +6781,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="154" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="151"/>
-      <c r="C1" s="151"/>
-      <c r="D1" s="151"/>
-      <c r="E1" s="151"/>
-      <c r="F1" s="151"/>
-      <c r="G1" s="151"/>
-      <c r="H1" s="151"/>
-      <c r="I1" s="152"/>
+      <c r="B1" s="155"/>
+      <c r="C1" s="155"/>
+      <c r="D1" s="155"/>
+      <c r="E1" s="155"/>
+      <c r="F1" s="155"/>
+      <c r="G1" s="155"/>
+      <c r="H1" s="155"/>
+      <c r="I1" s="156"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">

--- a/formats/formato_SOP.xlsx
+++ b/formats/formato_SOP.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{B4C81DFA-2F42-43D1-A45D-C4F01C3237E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87C2E396-1B2D-4515-935F-A4BA13CCC027}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SOP" sheetId="2" r:id="rId1"/>
@@ -2442,39 +2442,401 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2510,18 +2872,6 @@
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2538,9 +2888,6 @@
       <alignment horizontal="left"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -2587,353 +2934,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
@@ -3496,60 +3496,60 @@
       <c r="O1" s="2"/>
     </row>
     <row r="2" spans="2:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="116" t="e" vm="1">
+      <c r="B2" s="90" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="C2" s="116"/>
-      <c r="D2" s="117" t="s">
+      <c r="C2" s="90"/>
+      <c r="D2" s="91" t="s">
         <v>164</v>
       </c>
-      <c r="E2" s="118"/>
-      <c r="F2" s="118"/>
-      <c r="G2" s="118"/>
-      <c r="H2" s="118"/>
-      <c r="I2" s="118"/>
-      <c r="J2" s="118"/>
-      <c r="K2" s="118"/>
-      <c r="L2" s="118"/>
-      <c r="M2" s="118"/>
-      <c r="N2" s="119" t="s">
+      <c r="E2" s="92"/>
+      <c r="F2" s="92"/>
+      <c r="G2" s="92"/>
+      <c r="H2" s="92"/>
+      <c r="I2" s="92"/>
+      <c r="J2" s="92"/>
+      <c r="K2" s="92"/>
+      <c r="L2" s="92"/>
+      <c r="M2" s="92"/>
+      <c r="N2" s="93" t="s">
         <v>102</v>
       </c>
-      <c r="O2" s="120"/>
+      <c r="O2" s="94"/>
     </row>
     <row r="3" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B3" s="121"/>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121"/>
-      <c r="K3" s="121"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="121"/>
-      <c r="N3" s="121"/>
-      <c r="O3" s="121"/>
+      <c r="B3" s="95"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="95"/>
+      <c r="E3" s="95"/>
+      <c r="F3" s="95"/>
+      <c r="G3" s="95"/>
+      <c r="H3" s="95"/>
+      <c r="I3" s="95"/>
+      <c r="J3" s="95"/>
+      <c r="K3" s="95"/>
+      <c r="L3" s="95"/>
+      <c r="M3" s="95"/>
+      <c r="N3" s="95"/>
+      <c r="O3" s="95"/>
     </row>
     <row r="4" spans="2:15" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B4" s="67" t="s">
+      <c r="B4" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-      <c r="O4" s="69"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
+      <c r="J4" s="33"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="33"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="34"/>
     </row>
     <row r="5" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="11" t="s">
@@ -3558,114 +3558,114 @@
       <c r="C5" s="12"/>
       <c r="D5" s="12"/>
       <c r="E5" s="12"/>
-      <c r="F5" s="87" t="s">
+      <c r="F5" s="117" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="88"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="90" t="s">
+      <c r="G5" s="118"/>
+      <c r="H5" s="119"/>
+      <c r="I5" s="120" t="s">
         <v>137</v>
       </c>
-      <c r="J5" s="91"/>
-      <c r="K5" s="92"/>
-      <c r="L5" s="40" t="s">
+      <c r="J5" s="121"/>
+      <c r="K5" s="122"/>
+      <c r="L5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="M5" s="23"/>
-      <c r="N5" s="23"/>
-      <c r="O5" s="24"/>
+      <c r="M5" s="21"/>
+      <c r="N5" s="21"/>
+      <c r="O5" s="22"/>
     </row>
     <row r="6" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B6" s="31"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="59"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="45"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="47" t="s">
+      <c r="B6" s="129"/>
+      <c r="C6" s="130"/>
+      <c r="D6" s="130"/>
+      <c r="E6" s="131"/>
+      <c r="F6" s="139"/>
+      <c r="G6" s="140"/>
+      <c r="H6" s="153"/>
+      <c r="I6" s="139"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="141"/>
+      <c r="L6" s="103" t="s">
         <v>189</v>
       </c>
-      <c r="M6" s="23"/>
-      <c r="N6" s="23"/>
-      <c r="O6" s="24"/>
+      <c r="M6" s="21"/>
+      <c r="N6" s="21"/>
+      <c r="O6" s="22"/>
     </row>
     <row r="7" spans="2:15" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="41" t="s">
+      <c r="C7" s="21"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="42"/>
-      <c r="J7" s="42"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="43"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="138"/>
     </row>
     <row r="8" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B8" s="47"/>
-      <c r="C8" s="23"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="24"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="39"/>
+      <c r="B8" s="103"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="135"/>
+      <c r="G8" s="136"/>
+      <c r="H8" s="135"/>
+      <c r="I8" s="136"/>
+      <c r="J8" s="135"/>
+      <c r="K8" s="136"/>
+      <c r="L8" s="135"/>
+      <c r="M8" s="136"/>
+      <c r="N8" s="135"/>
+      <c r="O8" s="137"/>
     </row>
     <row r="9" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B9" s="40" t="s">
+      <c r="B9" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="40" t="s">
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="K9" s="23"/>
-      <c r="L9" s="24"/>
-      <c r="M9" s="40" t="s">
+      <c r="K9" s="21"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="N9" s="23"/>
-      <c r="O9" s="24"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="22"/>
     </row>
     <row r="10" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B10" s="47"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
-      <c r="I10" s="24"/>
-      <c r="J10" s="47"/>
-      <c r="K10" s="23"/>
-      <c r="L10" s="24"/>
-      <c r="M10" s="47"/>
-      <c r="N10" s="23"/>
-      <c r="O10" s="24"/>
+      <c r="B10" s="103"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="103"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="103"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="22"/>
     </row>
     <row r="11" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B11" s="104" t="s">
@@ -3688,119 +3688,119 @@
       <c r="O11" s="108"/>
     </row>
     <row r="12" spans="2:15" ht="16.5" x14ac:dyDescent="0.25">
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="142" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="49"/>
-      <c r="D12" s="49"/>
-      <c r="E12" s="49"/>
-      <c r="F12" s="49"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="50"/>
-      <c r="I12" s="57" t="s">
+      <c r="C12" s="143"/>
+      <c r="D12" s="143"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="143"/>
+      <c r="G12" s="143"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="151" t="s">
         <v>178</v>
       </c>
-      <c r="J12" s="49"/>
-      <c r="K12" s="49"/>
-      <c r="L12" s="49"/>
-      <c r="M12" s="49"/>
-      <c r="N12" s="49"/>
-      <c r="O12" s="58"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="143"/>
+      <c r="L12" s="143"/>
+      <c r="M12" s="143"/>
+      <c r="N12" s="143"/>
+      <c r="O12" s="152"/>
     </row>
     <row r="13" spans="2:15" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="51"/>
-      <c r="C13" s="52"/>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="34" t="str">
+      <c r="B13" s="145"/>
+      <c r="C13" s="146"/>
+      <c r="D13" s="146"/>
+      <c r="E13" s="146"/>
+      <c r="F13" s="146"/>
+      <c r="G13" s="146"/>
+      <c r="H13" s="147"/>
+      <c r="I13" s="132" t="str">
         <f>IFERROR(VLOOKUP(F8,Listas!$C$12:$D$17, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="J13" s="35"/>
-      <c r="K13" s="35"/>
-      <c r="L13" s="35"/>
-      <c r="M13" s="35"/>
-      <c r="N13" s="35"/>
-      <c r="O13" s="36"/>
+      <c r="J13" s="133"/>
+      <c r="K13" s="133"/>
+      <c r="L13" s="133"/>
+      <c r="M13" s="133"/>
+      <c r="N13" s="133"/>
+      <c r="O13" s="134"/>
     </row>
     <row r="14" spans="2:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="51"/>
-      <c r="C14" s="52"/>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="34" t="str">
+      <c r="B14" s="145"/>
+      <c r="C14" s="146"/>
+      <c r="D14" s="146"/>
+      <c r="E14" s="146"/>
+      <c r="F14" s="146"/>
+      <c r="G14" s="146"/>
+      <c r="H14" s="147"/>
+      <c r="I14" s="132" t="str">
         <f>IFERROR(VLOOKUP(H8,Listas!$C$12:$D$17, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="J14" s="35"/>
-      <c r="K14" s="35"/>
-      <c r="L14" s="35"/>
-      <c r="M14" s="35"/>
-      <c r="N14" s="35"/>
-      <c r="O14" s="36"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
+      <c r="M14" s="133"/>
+      <c r="N14" s="133"/>
+      <c r="O14" s="134"/>
     </row>
     <row r="15" spans="2:15" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="51"/>
-      <c r="C15" s="52"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="34" t="str">
+      <c r="B15" s="145"/>
+      <c r="C15" s="146"/>
+      <c r="D15" s="146"/>
+      <c r="E15" s="146"/>
+      <c r="F15" s="146"/>
+      <c r="G15" s="146"/>
+      <c r="H15" s="147"/>
+      <c r="I15" s="132" t="str">
         <f>IFERROR(VLOOKUP(J8,Listas!$C$12:$D$17, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="J15" s="35"/>
-      <c r="K15" s="35"/>
-      <c r="L15" s="35"/>
-      <c r="M15" s="35"/>
-      <c r="N15" s="35"/>
-      <c r="O15" s="36"/>
+      <c r="J15" s="133"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="133"/>
+      <c r="M15" s="133"/>
+      <c r="N15" s="133"/>
+      <c r="O15" s="134"/>
     </row>
     <row r="16" spans="2:15" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="51"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="53"/>
-      <c r="I16" s="34" t="str">
+      <c r="B16" s="145"/>
+      <c r="C16" s="146"/>
+      <c r="D16" s="146"/>
+      <c r="E16" s="146"/>
+      <c r="F16" s="146"/>
+      <c r="G16" s="146"/>
+      <c r="H16" s="147"/>
+      <c r="I16" s="132" t="str">
         <f>IFERROR(VLOOKUP(L8,Listas!$C$12:$D$17, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="J16" s="35"/>
-      <c r="K16" s="35"/>
-      <c r="L16" s="35"/>
-      <c r="M16" s="35"/>
-      <c r="N16" s="35"/>
-      <c r="O16" s="36"/>
+      <c r="J16" s="133"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="133"/>
+      <c r="M16" s="133"/>
+      <c r="N16" s="133"/>
+      <c r="O16" s="134"/>
     </row>
     <row r="17" spans="2:15" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="54"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
-      <c r="F17" s="55"/>
-      <c r="G17" s="55"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="112" t="str">
+      <c r="B17" s="148"/>
+      <c r="C17" s="149"/>
+      <c r="D17" s="149"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="149"/>
+      <c r="G17" s="149"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="96" t="str">
         <f>IFERROR(VLOOKUP(N8,Listas!$C$12:$D$17, 2, FALSE), "")</f>
         <v/>
       </c>
-      <c r="J17" s="113"/>
-      <c r="K17" s="113"/>
-      <c r="L17" s="113"/>
-      <c r="M17" s="113"/>
-      <c r="N17" s="113"/>
-      <c r="O17" s="114"/>
+      <c r="J17" s="97"/>
+      <c r="K17" s="97"/>
+      <c r="L17" s="97"/>
+      <c r="M17" s="97"/>
+      <c r="N17" s="97"/>
+      <c r="O17" s="98"/>
     </row>
     <row r="18" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="5"/>
@@ -3819,150 +3819,150 @@
       <c r="O18" s="5"/>
     </row>
     <row r="19" spans="2:15" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B19" s="67" t="s">
+      <c r="B19" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="68"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="68"/>
-      <c r="O19" s="69"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="33"/>
+      <c r="J19" s="33"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="33"/>
+      <c r="M19" s="33"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="34"/>
     </row>
     <row r="20" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B20" s="40" t="s">
+      <c r="B20" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="23"/>
-      <c r="D20" s="23"/>
-      <c r="E20" s="23"/>
-      <c r="F20" s="23"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="24"/>
-      <c r="I20" s="40" t="s">
+      <c r="C20" s="21"/>
+      <c r="D20" s="21"/>
+      <c r="E20" s="21"/>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="J20" s="23"/>
-      <c r="K20" s="23"/>
-      <c r="L20" s="23"/>
-      <c r="M20" s="23"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="24"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="21"/>
+      <c r="L20" s="21"/>
+      <c r="M20" s="21"/>
+      <c r="N20" s="21"/>
+      <c r="O20" s="22"/>
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B21" s="22"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="26"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="26"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+      <c r="L21" s="23"/>
+      <c r="M21" s="23"/>
+      <c r="N21" s="23"/>
+      <c r="O21" s="24"/>
     </row>
     <row r="22" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B22" s="62"/>
-      <c r="C22" s="76"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
-      <c r="H22" s="63"/>
-      <c r="I22" s="62"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="76"/>
-      <c r="M22" s="76"/>
-      <c r="N22" s="76"/>
-      <c r="O22" s="63"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="109"/>
+      <c r="D22" s="109"/>
+      <c r="E22" s="109"/>
+      <c r="F22" s="109"/>
+      <c r="G22" s="109"/>
+      <c r="H22" s="38"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="109"/>
+      <c r="K22" s="109"/>
+      <c r="L22" s="109"/>
+      <c r="M22" s="109"/>
+      <c r="N22" s="109"/>
+      <c r="O22" s="38"/>
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B23" s="62"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="63"/>
-      <c r="I23" s="62"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="76"/>
-      <c r="M23" s="76"/>
-      <c r="N23" s="76"/>
-      <c r="O23" s="63"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="109"/>
+      <c r="D23" s="109"/>
+      <c r="E23" s="109"/>
+      <c r="F23" s="109"/>
+      <c r="G23" s="109"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="109"/>
+      <c r="K23" s="109"/>
+      <c r="L23" s="109"/>
+      <c r="M23" s="109"/>
+      <c r="N23" s="109"/>
+      <c r="O23" s="38"/>
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B24" s="27"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="28"/>
-      <c r="K24" s="28"/>
-      <c r="L24" s="28"/>
-      <c r="M24" s="28"/>
-      <c r="N24" s="28"/>
-      <c r="O24" s="29"/>
+      <c r="B24" s="25"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="27"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="27"/>
     </row>
     <row r="25" spans="2:15" ht="27.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B25" s="40" t="s">
+      <c r="B25" s="30" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="23"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="144" t="s">
+      <c r="C25" s="21"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="77" t="s">
         <v>167</v>
       </c>
-      <c r="F25" s="145"/>
-      <c r="G25" s="40" t="s">
+      <c r="F25" s="78"/>
+      <c r="G25" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="H25" s="23"/>
-      <c r="I25" s="40" t="s">
+      <c r="H25" s="21"/>
+      <c r="I25" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="41" t="s">
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="39" t="s">
         <v>142</v>
       </c>
-      <c r="M25" s="42"/>
-      <c r="N25" s="41" t="s">
+      <c r="M25" s="40"/>
+      <c r="N25" s="39" t="s">
         <v>145</v>
       </c>
-      <c r="O25" s="150"/>
+      <c r="O25" s="43"/>
     </row>
     <row r="26" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B26" s="22"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="80"/>
-      <c r="F26" s="81"/>
-      <c r="G26" s="80"/>
-      <c r="H26" s="81"/>
-      <c r="I26" s="146"/>
-      <c r="J26" s="147"/>
-      <c r="K26" s="148"/>
-      <c r="L26" s="146"/>
-      <c r="M26" s="147"/>
-      <c r="N26" s="149"/>
-      <c r="O26" s="148"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="44"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="44"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="42"/>
+      <c r="K26" s="79"/>
+      <c r="L26" s="41"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="80"/>
+      <c r="O26" s="79"/>
     </row>
     <row r="27" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="5"/>
@@ -3981,374 +3981,374 @@
       <c r="O27" s="5"/>
     </row>
     <row r="28" spans="2:15" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B28" s="109" t="s">
+      <c r="B28" s="110" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="110"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="110"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="110"/>
-      <c r="N28" s="110"/>
-      <c r="O28" s="111"/>
+      <c r="C28" s="111"/>
+      <c r="D28" s="111"/>
+      <c r="E28" s="111"/>
+      <c r="F28" s="111"/>
+      <c r="G28" s="111"/>
+      <c r="H28" s="111"/>
+      <c r="I28" s="111"/>
+      <c r="J28" s="111"/>
+      <c r="K28" s="111"/>
+      <c r="L28" s="111"/>
+      <c r="M28" s="111"/>
+      <c r="N28" s="111"/>
+      <c r="O28" s="112"/>
     </row>
     <row r="29" spans="2:15" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B29" s="131" t="s">
+      <c r="B29" s="60" t="s">
         <v>26</v>
       </c>
-      <c r="C29" s="132"/>
-      <c r="D29" s="132"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="132"/>
-      <c r="I29" s="132"/>
-      <c r="J29" s="132"/>
-      <c r="K29" s="132"/>
-      <c r="L29" s="132"/>
-      <c r="M29" s="132"/>
-      <c r="N29" s="132"/>
-      <c r="O29" s="133"/>
+      <c r="C29" s="61"/>
+      <c r="D29" s="61"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="61"/>
+      <c r="K29" s="61"/>
+      <c r="L29" s="61"/>
+      <c r="M29" s="61"/>
+      <c r="N29" s="61"/>
+      <c r="O29" s="62"/>
     </row>
     <row r="30" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="142" t="s">
+      <c r="B30" s="74" t="s">
         <v>141</v>
       </c>
-      <c r="C30" s="142"/>
-      <c r="D30" s="142"/>
-      <c r="E30" s="142"/>
-      <c r="F30" s="142"/>
-      <c r="G30" s="142"/>
-      <c r="H30" s="142"/>
-      <c r="I30" s="142"/>
-      <c r="J30" s="143"/>
-      <c r="K30" s="139" t="s">
+      <c r="C30" s="74"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="75"/>
+      <c r="K30" s="71" t="s">
         <v>140</v>
       </c>
-      <c r="L30" s="140"/>
-      <c r="M30" s="140"/>
-      <c r="N30" s="140"/>
-      <c r="O30" s="141"/>
+      <c r="L30" s="72"/>
+      <c r="M30" s="72"/>
+      <c r="N30" s="72"/>
+      <c r="O30" s="73"/>
     </row>
     <row r="31" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="114" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="21"/>
-      <c r="D31" s="20" t="s">
+      <c r="C31" s="116"/>
+      <c r="D31" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="E31" s="21"/>
+      <c r="E31" s="116"/>
       <c r="F31" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G31" s="20" t="s">
+      <c r="G31" s="114" t="s">
         <v>30</v>
       </c>
-      <c r="H31" s="21"/>
-      <c r="I31" s="20" t="s">
+      <c r="H31" s="116"/>
+      <c r="I31" s="114" t="s">
         <v>169</v>
       </c>
-      <c r="J31" s="103"/>
-      <c r="K31" s="151" t="s">
+      <c r="J31" s="115"/>
+      <c r="K31" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="L31" s="123"/>
+      <c r="L31" s="47"/>
       <c r="M31" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="N31" s="122" t="s">
+      <c r="N31" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="O31" s="123"/>
+      <c r="O31" s="47"/>
     </row>
     <row r="32" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B32" s="99" t="s">
+      <c r="B32" s="29" t="s">
         <v>170</v>
       </c>
-      <c r="C32" s="99"/>
-      <c r="D32" s="64"/>
-      <c r="E32" s="99"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="29"/>
       <c r="F32" s="16"/>
-      <c r="G32" s="64"/>
-      <c r="H32" s="99"/>
-      <c r="I32" s="64"/>
-      <c r="J32" s="65"/>
-      <c r="K32" s="66"/>
-      <c r="L32" s="24"/>
+      <c r="G32" s="28"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="113"/>
+      <c r="K32" s="65"/>
+      <c r="L32" s="22"/>
       <c r="M32" s="4"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="24"/>
+      <c r="N32" s="20"/>
+      <c r="O32" s="22"/>
     </row>
     <row r="33" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B33" s="99" t="s">
+      <c r="B33" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="C33" s="99"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="99"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="29"/>
       <c r="F33" s="16"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="99"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="70"/>
-      <c r="K33" s="71"/>
-      <c r="L33" s="24"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="29"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="76"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="22"/>
       <c r="M33" s="4"/>
-      <c r="N33" s="22"/>
-      <c r="O33" s="24"/>
+      <c r="N33" s="20"/>
+      <c r="O33" s="22"/>
     </row>
     <row r="34" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B34" s="99" t="s">
+      <c r="B34" s="29" t="s">
         <v>116</v>
       </c>
-      <c r="C34" s="99"/>
-      <c r="D34" s="64"/>
-      <c r="E34" s="99"/>
+      <c r="C34" s="29"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="29"/>
       <c r="F34" s="16"/>
-      <c r="G34" s="64"/>
-      <c r="H34" s="99"/>
-      <c r="I34" s="64"/>
-      <c r="J34" s="65"/>
-      <c r="K34" s="66"/>
-      <c r="L34" s="24"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="113"/>
+      <c r="K34" s="65"/>
+      <c r="L34" s="22"/>
       <c r="M34" s="4"/>
-      <c r="N34" s="22"/>
-      <c r="O34" s="24"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="22"/>
     </row>
     <row r="35" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B35" s="99" t="s">
+      <c r="B35" s="29" t="s">
         <v>117</v>
       </c>
-      <c r="C35" s="99"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="99"/>
+      <c r="C35" s="29"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="29"/>
       <c r="F35" s="16"/>
-      <c r="G35" s="64"/>
-      <c r="H35" s="99"/>
-      <c r="I35" s="64"/>
-      <c r="J35" s="70"/>
-      <c r="K35" s="71"/>
-      <c r="L35" s="24"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="29"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="76"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="22"/>
       <c r="M35" s="4"/>
-      <c r="N35" s="22"/>
-      <c r="O35" s="24"/>
+      <c r="N35" s="20"/>
+      <c r="O35" s="22"/>
     </row>
     <row r="36" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B36" s="15" t="s">
         <v>118</v>
       </c>
       <c r="C36" s="15"/>
-      <c r="D36" s="64"/>
-      <c r="E36" s="99"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="29"/>
       <c r="F36" s="16"/>
-      <c r="G36" s="64"/>
-      <c r="H36" s="99"/>
-      <c r="I36" s="64"/>
-      <c r="J36" s="70"/>
-      <c r="K36" s="71"/>
-      <c r="L36" s="24"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="76"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="22"/>
       <c r="M36" s="4"/>
-      <c r="N36" s="22"/>
-      <c r="O36" s="24"/>
+      <c r="N36" s="20"/>
+      <c r="O36" s="22"/>
     </row>
     <row r="37" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B37" s="15" t="s">
         <v>119</v>
       </c>
       <c r="C37" s="15"/>
-      <c r="D37" s="64"/>
-      <c r="E37" s="99"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="29"/>
       <c r="F37" s="16"/>
-      <c r="G37" s="64"/>
-      <c r="H37" s="99"/>
-      <c r="I37" s="64"/>
-      <c r="J37" s="70"/>
-      <c r="K37" s="71"/>
-      <c r="L37" s="24"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="76"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="22"/>
       <c r="M37" s="4"/>
-      <c r="N37" s="22"/>
-      <c r="O37" s="24"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="22"/>
     </row>
     <row r="38" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B38" s="134" t="s">
+      <c r="B38" s="66" t="s">
         <v>25</v>
       </c>
-      <c r="C38" s="135"/>
-      <c r="D38" s="135"/>
-      <c r="E38" s="135"/>
-      <c r="F38" s="135"/>
-      <c r="G38" s="135"/>
-      <c r="H38" s="135"/>
-      <c r="I38" s="135"/>
-      <c r="J38" s="135"/>
-      <c r="K38" s="132"/>
-      <c r="L38" s="132"/>
-      <c r="M38" s="132"/>
-      <c r="N38" s="132"/>
-      <c r="O38" s="133"/>
+      <c r="C38" s="67"/>
+      <c r="D38" s="67"/>
+      <c r="E38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="67"/>
+      <c r="K38" s="61"/>
+      <c r="L38" s="61"/>
+      <c r="M38" s="61"/>
+      <c r="N38" s="61"/>
+      <c r="O38" s="62"/>
     </row>
     <row r="39" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B39" s="136" t="s">
+      <c r="B39" s="68" t="s">
         <v>141</v>
       </c>
-      <c r="C39" s="137"/>
-      <c r="D39" s="137"/>
-      <c r="E39" s="137"/>
-      <c r="F39" s="137"/>
-      <c r="G39" s="137"/>
-      <c r="H39" s="137"/>
-      <c r="I39" s="137"/>
-      <c r="J39" s="138"/>
-      <c r="K39" s="139" t="s">
+      <c r="C39" s="69"/>
+      <c r="D39" s="69"/>
+      <c r="E39" s="69"/>
+      <c r="F39" s="69"/>
+      <c r="G39" s="69"/>
+      <c r="H39" s="69"/>
+      <c r="I39" s="69"/>
+      <c r="J39" s="70"/>
+      <c r="K39" s="71" t="s">
         <v>140</v>
       </c>
-      <c r="L39" s="140"/>
-      <c r="M39" s="140"/>
-      <c r="N39" s="140"/>
-      <c r="O39" s="141"/>
+      <c r="L39" s="72"/>
+      <c r="M39" s="72"/>
+      <c r="N39" s="72"/>
+      <c r="O39" s="73"/>
     </row>
     <row r="40" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B40" s="102" t="s">
+      <c r="B40" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="29"/>
-      <c r="D40" s="102" t="s">
+      <c r="C40" s="27"/>
+      <c r="D40" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="E40" s="29"/>
+      <c r="E40" s="27"/>
       <c r="F40" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G40" s="102" t="s">
+      <c r="G40" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="H40" s="29"/>
-      <c r="I40" s="102" t="s">
+      <c r="H40" s="27"/>
+      <c r="I40" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="J40" s="152"/>
-      <c r="K40" s="153" t="s">
+      <c r="J40" s="49"/>
+      <c r="K40" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="L40" s="123"/>
+      <c r="L40" s="47"/>
       <c r="M40" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="N40" s="122" t="s">
+      <c r="N40" s="51" t="s">
         <v>30</v>
       </c>
-      <c r="O40" s="123"/>
+      <c r="O40" s="47"/>
     </row>
     <row r="41" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B41" s="101" t="s">
+      <c r="B41" s="63" t="s">
         <v>116</v>
       </c>
-      <c r="C41" s="24"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="24"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="22"/>
       <c r="F41" s="4"/>
-      <c r="G41" s="22"/>
-      <c r="H41" s="24"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="100"/>
-      <c r="K41" s="66"/>
-      <c r="L41" s="24"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="22"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="64"/>
+      <c r="K41" s="65"/>
+      <c r="L41" s="22"/>
       <c r="M41" s="4"/>
-      <c r="N41" s="22"/>
-      <c r="O41" s="24"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="22"/>
     </row>
     <row r="42" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B42" s="101" t="s">
+      <c r="B42" s="63" t="s">
         <v>117</v>
       </c>
-      <c r="C42" s="24"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="24"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="22"/>
       <c r="F42" s="4"/>
-      <c r="G42" s="22"/>
-      <c r="H42" s="24"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="100"/>
-      <c r="K42" s="66"/>
-      <c r="L42" s="24"/>
+      <c r="G42" s="20"/>
+      <c r="H42" s="22"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="64"/>
+      <c r="K42" s="65"/>
+      <c r="L42" s="22"/>
       <c r="M42" s="4"/>
-      <c r="N42" s="22"/>
-      <c r="O42" s="24"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="22"/>
     </row>
     <row r="43" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B43" s="101" t="s">
+      <c r="B43" s="63" t="s">
         <v>118</v>
       </c>
-      <c r="C43" s="24"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="24"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="22"/>
       <c r="F43" s="4"/>
-      <c r="G43" s="22"/>
-      <c r="H43" s="24"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="100"/>
-      <c r="K43" s="66"/>
-      <c r="L43" s="24"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="22"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="64"/>
+      <c r="K43" s="65"/>
+      <c r="L43" s="22"/>
       <c r="M43" s="4"/>
-      <c r="N43" s="22"/>
-      <c r="O43" s="24"/>
+      <c r="N43" s="20"/>
+      <c r="O43" s="22"/>
     </row>
     <row r="44" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B44" s="101" t="s">
+      <c r="B44" s="63" t="s">
         <v>119</v>
       </c>
-      <c r="C44" s="24"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="24"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="22"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="24"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="66"/>
-      <c r="L44" s="24"/>
+      <c r="G44" s="20"/>
+      <c r="H44" s="22"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="64"/>
+      <c r="K44" s="65"/>
+      <c r="L44" s="22"/>
       <c r="M44" s="4"/>
-      <c r="N44" s="22"/>
-      <c r="O44" s="24"/>
+      <c r="N44" s="20"/>
+      <c r="O44" s="22"/>
     </row>
     <row r="45" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B45" s="101"/>
-      <c r="C45" s="24"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="24"/>
+      <c r="B45" s="63"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="22"/>
       <c r="F45" s="4"/>
-      <c r="G45" s="22"/>
-      <c r="H45" s="24"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="100"/>
-      <c r="K45" s="66"/>
-      <c r="L45" s="24"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="22"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="64"/>
+      <c r="K45" s="65"/>
+      <c r="L45" s="22"/>
       <c r="M45" s="4"/>
-      <c r="N45" s="22"/>
-      <c r="O45" s="24"/>
+      <c r="N45" s="20"/>
+      <c r="O45" s="22"/>
     </row>
     <row r="46" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B46" s="101"/>
-      <c r="C46" s="24"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="24"/>
+      <c r="B46" s="63"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="20"/>
+      <c r="E46" s="22"/>
       <c r="F46" s="4"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="24"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="100"/>
-      <c r="K46" s="66"/>
-      <c r="L46" s="24"/>
+      <c r="G46" s="20"/>
+      <c r="H46" s="22"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="64"/>
+      <c r="K46" s="65"/>
+      <c r="L46" s="22"/>
       <c r="M46" s="4"/>
-      <c r="N46" s="22"/>
-      <c r="O46" s="24"/>
+      <c r="N46" s="20"/>
+      <c r="O46" s="22"/>
     </row>
     <row r="47" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="5"/>
@@ -4367,96 +4367,96 @@
       <c r="O47" s="5"/>
     </row>
     <row r="48" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B48" s="67" t="s">
+      <c r="B48" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="C48" s="68"/>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="68"/>
-      <c r="G48" s="68"/>
-      <c r="H48" s="68"/>
-      <c r="I48" s="68"/>
-      <c r="J48" s="68"/>
-      <c r="K48" s="68"/>
-      <c r="L48" s="68"/>
-      <c r="M48" s="68"/>
-      <c r="N48" s="68"/>
-      <c r="O48" s="69"/>
+      <c r="C48" s="33"/>
+      <c r="D48" s="33"/>
+      <c r="E48" s="33"/>
+      <c r="F48" s="33"/>
+      <c r="G48" s="33"/>
+      <c r="H48" s="33"/>
+      <c r="I48" s="33"/>
+      <c r="J48" s="33"/>
+      <c r="K48" s="33"/>
+      <c r="L48" s="33"/>
+      <c r="M48" s="33"/>
+      <c r="N48" s="33"/>
+      <c r="O48" s="34"/>
     </row>
     <row r="49" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B49" s="86" t="s">
+      <c r="B49" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="C49" s="23"/>
-      <c r="D49" s="23"/>
-      <c r="E49" s="23"/>
-      <c r="F49" s="23"/>
-      <c r="G49" s="23"/>
-      <c r="H49" s="23"/>
-      <c r="I49" s="23"/>
-      <c r="J49" s="23"/>
-      <c r="K49" s="23"/>
-      <c r="L49" s="23"/>
-      <c r="M49" s="23"/>
-      <c r="N49" s="23"/>
-      <c r="O49" s="24"/>
+      <c r="C49" s="21"/>
+      <c r="D49" s="21"/>
+      <c r="E49" s="21"/>
+      <c r="F49" s="21"/>
+      <c r="G49" s="21"/>
+      <c r="H49" s="21"/>
+      <c r="I49" s="21"/>
+      <c r="J49" s="21"/>
+      <c r="K49" s="21"/>
+      <c r="L49" s="21"/>
+      <c r="M49" s="21"/>
+      <c r="N49" s="21"/>
+      <c r="O49" s="22"/>
     </row>
     <row r="50" spans="2:15" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="40" t="s">
+      <c r="B50" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="C50" s="23"/>
-      <c r="D50" s="24"/>
-      <c r="E50" s="40" t="s">
+      <c r="C50" s="21"/>
+      <c r="D50" s="22"/>
+      <c r="E50" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="F50" s="23"/>
-      <c r="G50" s="24"/>
-      <c r="H50" s="40" t="s">
+      <c r="F50" s="21"/>
+      <c r="G50" s="22"/>
+      <c r="H50" s="30" t="s">
         <v>34</v>
       </c>
-      <c r="I50" s="23"/>
-      <c r="J50" s="23"/>
-      <c r="K50" s="24"/>
-      <c r="L50" s="40" t="s">
+      <c r="I50" s="21"/>
+      <c r="J50" s="21"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="M50" s="23"/>
-      <c r="N50" s="23"/>
-      <c r="O50" s="24"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="21"/>
+      <c r="O50" s="22"/>
     </row>
     <row r="51" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B51" s="22"/>
-      <c r="C51" s="25"/>
-      <c r="D51" s="26"/>
-      <c r="E51" s="22"/>
-      <c r="F51" s="25"/>
-      <c r="G51" s="26"/>
-      <c r="H51" s="22"/>
-      <c r="I51" s="25"/>
-      <c r="J51" s="25"/>
-      <c r="K51" s="26"/>
-      <c r="L51" s="22"/>
-      <c r="M51" s="25"/>
-      <c r="N51" s="25"/>
-      <c r="O51" s="26"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="24"/>
+      <c r="E51" s="20"/>
+      <c r="F51" s="23"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="20"/>
+      <c r="I51" s="23"/>
+      <c r="J51" s="23"/>
+      <c r="K51" s="24"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="23"/>
+      <c r="N51" s="23"/>
+      <c r="O51" s="24"/>
     </row>
     <row r="52" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B52" s="27"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="27"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="27"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="27"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="29"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="27"/>
+      <c r="H52" s="25"/>
+      <c r="I52" s="26"/>
+      <c r="J52" s="26"/>
+      <c r="K52" s="27"/>
+      <c r="L52" s="25"/>
+      <c r="M52" s="26"/>
+      <c r="N52" s="26"/>
+      <c r="O52" s="27"/>
     </row>
     <row r="53" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B53" s="5"/>
@@ -4475,202 +4475,202 @@
       <c r="O53" s="5"/>
     </row>
     <row r="54" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B54" s="86" t="s">
+      <c r="B54" s="52" t="s">
         <v>35</v>
       </c>
-      <c r="C54" s="23"/>
-      <c r="D54" s="23"/>
-      <c r="E54" s="23"/>
-      <c r="F54" s="23"/>
-      <c r="G54" s="23"/>
-      <c r="H54" s="23"/>
-      <c r="I54" s="23"/>
-      <c r="J54" s="23"/>
-      <c r="K54" s="23"/>
-      <c r="L54" s="23"/>
-      <c r="M54" s="23"/>
-      <c r="N54" s="23"/>
-      <c r="O54" s="24"/>
+      <c r="C54" s="21"/>
+      <c r="D54" s="21"/>
+      <c r="E54" s="21"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
+      <c r="O54" s="22"/>
     </row>
     <row r="55" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B55" s="40" t="s">
+      <c r="B55" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="C55" s="23"/>
-      <c r="D55" s="24"/>
-      <c r="E55" s="40" t="s">
+      <c r="C55" s="21"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="F55" s="23"/>
-      <c r="G55" s="24"/>
-      <c r="H55" s="40" t="s">
+      <c r="F55" s="21"/>
+      <c r="G55" s="22"/>
+      <c r="H55" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="I55" s="23"/>
-      <c r="J55" s="23"/>
-      <c r="K55" s="24"/>
-      <c r="L55" s="40" t="s">
+      <c r="I55" s="21"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="22"/>
+      <c r="L55" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="M55" s="23"/>
-      <c r="N55" s="23"/>
-      <c r="O55" s="24"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="22"/>
     </row>
     <row r="56" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="93" t="s">
+      <c r="B56" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="C56" s="94"/>
-      <c r="D56" s="95"/>
-      <c r="E56" s="22" t="s">
+      <c r="C56" s="54"/>
+      <c r="D56" s="55"/>
+      <c r="E56" s="20" t="s">
         <v>154</v>
       </c>
-      <c r="F56" s="25"/>
-      <c r="G56" s="26"/>
-      <c r="H56" s="22"/>
-      <c r="I56" s="25"/>
-      <c r="J56" s="25"/>
-      <c r="K56" s="26"/>
-      <c r="L56" s="22"/>
-      <c r="M56" s="25"/>
-      <c r="N56" s="25"/>
-      <c r="O56" s="26"/>
+      <c r="F56" s="23"/>
+      <c r="G56" s="24"/>
+      <c r="H56" s="20"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="23"/>
+      <c r="K56" s="24"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="23"/>
+      <c r="N56" s="23"/>
+      <c r="O56" s="24"/>
     </row>
     <row r="57" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="96"/>
-      <c r="C57" s="97"/>
-      <c r="D57" s="98"/>
-      <c r="E57" s="27"/>
-      <c r="F57" s="28"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="27"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="28"/>
-      <c r="K57" s="29"/>
-      <c r="L57" s="27"/>
-      <c r="M57" s="28"/>
-      <c r="N57" s="28"/>
-      <c r="O57" s="29"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="58"/>
+      <c r="E57" s="25"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="27"/>
+      <c r="H57" s="25"/>
+      <c r="I57" s="26"/>
+      <c r="J57" s="26"/>
+      <c r="K57" s="27"/>
+      <c r="L57" s="25"/>
+      <c r="M57" s="26"/>
+      <c r="N57" s="26"/>
+      <c r="O57" s="27"/>
     </row>
     <row r="58" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B58" s="40" t="s">
+      <c r="B58" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="C58" s="23"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="40" t="s">
+      <c r="C58" s="21"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="F58" s="23"/>
-      <c r="G58" s="24"/>
-      <c r="H58" s="40" t="s">
+      <c r="F58" s="21"/>
+      <c r="G58" s="22"/>
+      <c r="H58" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="I58" s="23"/>
-      <c r="J58" s="23"/>
-      <c r="K58" s="24"/>
-      <c r="L58" s="40" t="s">
+      <c r="I58" s="21"/>
+      <c r="J58" s="21"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="M58" s="23"/>
-      <c r="N58" s="23"/>
-      <c r="O58" s="24"/>
+      <c r="M58" s="21"/>
+      <c r="N58" s="21"/>
+      <c r="O58" s="22"/>
     </row>
     <row r="59" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="93" t="s">
+      <c r="B59" s="53" t="s">
         <v>134</v>
       </c>
-      <c r="C59" s="94"/>
-      <c r="D59" s="95"/>
-      <c r="E59" s="22" t="s">
+      <c r="C59" s="54"/>
+      <c r="D59" s="55"/>
+      <c r="E59" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="F59" s="25"/>
-      <c r="G59" s="26"/>
-      <c r="H59" s="22"/>
-      <c r="I59" s="25"/>
-      <c r="J59" s="25"/>
-      <c r="K59" s="26"/>
-      <c r="L59" s="22"/>
-      <c r="M59" s="25"/>
-      <c r="N59" s="25"/>
-      <c r="O59" s="26"/>
+      <c r="F59" s="23"/>
+      <c r="G59" s="24"/>
+      <c r="H59" s="20"/>
+      <c r="I59" s="23"/>
+      <c r="J59" s="23"/>
+      <c r="K59" s="24"/>
+      <c r="L59" s="20"/>
+      <c r="M59" s="23"/>
+      <c r="N59" s="23"/>
+      <c r="O59" s="24"/>
     </row>
     <row r="60" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="96"/>
-      <c r="C60" s="97"/>
-      <c r="D60" s="98"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="28"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="28"/>
-      <c r="J60" s="28"/>
-      <c r="K60" s="29"/>
-      <c r="L60" s="27"/>
-      <c r="M60" s="28"/>
-      <c r="N60" s="28"/>
-      <c r="O60" s="29"/>
+      <c r="B60" s="56"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="25"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="27"/>
+      <c r="H60" s="25"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="26"/>
+      <c r="K60" s="27"/>
+      <c r="L60" s="25"/>
+      <c r="M60" s="26"/>
+      <c r="N60" s="26"/>
+      <c r="O60" s="27"/>
     </row>
     <row r="61" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B61" s="40" t="s">
+      <c r="B61" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="C61" s="23"/>
-      <c r="D61" s="24"/>
-      <c r="E61" s="40" t="s">
+      <c r="C61" s="21"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="30" t="s">
         <v>36</v>
       </c>
-      <c r="F61" s="23"/>
-      <c r="G61" s="24"/>
-      <c r="H61" s="40" t="s">
+      <c r="F61" s="21"/>
+      <c r="G61" s="22"/>
+      <c r="H61" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="I61" s="23"/>
-      <c r="J61" s="23"/>
-      <c r="K61" s="24"/>
-      <c r="L61" s="40" t="s">
+      <c r="I61" s="21"/>
+      <c r="J61" s="21"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="M61" s="23"/>
-      <c r="N61" s="23"/>
-      <c r="O61" s="24"/>
+      <c r="M61" s="21"/>
+      <c r="N61" s="21"/>
+      <c r="O61" s="22"/>
     </row>
     <row r="62" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="93" t="s">
+      <c r="B62" s="53" t="s">
         <v>172</v>
       </c>
-      <c r="C62" s="94"/>
-      <c r="D62" s="95"/>
-      <c r="E62" s="22" t="s">
+      <c r="C62" s="54"/>
+      <c r="D62" s="55"/>
+      <c r="E62" s="20" t="s">
         <v>155</v>
       </c>
-      <c r="F62" s="25"/>
-      <c r="G62" s="26"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="25"/>
-      <c r="J62" s="25"/>
-      <c r="K62" s="26"/>
-      <c r="L62" s="22"/>
-      <c r="M62" s="25"/>
-      <c r="N62" s="25"/>
-      <c r="O62" s="26"/>
+      <c r="F62" s="23"/>
+      <c r="G62" s="24"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="23"/>
+      <c r="J62" s="23"/>
+      <c r="K62" s="24"/>
+      <c r="L62" s="20"/>
+      <c r="M62" s="23"/>
+      <c r="N62" s="23"/>
+      <c r="O62" s="24"/>
     </row>
     <row r="63" spans="2:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="96"/>
-      <c r="C63" s="97"/>
-      <c r="D63" s="98"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="28"/>
-      <c r="G63" s="29"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="28"/>
-      <c r="J63" s="28"/>
-      <c r="K63" s="29"/>
-      <c r="L63" s="27"/>
-      <c r="M63" s="28"/>
-      <c r="N63" s="28"/>
-      <c r="O63" s="29"/>
+      <c r="B63" s="56"/>
+      <c r="C63" s="57"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="27"/>
+      <c r="H63" s="25"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="26"/>
+      <c r="K63" s="27"/>
+      <c r="L63" s="25"/>
+      <c r="M63" s="26"/>
+      <c r="N63" s="26"/>
+      <c r="O63" s="27"/>
     </row>
     <row r="64" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B64" s="5"/>
@@ -4689,41 +4689,41 @@
       <c r="O64" s="5"/>
     </row>
     <row r="65" spans="2:15" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="67" t="s">
+      <c r="B65" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="C65" s="68"/>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="68"/>
-      <c r="H65" s="68"/>
-      <c r="I65" s="68"/>
-      <c r="J65" s="68"/>
-      <c r="K65" s="68"/>
-      <c r="L65" s="68"/>
-      <c r="M65" s="68"/>
-      <c r="N65" s="68"/>
-      <c r="O65" s="69"/>
+      <c r="C65" s="33"/>
+      <c r="D65" s="33"/>
+      <c r="E65" s="33"/>
+      <c r="F65" s="33"/>
+      <c r="G65" s="33"/>
+      <c r="H65" s="33"/>
+      <c r="I65" s="33"/>
+      <c r="J65" s="33"/>
+      <c r="K65" s="33"/>
+      <c r="L65" s="33"/>
+      <c r="M65" s="33"/>
+      <c r="N65" s="33"/>
+      <c r="O65" s="34"/>
     </row>
     <row r="66" spans="2:15" ht="33" x14ac:dyDescent="0.3">
-      <c r="B66" s="30" t="s">
+      <c r="B66" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="C66" s="24"/>
+      <c r="C66" s="22"/>
       <c r="D66" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E66" s="30" t="s">
+      <c r="E66" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="F66" s="23"/>
-      <c r="G66" s="24"/>
-      <c r="H66" s="30" t="s">
+      <c r="F66" s="21"/>
+      <c r="G66" s="22"/>
+      <c r="H66" s="48" t="s">
         <v>42</v>
       </c>
-      <c r="I66" s="23"/>
-      <c r="J66" s="24"/>
+      <c r="I66" s="21"/>
+      <c r="J66" s="22"/>
       <c r="K66" s="6" t="s">
         <v>43</v>
       </c>
@@ -4733,340 +4733,340 @@
       <c r="M66" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="N66" s="30" t="s">
+      <c r="N66" s="48" t="s">
         <v>46</v>
       </c>
-      <c r="O66" s="24"/>
+      <c r="O66" s="22"/>
     </row>
     <row r="67" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B67" s="61" t="s">
+      <c r="B67" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="C67" s="26"/>
+      <c r="C67" s="24"/>
       <c r="D67" s="4"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="23"/>
-      <c r="G67" s="24"/>
-      <c r="H67" s="22"/>
-      <c r="I67" s="23"/>
-      <c r="J67" s="24"/>
+      <c r="E67" s="20"/>
+      <c r="F67" s="21"/>
+      <c r="G67" s="22"/>
+      <c r="H67" s="20"/>
+      <c r="I67" s="21"/>
+      <c r="J67" s="22"/>
       <c r="K67" s="4"/>
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
-      <c r="N67" s="22"/>
-      <c r="O67" s="24"/>
+      <c r="N67" s="20"/>
+      <c r="O67" s="22"/>
     </row>
     <row r="68" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B68" s="62"/>
-      <c r="C68" s="63"/>
+      <c r="B68" s="37"/>
+      <c r="C68" s="38"/>
       <c r="D68" s="4"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="23"/>
-      <c r="G68" s="24"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="23"/>
-      <c r="J68" s="24"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="22"/>
+      <c r="H68" s="20"/>
+      <c r="I68" s="21"/>
+      <c r="J68" s="22"/>
       <c r="K68" s="4"/>
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
-      <c r="N68" s="22"/>
-      <c r="O68" s="24"/>
+      <c r="N68" s="20"/>
+      <c r="O68" s="22"/>
     </row>
     <row r="69" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B69" s="62"/>
-      <c r="C69" s="63"/>
+      <c r="B69" s="37"/>
+      <c r="C69" s="38"/>
       <c r="D69" s="4"/>
-      <c r="E69" s="22"/>
-      <c r="F69" s="23"/>
-      <c r="G69" s="24"/>
-      <c r="H69" s="22"/>
-      <c r="I69" s="23"/>
-      <c r="J69" s="24"/>
+      <c r="E69" s="20"/>
+      <c r="F69" s="21"/>
+      <c r="G69" s="22"/>
+      <c r="H69" s="20"/>
+      <c r="I69" s="21"/>
+      <c r="J69" s="22"/>
       <c r="K69" s="4"/>
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
-      <c r="N69" s="22"/>
-      <c r="O69" s="24"/>
+      <c r="N69" s="20"/>
+      <c r="O69" s="22"/>
     </row>
     <row r="70" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B70" s="27"/>
-      <c r="C70" s="29"/>
+      <c r="B70" s="25"/>
+      <c r="C70" s="27"/>
       <c r="D70" s="4"/>
-      <c r="E70" s="22"/>
-      <c r="F70" s="23"/>
-      <c r="G70" s="24"/>
-      <c r="H70" s="22"/>
-      <c r="I70" s="23"/>
-      <c r="J70" s="24"/>
+      <c r="E70" s="20"/>
+      <c r="F70" s="21"/>
+      <c r="G70" s="22"/>
+      <c r="H70" s="20"/>
+      <c r="I70" s="21"/>
+      <c r="J70" s="22"/>
       <c r="K70" s="4"/>
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
-      <c r="N70" s="22"/>
-      <c r="O70" s="24"/>
+      <c r="N70" s="20"/>
+      <c r="O70" s="22"/>
     </row>
     <row r="71" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B71" s="61" t="s">
+      <c r="B71" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="C71" s="26"/>
+      <c r="C71" s="24"/>
       <c r="D71" s="4"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="23"/>
-      <c r="G71" s="24"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="23"/>
-      <c r="J71" s="24"/>
+      <c r="E71" s="20"/>
+      <c r="F71" s="21"/>
+      <c r="G71" s="22"/>
+      <c r="H71" s="20"/>
+      <c r="I71" s="21"/>
+      <c r="J71" s="22"/>
       <c r="K71" s="4"/>
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
-      <c r="N71" s="22"/>
-      <c r="O71" s="24"/>
+      <c r="N71" s="20"/>
+      <c r="O71" s="22"/>
     </row>
     <row r="72" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B72" s="62"/>
-      <c r="C72" s="63"/>
+      <c r="B72" s="37"/>
+      <c r="C72" s="38"/>
       <c r="D72" s="4"/>
-      <c r="E72" s="22"/>
-      <c r="F72" s="23"/>
-      <c r="G72" s="24"/>
-      <c r="H72" s="22"/>
-      <c r="I72" s="23"/>
-      <c r="J72" s="24"/>
+      <c r="E72" s="20"/>
+      <c r="F72" s="21"/>
+      <c r="G72" s="22"/>
+      <c r="H72" s="20"/>
+      <c r="I72" s="21"/>
+      <c r="J72" s="22"/>
       <c r="K72" s="4"/>
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
-      <c r="N72" s="22"/>
-      <c r="O72" s="24"/>
+      <c r="N72" s="20"/>
+      <c r="O72" s="22"/>
     </row>
     <row r="73" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B73" s="62"/>
-      <c r="C73" s="63"/>
+      <c r="B73" s="37"/>
+      <c r="C73" s="38"/>
       <c r="D73" s="4"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="23"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="22"/>
-      <c r="I73" s="23"/>
-      <c r="J73" s="24"/>
+      <c r="E73" s="20"/>
+      <c r="F73" s="21"/>
+      <c r="G73" s="22"/>
+      <c r="H73" s="20"/>
+      <c r="I73" s="21"/>
+      <c r="J73" s="22"/>
       <c r="K73" s="4"/>
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
-      <c r="N73" s="22"/>
-      <c r="O73" s="24"/>
+      <c r="N73" s="20"/>
+      <c r="O73" s="22"/>
     </row>
     <row r="74" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B74" s="27"/>
-      <c r="C74" s="29"/>
+      <c r="B74" s="25"/>
+      <c r="C74" s="27"/>
       <c r="D74" s="4"/>
-      <c r="E74" s="22"/>
-      <c r="F74" s="23"/>
-      <c r="G74" s="24"/>
-      <c r="H74" s="22"/>
-      <c r="I74" s="23"/>
-      <c r="J74" s="24"/>
+      <c r="E74" s="20"/>
+      <c r="F74" s="21"/>
+      <c r="G74" s="22"/>
+      <c r="H74" s="20"/>
+      <c r="I74" s="21"/>
+      <c r="J74" s="22"/>
       <c r="K74" s="4"/>
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
-      <c r="N74" s="22"/>
-      <c r="O74" s="24"/>
+      <c r="N74" s="20"/>
+      <c r="O74" s="22"/>
     </row>
     <row r="75" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B75" s="61" t="s">
+      <c r="B75" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="C75" s="26"/>
+      <c r="C75" s="24"/>
       <c r="D75" s="4"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="24"/>
-      <c r="H75" s="22"/>
-      <c r="I75" s="23"/>
-      <c r="J75" s="24"/>
+      <c r="E75" s="20"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="22"/>
+      <c r="H75" s="20"/>
+      <c r="I75" s="21"/>
+      <c r="J75" s="22"/>
       <c r="K75" s="4"/>
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
-      <c r="N75" s="22"/>
-      <c r="O75" s="24"/>
+      <c r="N75" s="20"/>
+      <c r="O75" s="22"/>
     </row>
     <row r="76" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B76" s="62"/>
-      <c r="C76" s="63"/>
+      <c r="B76" s="37"/>
+      <c r="C76" s="38"/>
       <c r="D76" s="4"/>
-      <c r="E76" s="22"/>
-      <c r="F76" s="23"/>
-      <c r="G76" s="24"/>
-      <c r="H76" s="22"/>
-      <c r="I76" s="23"/>
-      <c r="J76" s="24"/>
+      <c r="E76" s="20"/>
+      <c r="F76" s="21"/>
+      <c r="G76" s="22"/>
+      <c r="H76" s="20"/>
+      <c r="I76" s="21"/>
+      <c r="J76" s="22"/>
       <c r="K76" s="4"/>
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
-      <c r="N76" s="22"/>
-      <c r="O76" s="24"/>
+      <c r="N76" s="20"/>
+      <c r="O76" s="22"/>
     </row>
     <row r="77" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B77" s="62"/>
-      <c r="C77" s="63"/>
+      <c r="B77" s="37"/>
+      <c r="C77" s="38"/>
       <c r="D77" s="4"/>
-      <c r="E77" s="22"/>
-      <c r="F77" s="23"/>
-      <c r="G77" s="24"/>
-      <c r="H77" s="22"/>
-      <c r="I77" s="23"/>
-      <c r="J77" s="24"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="21"/>
+      <c r="G77" s="22"/>
+      <c r="H77" s="20"/>
+      <c r="I77" s="21"/>
+      <c r="J77" s="22"/>
       <c r="K77" s="4"/>
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
-      <c r="N77" s="22"/>
-      <c r="O77" s="24"/>
+      <c r="N77" s="20"/>
+      <c r="O77" s="22"/>
     </row>
     <row r="78" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B78" s="27"/>
-      <c r="C78" s="29"/>
+      <c r="B78" s="25"/>
+      <c r="C78" s="27"/>
       <c r="D78" s="4"/>
-      <c r="E78" s="22"/>
-      <c r="F78" s="23"/>
-      <c r="G78" s="24"/>
-      <c r="H78" s="22"/>
-      <c r="I78" s="23"/>
-      <c r="J78" s="24"/>
+      <c r="E78" s="20"/>
+      <c r="F78" s="21"/>
+      <c r="G78" s="22"/>
+      <c r="H78" s="20"/>
+      <c r="I78" s="21"/>
+      <c r="J78" s="22"/>
       <c r="K78" s="4"/>
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
-      <c r="N78" s="22"/>
-      <c r="O78" s="24"/>
+      <c r="N78" s="20"/>
+      <c r="O78" s="22"/>
     </row>
     <row r="79" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B79" s="61" t="s">
+      <c r="B79" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="C79" s="26"/>
+      <c r="C79" s="24"/>
       <c r="D79" s="4"/>
-      <c r="E79" s="22"/>
-      <c r="F79" s="23"/>
-      <c r="G79" s="24"/>
-      <c r="H79" s="22"/>
-      <c r="I79" s="23"/>
-      <c r="J79" s="24"/>
+      <c r="E79" s="20"/>
+      <c r="F79" s="21"/>
+      <c r="G79" s="22"/>
+      <c r="H79" s="20"/>
+      <c r="I79" s="21"/>
+      <c r="J79" s="22"/>
       <c r="K79" s="4"/>
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
-      <c r="N79" s="22"/>
-      <c r="O79" s="24"/>
+      <c r="N79" s="20"/>
+      <c r="O79" s="22"/>
     </row>
     <row r="80" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B80" s="62"/>
-      <c r="C80" s="63"/>
+      <c r="B80" s="37"/>
+      <c r="C80" s="38"/>
       <c r="D80" s="4"/>
-      <c r="E80" s="22"/>
-      <c r="F80" s="23"/>
-      <c r="G80" s="24"/>
-      <c r="H80" s="22"/>
-      <c r="I80" s="23"/>
-      <c r="J80" s="24"/>
+      <c r="E80" s="20"/>
+      <c r="F80" s="21"/>
+      <c r="G80" s="22"/>
+      <c r="H80" s="20"/>
+      <c r="I80" s="21"/>
+      <c r="J80" s="22"/>
       <c r="K80" s="4"/>
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
-      <c r="N80" s="22"/>
-      <c r="O80" s="24"/>
+      <c r="N80" s="20"/>
+      <c r="O80" s="22"/>
     </row>
     <row r="81" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B81" s="62"/>
-      <c r="C81" s="63"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="38"/>
       <c r="D81" s="4"/>
-      <c r="E81" s="22"/>
-      <c r="F81" s="23"/>
-      <c r="G81" s="24"/>
-      <c r="H81" s="22"/>
-      <c r="I81" s="23"/>
-      <c r="J81" s="24"/>
+      <c r="E81" s="20"/>
+      <c r="F81" s="21"/>
+      <c r="G81" s="22"/>
+      <c r="H81" s="20"/>
+      <c r="I81" s="21"/>
+      <c r="J81" s="22"/>
       <c r="K81" s="4"/>
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
-      <c r="N81" s="22"/>
-      <c r="O81" s="24"/>
+      <c r="N81" s="20"/>
+      <c r="O81" s="22"/>
     </row>
     <row r="82" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B82" s="27"/>
-      <c r="C82" s="29"/>
+      <c r="B82" s="25"/>
+      <c r="C82" s="27"/>
       <c r="D82" s="4"/>
-      <c r="E82" s="22"/>
-      <c r="F82" s="23"/>
-      <c r="G82" s="24"/>
-      <c r="H82" s="22"/>
-      <c r="I82" s="23"/>
-      <c r="J82" s="24"/>
+      <c r="E82" s="20"/>
+      <c r="F82" s="21"/>
+      <c r="G82" s="22"/>
+      <c r="H82" s="20"/>
+      <c r="I82" s="21"/>
+      <c r="J82" s="22"/>
       <c r="K82" s="4"/>
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
-      <c r="N82" s="22"/>
-      <c r="O82" s="24"/>
+      <c r="N82" s="20"/>
+      <c r="O82" s="22"/>
     </row>
     <row r="83" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B83" s="61" t="s">
+      <c r="B83" s="36" t="s">
         <v>49</v>
       </c>
-      <c r="C83" s="26"/>
+      <c r="C83" s="24"/>
       <c r="D83" s="4"/>
-      <c r="E83" s="22"/>
-      <c r="F83" s="23"/>
-      <c r="G83" s="24"/>
-      <c r="H83" s="22"/>
-      <c r="I83" s="23"/>
-      <c r="J83" s="24"/>
+      <c r="E83" s="20"/>
+      <c r="F83" s="21"/>
+      <c r="G83" s="22"/>
+      <c r="H83" s="20"/>
+      <c r="I83" s="21"/>
+      <c r="J83" s="22"/>
       <c r="K83" s="4"/>
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
-      <c r="N83" s="22"/>
-      <c r="O83" s="24"/>
+      <c r="N83" s="20"/>
+      <c r="O83" s="22"/>
     </row>
     <row r="84" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B84" s="62"/>
-      <c r="C84" s="63"/>
+      <c r="B84" s="37"/>
+      <c r="C84" s="38"/>
       <c r="D84" s="4"/>
-      <c r="E84" s="22"/>
-      <c r="F84" s="23"/>
-      <c r="G84" s="24"/>
-      <c r="H84" s="22"/>
-      <c r="I84" s="23"/>
-      <c r="J84" s="24"/>
+      <c r="E84" s="20"/>
+      <c r="F84" s="21"/>
+      <c r="G84" s="22"/>
+      <c r="H84" s="20"/>
+      <c r="I84" s="21"/>
+      <c r="J84" s="22"/>
       <c r="K84" s="4"/>
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
-      <c r="N84" s="22"/>
-      <c r="O84" s="24"/>
+      <c r="N84" s="20"/>
+      <c r="O84" s="22"/>
     </row>
     <row r="85" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B85" s="62"/>
-      <c r="C85" s="63"/>
+      <c r="B85" s="37"/>
+      <c r="C85" s="38"/>
       <c r="D85" s="4"/>
-      <c r="E85" s="22"/>
-      <c r="F85" s="23"/>
-      <c r="G85" s="24"/>
-      <c r="H85" s="22"/>
-      <c r="I85" s="23"/>
-      <c r="J85" s="24"/>
+      <c r="E85" s="20"/>
+      <c r="F85" s="21"/>
+      <c r="G85" s="22"/>
+      <c r="H85" s="20"/>
+      <c r="I85" s="21"/>
+      <c r="J85" s="22"/>
       <c r="K85" s="4"/>
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
-      <c r="N85" s="22"/>
-      <c r="O85" s="24"/>
+      <c r="N85" s="20"/>
+      <c r="O85" s="22"/>
     </row>
     <row r="86" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B86" s="27"/>
-      <c r="C86" s="29"/>
+      <c r="B86" s="25"/>
+      <c r="C86" s="27"/>
       <c r="D86" s="4"/>
-      <c r="E86" s="22"/>
-      <c r="F86" s="23"/>
-      <c r="G86" s="24"/>
-      <c r="H86" s="22"/>
-      <c r="I86" s="23"/>
-      <c r="J86" s="24"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="21"/>
+      <c r="G86" s="22"/>
+      <c r="H86" s="20"/>
+      <c r="I86" s="21"/>
+      <c r="J86" s="22"/>
       <c r="K86" s="4"/>
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
-      <c r="N86" s="22"/>
-      <c r="O86" s="24"/>
+      <c r="N86" s="20"/>
+      <c r="O86" s="22"/>
     </row>
     <row r="87" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B87" s="5"/>
@@ -5085,118 +5085,118 @@
       <c r="O87" s="5"/>
     </row>
     <row r="88" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B88" s="67" t="s">
+      <c r="B88" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="C88" s="68"/>
-      <c r="D88" s="68"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
-      <c r="H88" s="68"/>
-      <c r="I88" s="68"/>
-      <c r="J88" s="68"/>
-      <c r="K88" s="68"/>
-      <c r="L88" s="68"/>
-      <c r="M88" s="68"/>
-      <c r="N88" s="68"/>
-      <c r="O88" s="69"/>
+      <c r="C88" s="33"/>
+      <c r="D88" s="33"/>
+      <c r="E88" s="33"/>
+      <c r="F88" s="33"/>
+      <c r="G88" s="33"/>
+      <c r="H88" s="33"/>
+      <c r="I88" s="33"/>
+      <c r="J88" s="33"/>
+      <c r="K88" s="33"/>
+      <c r="L88" s="33"/>
+      <c r="M88" s="33"/>
+      <c r="N88" s="33"/>
+      <c r="O88" s="34"/>
     </row>
     <row r="89" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B89" s="85" t="s">
+      <c r="B89" s="87" t="s">
         <v>27</v>
       </c>
-      <c r="C89" s="24"/>
-      <c r="D89" s="85" t="s">
+      <c r="C89" s="22"/>
+      <c r="D89" s="87" t="s">
         <v>60</v>
       </c>
-      <c r="E89" s="23"/>
-      <c r="F89" s="23"/>
-      <c r="G89" s="23"/>
-      <c r="H89" s="23"/>
-      <c r="I89" s="24"/>
-      <c r="J89" s="85" t="s">
+      <c r="E89" s="21"/>
+      <c r="F89" s="21"/>
+      <c r="G89" s="21"/>
+      <c r="H89" s="21"/>
+      <c r="I89" s="22"/>
+      <c r="J89" s="87" t="s">
         <v>61</v>
       </c>
-      <c r="K89" s="23"/>
-      <c r="L89" s="24"/>
-      <c r="M89" s="85" t="s">
+      <c r="K89" s="21"/>
+      <c r="L89" s="22"/>
+      <c r="M89" s="87" t="s">
         <v>62</v>
       </c>
-      <c r="N89" s="23"/>
-      <c r="O89" s="24"/>
+      <c r="N89" s="21"/>
+      <c r="O89" s="22"/>
     </row>
     <row r="90" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B90" s="72" t="s">
+      <c r="B90" s="88" t="s">
         <v>63</v>
       </c>
-      <c r="C90" s="24"/>
-      <c r="D90" s="22"/>
-      <c r="E90" s="23"/>
-      <c r="F90" s="23"/>
-      <c r="G90" s="23"/>
-      <c r="H90" s="23"/>
-      <c r="I90" s="24"/>
-      <c r="J90" s="22"/>
-      <c r="K90" s="23"/>
-      <c r="L90" s="24"/>
-      <c r="M90" s="22"/>
-      <c r="N90" s="23"/>
-      <c r="O90" s="24"/>
+      <c r="C90" s="22"/>
+      <c r="D90" s="20"/>
+      <c r="E90" s="21"/>
+      <c r="F90" s="21"/>
+      <c r="G90" s="21"/>
+      <c r="H90" s="21"/>
+      <c r="I90" s="22"/>
+      <c r="J90" s="20"/>
+      <c r="K90" s="21"/>
+      <c r="L90" s="22"/>
+      <c r="M90" s="20"/>
+      <c r="N90" s="21"/>
+      <c r="O90" s="22"/>
     </row>
     <row r="91" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B91" s="72" t="s">
+      <c r="B91" s="88" t="s">
         <v>37</v>
       </c>
-      <c r="C91" s="24"/>
-      <c r="D91" s="22"/>
-      <c r="E91" s="23"/>
-      <c r="F91" s="23"/>
-      <c r="G91" s="23"/>
-      <c r="H91" s="23"/>
-      <c r="I91" s="24"/>
-      <c r="J91" s="22"/>
-      <c r="K91" s="23"/>
-      <c r="L91" s="24"/>
-      <c r="M91" s="22"/>
-      <c r="N91" s="23"/>
-      <c r="O91" s="24"/>
+      <c r="C91" s="22"/>
+      <c r="D91" s="20"/>
+      <c r="E91" s="21"/>
+      <c r="F91" s="21"/>
+      <c r="G91" s="21"/>
+      <c r="H91" s="21"/>
+      <c r="I91" s="22"/>
+      <c r="J91" s="20"/>
+      <c r="K91" s="21"/>
+      <c r="L91" s="22"/>
+      <c r="M91" s="20"/>
+      <c r="N91" s="21"/>
+      <c r="O91" s="22"/>
     </row>
     <row r="92" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B92" s="72" t="s">
+      <c r="B92" s="88" t="s">
         <v>64</v>
       </c>
-      <c r="C92" s="24"/>
-      <c r="D92" s="22"/>
-      <c r="E92" s="23"/>
-      <c r="F92" s="23"/>
-      <c r="G92" s="23"/>
-      <c r="H92" s="23"/>
-      <c r="I92" s="24"/>
-      <c r="J92" s="22"/>
-      <c r="K92" s="23"/>
-      <c r="L92" s="24"/>
-      <c r="M92" s="22"/>
-      <c r="N92" s="23"/>
-      <c r="O92" s="24"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="20"/>
+      <c r="E92" s="21"/>
+      <c r="F92" s="21"/>
+      <c r="G92" s="21"/>
+      <c r="H92" s="21"/>
+      <c r="I92" s="22"/>
+      <c r="J92" s="20"/>
+      <c r="K92" s="21"/>
+      <c r="L92" s="22"/>
+      <c r="M92" s="20"/>
+      <c r="N92" s="21"/>
+      <c r="O92" s="22"/>
     </row>
     <row r="93" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B93" s="72" t="s">
+      <c r="B93" s="88" t="s">
         <v>65</v>
       </c>
-      <c r="C93" s="24"/>
-      <c r="D93" s="22"/>
-      <c r="E93" s="23"/>
-      <c r="F93" s="23"/>
-      <c r="G93" s="23"/>
-      <c r="H93" s="23"/>
-      <c r="I93" s="24"/>
-      <c r="J93" s="22"/>
-      <c r="K93" s="23"/>
-      <c r="L93" s="24"/>
-      <c r="M93" s="22"/>
-      <c r="N93" s="23"/>
-      <c r="O93" s="24"/>
+      <c r="C93" s="22"/>
+      <c r="D93" s="20"/>
+      <c r="E93" s="21"/>
+      <c r="F93" s="21"/>
+      <c r="G93" s="21"/>
+      <c r="H93" s="21"/>
+      <c r="I93" s="22"/>
+      <c r="J93" s="20"/>
+      <c r="K93" s="21"/>
+      <c r="L93" s="22"/>
+      <c r="M93" s="20"/>
+      <c r="N93" s="21"/>
+      <c r="O93" s="22"/>
     </row>
     <row r="94" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B94" s="5"/>
@@ -5215,154 +5215,154 @@
       <c r="O94" s="5"/>
     </row>
     <row r="95" spans="2:15" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="67" t="s">
+      <c r="B95" s="32" t="s">
         <v>50</v>
       </c>
-      <c r="C95" s="68"/>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="68"/>
-      <c r="G95" s="68"/>
-      <c r="H95" s="68"/>
-      <c r="I95" s="68"/>
-      <c r="J95" s="68"/>
-      <c r="K95" s="68"/>
-      <c r="L95" s="68"/>
-      <c r="M95" s="68"/>
-      <c r="N95" s="68"/>
-      <c r="O95" s="69"/>
+      <c r="C95" s="33"/>
+      <c r="D95" s="33"/>
+      <c r="E95" s="33"/>
+      <c r="F95" s="33"/>
+      <c r="G95" s="33"/>
+      <c r="H95" s="33"/>
+      <c r="I95" s="33"/>
+      <c r="J95" s="33"/>
+      <c r="K95" s="33"/>
+      <c r="L95" s="33"/>
+      <c r="M95" s="33"/>
+      <c r="N95" s="33"/>
+      <c r="O95" s="34"/>
     </row>
     <row r="96" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B96" s="85" t="s">
+      <c r="B96" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="C96" s="23"/>
-      <c r="D96" s="23"/>
-      <c r="E96" s="24"/>
-      <c r="F96" s="85" t="s">
+      <c r="C96" s="21"/>
+      <c r="D96" s="21"/>
+      <c r="E96" s="22"/>
+      <c r="F96" s="87" t="s">
         <v>52</v>
       </c>
-      <c r="G96" s="24"/>
-      <c r="H96" s="85" t="s">
+      <c r="G96" s="22"/>
+      <c r="H96" s="87" t="s">
         <v>53</v>
       </c>
-      <c r="I96" s="23"/>
-      <c r="J96" s="23"/>
-      <c r="K96" s="23"/>
-      <c r="L96" s="23"/>
-      <c r="M96" s="24"/>
-      <c r="N96" s="85" t="s">
+      <c r="I96" s="21"/>
+      <c r="J96" s="21"/>
+      <c r="K96" s="21"/>
+      <c r="L96" s="21"/>
+      <c r="M96" s="22"/>
+      <c r="N96" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="O96" s="24"/>
+      <c r="O96" s="22"/>
     </row>
     <row r="97" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B97" s="72" t="s">
+      <c r="B97" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="C97" s="23"/>
-      <c r="D97" s="23"/>
-      <c r="E97" s="24"/>
-      <c r="F97" s="22"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="22"/>
-      <c r="I97" s="23"/>
-      <c r="J97" s="23"/>
-      <c r="K97" s="23"/>
-      <c r="L97" s="23"/>
-      <c r="M97" s="24"/>
-      <c r="N97" s="22"/>
-      <c r="O97" s="24"/>
+      <c r="C97" s="21"/>
+      <c r="D97" s="21"/>
+      <c r="E97" s="22"/>
+      <c r="F97" s="20"/>
+      <c r="G97" s="22"/>
+      <c r="H97" s="20"/>
+      <c r="I97" s="21"/>
+      <c r="J97" s="21"/>
+      <c r="K97" s="21"/>
+      <c r="L97" s="21"/>
+      <c r="M97" s="22"/>
+      <c r="N97" s="20"/>
+      <c r="O97" s="22"/>
     </row>
     <row r="98" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B98" s="72" t="s">
+      <c r="B98" s="88" t="s">
         <v>55</v>
       </c>
-      <c r="C98" s="23"/>
-      <c r="D98" s="23"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="22"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="22"/>
-      <c r="I98" s="23"/>
-      <c r="J98" s="23"/>
-      <c r="K98" s="23"/>
-      <c r="L98" s="23"/>
-      <c r="M98" s="24"/>
-      <c r="N98" s="22"/>
-      <c r="O98" s="24"/>
+      <c r="C98" s="21"/>
+      <c r="D98" s="21"/>
+      <c r="E98" s="22"/>
+      <c r="F98" s="20"/>
+      <c r="G98" s="22"/>
+      <c r="H98" s="20"/>
+      <c r="I98" s="21"/>
+      <c r="J98" s="21"/>
+      <c r="K98" s="21"/>
+      <c r="L98" s="21"/>
+      <c r="M98" s="22"/>
+      <c r="N98" s="20"/>
+      <c r="O98" s="22"/>
     </row>
     <row r="99" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B99" s="72" t="s">
+      <c r="B99" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="C99" s="23"/>
-      <c r="D99" s="23"/>
-      <c r="E99" s="24"/>
-      <c r="F99" s="22"/>
-      <c r="G99" s="24"/>
-      <c r="H99" s="22"/>
-      <c r="I99" s="23"/>
-      <c r="J99" s="23"/>
-      <c r="K99" s="23"/>
-      <c r="L99" s="23"/>
-      <c r="M99" s="24"/>
-      <c r="N99" s="22"/>
-      <c r="O99" s="24"/>
+      <c r="C99" s="21"/>
+      <c r="D99" s="21"/>
+      <c r="E99" s="22"/>
+      <c r="F99" s="20"/>
+      <c r="G99" s="22"/>
+      <c r="H99" s="20"/>
+      <c r="I99" s="21"/>
+      <c r="J99" s="21"/>
+      <c r="K99" s="21"/>
+      <c r="L99" s="21"/>
+      <c r="M99" s="22"/>
+      <c r="N99" s="20"/>
+      <c r="O99" s="22"/>
     </row>
     <row r="100" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B100" s="72" t="s">
+      <c r="B100" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="C100" s="23"/>
-      <c r="D100" s="23"/>
-      <c r="E100" s="24"/>
-      <c r="F100" s="22"/>
-      <c r="G100" s="24"/>
-      <c r="H100" s="22"/>
-      <c r="I100" s="23"/>
-      <c r="J100" s="23"/>
-      <c r="K100" s="23"/>
-      <c r="L100" s="23"/>
-      <c r="M100" s="24"/>
-      <c r="N100" s="22"/>
-      <c r="O100" s="24"/>
+      <c r="C100" s="21"/>
+      <c r="D100" s="21"/>
+      <c r="E100" s="22"/>
+      <c r="F100" s="20"/>
+      <c r="G100" s="22"/>
+      <c r="H100" s="20"/>
+      <c r="I100" s="21"/>
+      <c r="J100" s="21"/>
+      <c r="K100" s="21"/>
+      <c r="L100" s="21"/>
+      <c r="M100" s="22"/>
+      <c r="N100" s="20"/>
+      <c r="O100" s="22"/>
     </row>
     <row r="101" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B101" s="72" t="s">
+      <c r="B101" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="C101" s="23"/>
-      <c r="D101" s="23"/>
-      <c r="E101" s="24"/>
-      <c r="F101" s="22"/>
-      <c r="G101" s="24"/>
-      <c r="H101" s="22"/>
-      <c r="I101" s="23"/>
-      <c r="J101" s="23"/>
-      <c r="K101" s="23"/>
-      <c r="L101" s="23"/>
-      <c r="M101" s="24"/>
-      <c r="N101" s="22"/>
-      <c r="O101" s="24"/>
+      <c r="C101" s="21"/>
+      <c r="D101" s="21"/>
+      <c r="E101" s="22"/>
+      <c r="F101" s="20"/>
+      <c r="G101" s="22"/>
+      <c r="H101" s="20"/>
+      <c r="I101" s="21"/>
+      <c r="J101" s="21"/>
+      <c r="K101" s="21"/>
+      <c r="L101" s="21"/>
+      <c r="M101" s="22"/>
+      <c r="N101" s="20"/>
+      <c r="O101" s="22"/>
     </row>
     <row r="102" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B102" s="72" t="s">
+      <c r="B102" s="88" t="s">
         <v>59</v>
       </c>
-      <c r="C102" s="23"/>
-      <c r="D102" s="23"/>
-      <c r="E102" s="24"/>
-      <c r="F102" s="22"/>
-      <c r="G102" s="24"/>
-      <c r="H102" s="22"/>
-      <c r="I102" s="23"/>
-      <c r="J102" s="23"/>
-      <c r="K102" s="23"/>
-      <c r="L102" s="23"/>
-      <c r="M102" s="24"/>
-      <c r="N102" s="22"/>
-      <c r="O102" s="24"/>
+      <c r="C102" s="21"/>
+      <c r="D102" s="21"/>
+      <c r="E102" s="22"/>
+      <c r="F102" s="20"/>
+      <c r="G102" s="22"/>
+      <c r="H102" s="20"/>
+      <c r="I102" s="21"/>
+      <c r="J102" s="21"/>
+      <c r="K102" s="21"/>
+      <c r="L102" s="21"/>
+      <c r="M102" s="22"/>
+      <c r="N102" s="20"/>
+      <c r="O102" s="22"/>
     </row>
     <row r="103" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B103" s="5"/>
@@ -5381,145 +5381,145 @@
       <c r="O103" s="5"/>
     </row>
     <row r="104" spans="2:15" ht="21.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B104" s="67" t="s">
+      <c r="B104" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="C104" s="68"/>
-      <c r="D104" s="68"/>
-      <c r="E104" s="68"/>
-      <c r="F104" s="68"/>
-      <c r="G104" s="68"/>
-      <c r="H104" s="68"/>
-      <c r="I104" s="68"/>
-      <c r="J104" s="68"/>
-      <c r="K104" s="68"/>
-      <c r="L104" s="68"/>
-      <c r="M104" s="68"/>
-      <c r="N104" s="68"/>
-      <c r="O104" s="69"/>
+      <c r="C104" s="33"/>
+      <c r="D104" s="33"/>
+      <c r="E104" s="33"/>
+      <c r="F104" s="33"/>
+      <c r="G104" s="33"/>
+      <c r="H104" s="33"/>
+      <c r="I104" s="33"/>
+      <c r="J104" s="33"/>
+      <c r="K104" s="33"/>
+      <c r="L104" s="33"/>
+      <c r="M104" s="33"/>
+      <c r="N104" s="33"/>
+      <c r="O104" s="34"/>
     </row>
     <row r="105" spans="2:15" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="73" t="s">
+      <c r="B105" s="126" t="s">
         <v>163</v>
       </c>
-      <c r="C105" s="74"/>
-      <c r="D105" s="74"/>
-      <c r="E105" s="74"/>
-      <c r="F105" s="74"/>
-      <c r="G105" s="74"/>
-      <c r="H105" s="74"/>
-      <c r="I105" s="74"/>
-      <c r="J105" s="74"/>
-      <c r="K105" s="74"/>
-      <c r="L105" s="74"/>
-      <c r="M105" s="74"/>
-      <c r="N105" s="74"/>
-      <c r="O105" s="74"/>
+      <c r="C105" s="127"/>
+      <c r="D105" s="127"/>
+      <c r="E105" s="127"/>
+      <c r="F105" s="127"/>
+      <c r="G105" s="127"/>
+      <c r="H105" s="127"/>
+      <c r="I105" s="127"/>
+      <c r="J105" s="127"/>
+      <c r="K105" s="127"/>
+      <c r="L105" s="127"/>
+      <c r="M105" s="127"/>
+      <c r="N105" s="127"/>
+      <c r="O105" s="127"/>
     </row>
     <row r="106" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B106" s="85" t="s">
+      <c r="B106" s="87" t="s">
         <v>66</v>
       </c>
-      <c r="C106" s="23"/>
-      <c r="D106" s="23"/>
-      <c r="E106" s="23"/>
-      <c r="F106" s="24"/>
-      <c r="G106" s="85" t="s">
+      <c r="C106" s="21"/>
+      <c r="D106" s="21"/>
+      <c r="E106" s="21"/>
+      <c r="F106" s="22"/>
+      <c r="G106" s="87" t="s">
         <v>67</v>
       </c>
-      <c r="H106" s="23"/>
-      <c r="I106" s="24"/>
-      <c r="J106" s="77" t="s">
+      <c r="H106" s="21"/>
+      <c r="I106" s="22"/>
+      <c r="J106" s="123" t="s">
         <v>161</v>
       </c>
-      <c r="K106" s="78"/>
-      <c r="L106" s="79"/>
-      <c r="M106" s="85" t="s">
+      <c r="K106" s="124"/>
+      <c r="L106" s="125"/>
+      <c r="M106" s="87" t="s">
         <v>43</v>
       </c>
-      <c r="N106" s="24"/>
+      <c r="N106" s="22"/>
       <c r="O106" s="6" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="107" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B107" s="22"/>
-      <c r="C107" s="23"/>
-      <c r="D107" s="23"/>
-      <c r="E107" s="23"/>
-      <c r="F107" s="24"/>
-      <c r="G107" s="22"/>
-      <c r="H107" s="23"/>
-      <c r="I107" s="24"/>
-      <c r="J107" s="80"/>
-      <c r="K107" s="81"/>
-      <c r="L107" s="81"/>
-      <c r="M107" s="80"/>
-      <c r="N107" s="130"/>
+      <c r="B107" s="20"/>
+      <c r="C107" s="21"/>
+      <c r="D107" s="21"/>
+      <c r="E107" s="21"/>
+      <c r="F107" s="22"/>
+      <c r="G107" s="20"/>
+      <c r="H107" s="21"/>
+      <c r="I107" s="22"/>
+      <c r="J107" s="44"/>
+      <c r="K107" s="45"/>
+      <c r="L107" s="45"/>
+      <c r="M107" s="44"/>
+      <c r="N107" s="59"/>
       <c r="O107" s="4"/>
     </row>
     <row r="108" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B108" s="22"/>
-      <c r="C108" s="23"/>
-      <c r="D108" s="23"/>
-      <c r="E108" s="23"/>
-      <c r="F108" s="24"/>
-      <c r="G108" s="22"/>
-      <c r="H108" s="23"/>
-      <c r="I108" s="24"/>
-      <c r="J108" s="80"/>
-      <c r="K108" s="81"/>
-      <c r="L108" s="81"/>
-      <c r="M108" s="80"/>
-      <c r="N108" s="130"/>
+      <c r="B108" s="20"/>
+      <c r="C108" s="21"/>
+      <c r="D108" s="21"/>
+      <c r="E108" s="21"/>
+      <c r="F108" s="22"/>
+      <c r="G108" s="20"/>
+      <c r="H108" s="21"/>
+      <c r="I108" s="22"/>
+      <c r="J108" s="44"/>
+      <c r="K108" s="45"/>
+      <c r="L108" s="45"/>
+      <c r="M108" s="44"/>
+      <c r="N108" s="59"/>
       <c r="O108" s="4"/>
     </row>
     <row r="109" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B109" s="22"/>
-      <c r="C109" s="23"/>
-      <c r="D109" s="23"/>
-      <c r="E109" s="23"/>
-      <c r="F109" s="24"/>
-      <c r="G109" s="22"/>
-      <c r="H109" s="23"/>
-      <c r="I109" s="24"/>
-      <c r="J109" s="80"/>
-      <c r="K109" s="81"/>
-      <c r="L109" s="81"/>
-      <c r="M109" s="80"/>
-      <c r="N109" s="130"/>
+      <c r="B109" s="20"/>
+      <c r="C109" s="21"/>
+      <c r="D109" s="21"/>
+      <c r="E109" s="21"/>
+      <c r="F109" s="22"/>
+      <c r="G109" s="20"/>
+      <c r="H109" s="21"/>
+      <c r="I109" s="22"/>
+      <c r="J109" s="44"/>
+      <c r="K109" s="45"/>
+      <c r="L109" s="45"/>
+      <c r="M109" s="44"/>
+      <c r="N109" s="59"/>
       <c r="O109" s="4"/>
     </row>
     <row r="110" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B110" s="22"/>
-      <c r="C110" s="23"/>
-      <c r="D110" s="23"/>
-      <c r="E110" s="23"/>
-      <c r="F110" s="24"/>
-      <c r="G110" s="22"/>
-      <c r="H110" s="23"/>
-      <c r="I110" s="24"/>
-      <c r="J110" s="80"/>
-      <c r="K110" s="81"/>
-      <c r="L110" s="81"/>
-      <c r="M110" s="80"/>
-      <c r="N110" s="130"/>
+      <c r="B110" s="20"/>
+      <c r="C110" s="21"/>
+      <c r="D110" s="21"/>
+      <c r="E110" s="21"/>
+      <c r="F110" s="22"/>
+      <c r="G110" s="20"/>
+      <c r="H110" s="21"/>
+      <c r="I110" s="22"/>
+      <c r="J110" s="44"/>
+      <c r="K110" s="45"/>
+      <c r="L110" s="45"/>
+      <c r="M110" s="44"/>
+      <c r="N110" s="59"/>
       <c r="O110" s="4"/>
     </row>
     <row r="111" spans="2:15" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B111" s="22"/>
-      <c r="C111" s="23"/>
-      <c r="D111" s="23"/>
-      <c r="E111" s="23"/>
-      <c r="F111" s="24"/>
-      <c r="G111" s="22"/>
-      <c r="H111" s="23"/>
-      <c r="I111" s="24"/>
-      <c r="J111" s="80"/>
-      <c r="K111" s="81"/>
-      <c r="L111" s="81"/>
-      <c r="M111" s="80"/>
-      <c r="N111" s="130"/>
+      <c r="B111" s="20"/>
+      <c r="C111" s="21"/>
+      <c r="D111" s="21"/>
+      <c r="E111" s="21"/>
+      <c r="F111" s="22"/>
+      <c r="G111" s="20"/>
+      <c r="H111" s="21"/>
+      <c r="I111" s="22"/>
+      <c r="J111" s="44"/>
+      <c r="K111" s="45"/>
+      <c r="L111" s="45"/>
+      <c r="M111" s="44"/>
+      <c r="N111" s="59"/>
       <c r="O111" s="4"/>
     </row>
     <row r="112" spans="2:15" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
@@ -5539,120 +5539,120 @@
       <c r="O112" s="5"/>
     </row>
     <row r="113" spans="2:16" ht="21.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="67" t="s">
+      <c r="B113" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="C113" s="68"/>
-      <c r="D113" s="68"/>
-      <c r="E113" s="68"/>
-      <c r="F113" s="68"/>
-      <c r="G113" s="68"/>
-      <c r="H113" s="68"/>
-      <c r="I113" s="68"/>
-      <c r="J113" s="68"/>
-      <c r="K113" s="68"/>
-      <c r="L113" s="68"/>
-      <c r="M113" s="68"/>
-      <c r="N113" s="68"/>
-      <c r="O113" s="69"/>
+      <c r="C113" s="33"/>
+      <c r="D113" s="33"/>
+      <c r="E113" s="33"/>
+      <c r="F113" s="33"/>
+      <c r="G113" s="33"/>
+      <c r="H113" s="33"/>
+      <c r="I113" s="33"/>
+      <c r="J113" s="33"/>
+      <c r="K113" s="33"/>
+      <c r="L113" s="33"/>
+      <c r="M113" s="33"/>
+      <c r="N113" s="33"/>
+      <c r="O113" s="34"/>
     </row>
     <row r="114" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B114" s="60" t="s">
+      <c r="B114" s="128" t="s">
         <v>120</v>
       </c>
-      <c r="C114" s="23"/>
-      <c r="D114" s="23"/>
-      <c r="E114" s="23"/>
-      <c r="F114" s="23"/>
-      <c r="G114" s="23"/>
-      <c r="H114" s="23"/>
-      <c r="I114" s="23"/>
-      <c r="J114" s="23"/>
-      <c r="K114" s="23"/>
-      <c r="L114" s="23"/>
-      <c r="M114" s="23"/>
-      <c r="N114" s="23"/>
-      <c r="O114" s="24"/>
+      <c r="C114" s="21"/>
+      <c r="D114" s="21"/>
+      <c r="E114" s="21"/>
+      <c r="F114" s="21"/>
+      <c r="G114" s="21"/>
+      <c r="H114" s="21"/>
+      <c r="I114" s="21"/>
+      <c r="J114" s="21"/>
+      <c r="K114" s="21"/>
+      <c r="L114" s="21"/>
+      <c r="M114" s="21"/>
+      <c r="N114" s="21"/>
+      <c r="O114" s="22"/>
     </row>
     <row r="115" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B115" s="22"/>
-      <c r="C115" s="25"/>
-      <c r="D115" s="25"/>
-      <c r="E115" s="25"/>
-      <c r="F115" s="25"/>
-      <c r="G115" s="25"/>
-      <c r="H115" s="25"/>
-      <c r="I115" s="25"/>
-      <c r="J115" s="25"/>
-      <c r="K115" s="25"/>
-      <c r="L115" s="25"/>
-      <c r="M115" s="25"/>
-      <c r="N115" s="25"/>
-      <c r="O115" s="26"/>
+      <c r="B115" s="20"/>
+      <c r="C115" s="23"/>
+      <c r="D115" s="23"/>
+      <c r="E115" s="23"/>
+      <c r="F115" s="23"/>
+      <c r="G115" s="23"/>
+      <c r="H115" s="23"/>
+      <c r="I115" s="23"/>
+      <c r="J115" s="23"/>
+      <c r="K115" s="23"/>
+      <c r="L115" s="23"/>
+      <c r="M115" s="23"/>
+      <c r="N115" s="23"/>
+      <c r="O115" s="24"/>
     </row>
     <row r="116" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B116" s="62"/>
-      <c r="C116" s="76"/>
-      <c r="D116" s="76"/>
-      <c r="E116" s="76"/>
-      <c r="F116" s="76"/>
-      <c r="G116" s="76"/>
-      <c r="H116" s="76"/>
-      <c r="I116" s="76"/>
-      <c r="J116" s="76"/>
-      <c r="K116" s="76"/>
-      <c r="L116" s="76"/>
-      <c r="M116" s="76"/>
-      <c r="N116" s="76"/>
-      <c r="O116" s="63"/>
+      <c r="B116" s="37"/>
+      <c r="C116" s="109"/>
+      <c r="D116" s="109"/>
+      <c r="E116" s="109"/>
+      <c r="F116" s="109"/>
+      <c r="G116" s="109"/>
+      <c r="H116" s="109"/>
+      <c r="I116" s="109"/>
+      <c r="J116" s="109"/>
+      <c r="K116" s="109"/>
+      <c r="L116" s="109"/>
+      <c r="M116" s="109"/>
+      <c r="N116" s="109"/>
+      <c r="O116" s="38"/>
     </row>
     <row r="117" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B117" s="62"/>
-      <c r="C117" s="76"/>
-      <c r="D117" s="76"/>
-      <c r="E117" s="76"/>
-      <c r="F117" s="76"/>
-      <c r="G117" s="76"/>
-      <c r="H117" s="76"/>
-      <c r="I117" s="76"/>
-      <c r="J117" s="76"/>
-      <c r="K117" s="76"/>
-      <c r="L117" s="76"/>
-      <c r="M117" s="76"/>
-      <c r="N117" s="76"/>
-      <c r="O117" s="63"/>
+      <c r="B117" s="37"/>
+      <c r="C117" s="109"/>
+      <c r="D117" s="109"/>
+      <c r="E117" s="109"/>
+      <c r="F117" s="109"/>
+      <c r="G117" s="109"/>
+      <c r="H117" s="109"/>
+      <c r="I117" s="109"/>
+      <c r="J117" s="109"/>
+      <c r="K117" s="109"/>
+      <c r="L117" s="109"/>
+      <c r="M117" s="109"/>
+      <c r="N117" s="109"/>
+      <c r="O117" s="38"/>
     </row>
     <row r="118" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B118" s="62"/>
-      <c r="C118" s="76"/>
-      <c r="D118" s="76"/>
-      <c r="E118" s="76"/>
-      <c r="F118" s="76"/>
-      <c r="G118" s="76"/>
-      <c r="H118" s="76"/>
-      <c r="I118" s="76"/>
-      <c r="J118" s="76"/>
-      <c r="K118" s="76"/>
-      <c r="L118" s="76"/>
-      <c r="M118" s="76"/>
-      <c r="N118" s="76"/>
-      <c r="O118" s="63"/>
+      <c r="B118" s="37"/>
+      <c r="C118" s="109"/>
+      <c r="D118" s="109"/>
+      <c r="E118" s="109"/>
+      <c r="F118" s="109"/>
+      <c r="G118" s="109"/>
+      <c r="H118" s="109"/>
+      <c r="I118" s="109"/>
+      <c r="J118" s="109"/>
+      <c r="K118" s="109"/>
+      <c r="L118" s="109"/>
+      <c r="M118" s="109"/>
+      <c r="N118" s="109"/>
+      <c r="O118" s="38"/>
     </row>
     <row r="119" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B119" s="27"/>
-      <c r="C119" s="28"/>
-      <c r="D119" s="28"/>
-      <c r="E119" s="28"/>
-      <c r="F119" s="28"/>
-      <c r="G119" s="28"/>
-      <c r="H119" s="28"/>
-      <c r="I119" s="28"/>
-      <c r="J119" s="28"/>
-      <c r="K119" s="28"/>
-      <c r="L119" s="28"/>
-      <c r="M119" s="28"/>
-      <c r="N119" s="28"/>
-      <c r="O119" s="29"/>
+      <c r="B119" s="25"/>
+      <c r="C119" s="26"/>
+      <c r="D119" s="26"/>
+      <c r="E119" s="26"/>
+      <c r="F119" s="26"/>
+      <c r="G119" s="26"/>
+      <c r="H119" s="26"/>
+      <c r="I119" s="26"/>
+      <c r="J119" s="26"/>
+      <c r="K119" s="26"/>
+      <c r="L119" s="26"/>
+      <c r="M119" s="26"/>
+      <c r="N119" s="26"/>
+      <c r="O119" s="27"/>
     </row>
     <row r="120" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
       <c r="B120" s="8"/>
@@ -5671,111 +5671,423 @@
       <c r="O120" s="10"/>
     </row>
     <row r="121" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B121" s="126" t="s">
+      <c r="B121" s="83" t="s">
         <v>151</v>
       </c>
-      <c r="C121" s="127"/>
-      <c r="D121" s="127"/>
-      <c r="E121" s="127"/>
-      <c r="F121" s="127"/>
-      <c r="G121" s="127"/>
-      <c r="H121" s="128"/>
-      <c r="I121" s="126" t="s">
+      <c r="C121" s="84"/>
+      <c r="D121" s="84"/>
+      <c r="E121" s="84"/>
+      <c r="F121" s="84"/>
+      <c r="G121" s="84"/>
+      <c r="H121" s="85"/>
+      <c r="I121" s="83" t="s">
         <v>152</v>
       </c>
-      <c r="J121" s="127"/>
-      <c r="K121" s="127"/>
-      <c r="L121" s="127"/>
-      <c r="M121" s="127"/>
-      <c r="N121" s="127"/>
-      <c r="O121" s="129"/>
+      <c r="J121" s="84"/>
+      <c r="K121" s="84"/>
+      <c r="L121" s="84"/>
+      <c r="M121" s="84"/>
+      <c r="N121" s="84"/>
+      <c r="O121" s="86"/>
       <c r="P121" s="19"/>
     </row>
     <row r="122" spans="2:16" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="124" t="s">
+      <c r="B122" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="C122" s="125"/>
-      <c r="D122" s="125"/>
-      <c r="E122" s="125"/>
-      <c r="F122" s="125"/>
-      <c r="G122" s="125"/>
-      <c r="H122" s="125"/>
-      <c r="I122" s="124" t="s">
+      <c r="C122" s="82"/>
+      <c r="D122" s="82"/>
+      <c r="E122" s="82"/>
+      <c r="F122" s="82"/>
+      <c r="G122" s="82"/>
+      <c r="H122" s="82"/>
+      <c r="I122" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="J122" s="125"/>
-      <c r="K122" s="125"/>
-      <c r="L122" s="125"/>
-      <c r="M122" s="125"/>
-      <c r="N122" s="125"/>
-      <c r="O122" s="125"/>
+      <c r="J122" s="82"/>
+      <c r="K122" s="82"/>
+      <c r="L122" s="82"/>
+      <c r="M122" s="82"/>
+      <c r="N122" s="82"/>
+      <c r="O122" s="82"/>
       <c r="P122" s="19"/>
     </row>
     <row r="123" spans="2:16" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="B123" s="75" t="s">
+      <c r="B123" s="102" t="s">
         <v>149</v>
       </c>
-      <c r="C123" s="23"/>
-      <c r="D123" s="23"/>
-      <c r="E123" s="24"/>
-      <c r="F123" s="75" t="s">
+      <c r="C123" s="21"/>
+      <c r="D123" s="21"/>
+      <c r="E123" s="22"/>
+      <c r="F123" s="102" t="s">
         <v>149</v>
       </c>
-      <c r="G123" s="23"/>
-      <c r="H123" s="23"/>
-      <c r="I123" s="23"/>
-      <c r="J123" s="24"/>
-      <c r="K123" s="75" t="s">
+      <c r="G123" s="21"/>
+      <c r="H123" s="21"/>
+      <c r="I123" s="21"/>
+      <c r="J123" s="22"/>
+      <c r="K123" s="102" t="s">
         <v>150</v>
       </c>
-      <c r="L123" s="23"/>
-      <c r="M123" s="23"/>
-      <c r="N123" s="23"/>
-      <c r="O123" s="24"/>
+      <c r="L123" s="21"/>
+      <c r="M123" s="21"/>
+      <c r="N123" s="21"/>
+      <c r="O123" s="22"/>
     </row>
     <row r="124" spans="2:16" ht="51.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="82" t="s">
+      <c r="B124" s="99" t="s">
         <v>121</v>
       </c>
-      <c r="C124" s="83"/>
-      <c r="D124" s="83"/>
-      <c r="E124" s="84"/>
-      <c r="F124" s="82" t="s">
+      <c r="C124" s="100"/>
+      <c r="D124" s="100"/>
+      <c r="E124" s="101"/>
+      <c r="F124" s="99" t="s">
         <v>121</v>
       </c>
-      <c r="G124" s="83"/>
-      <c r="H124" s="83"/>
-      <c r="I124" s="83"/>
-      <c r="J124" s="84"/>
-      <c r="K124" s="82" t="s">
+      <c r="G124" s="100"/>
+      <c r="H124" s="100"/>
+      <c r="I124" s="100"/>
+      <c r="J124" s="101"/>
+      <c r="K124" s="99" t="s">
         <v>121</v>
       </c>
-      <c r="L124" s="83"/>
-      <c r="M124" s="83"/>
-      <c r="N124" s="83"/>
-      <c r="O124" s="84"/>
+      <c r="L124" s="100"/>
+      <c r="M124" s="100"/>
+      <c r="N124" s="100"/>
+      <c r="O124" s="101"/>
     </row>
     <row r="125" spans="2:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B125" s="115" t="s">
+      <c r="B125" s="89" t="s">
         <v>103</v>
       </c>
-      <c r="C125" s="68"/>
-      <c r="D125" s="68"/>
-      <c r="E125" s="68"/>
-      <c r="F125" s="68"/>
-      <c r="G125" s="68"/>
-      <c r="H125" s="68"/>
-      <c r="I125" s="68"/>
-      <c r="J125" s="68"/>
-      <c r="K125" s="68"/>
-      <c r="L125" s="68"/>
-      <c r="M125" s="68"/>
-      <c r="N125" s="68"/>
-      <c r="O125" s="69"/>
+      <c r="C125" s="33"/>
+      <c r="D125" s="33"/>
+      <c r="E125" s="33"/>
+      <c r="F125" s="33"/>
+      <c r="G125" s="33"/>
+      <c r="H125" s="33"/>
+      <c r="I125" s="33"/>
+      <c r="J125" s="33"/>
+      <c r="K125" s="33"/>
+      <c r="L125" s="33"/>
+      <c r="M125" s="33"/>
+      <c r="N125" s="33"/>
+      <c r="O125" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="336">
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="H67:J67"/>
+    <mergeCell ref="H51:K52"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="N43:O43"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="I13:O13"/>
+    <mergeCell ref="I14:O14"/>
+    <mergeCell ref="I15:O15"/>
+    <mergeCell ref="I16:O16"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="J8:K8"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="N8:O8"/>
+    <mergeCell ref="B9:I9"/>
+    <mergeCell ref="F7:O7"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B12:H17"/>
+    <mergeCell ref="I12:O12"/>
+    <mergeCell ref="F6:H6"/>
+    <mergeCell ref="J10:L10"/>
+    <mergeCell ref="L5:O5"/>
+    <mergeCell ref="B114:O114"/>
+    <mergeCell ref="N99:O99"/>
+    <mergeCell ref="B75:C78"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="N75:O75"/>
+    <mergeCell ref="K34:L34"/>
+    <mergeCell ref="H73:J73"/>
+    <mergeCell ref="B111:F111"/>
+    <mergeCell ref="E70:G70"/>
+    <mergeCell ref="H100:M100"/>
+    <mergeCell ref="B95:O95"/>
+    <mergeCell ref="H83:J83"/>
+    <mergeCell ref="E86:G86"/>
+    <mergeCell ref="N34:O34"/>
+    <mergeCell ref="I35:J35"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="J9:L9"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="E80:G80"/>
+    <mergeCell ref="N100:O100"/>
+    <mergeCell ref="F100:G100"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="B102:E102"/>
+    <mergeCell ref="G108:I108"/>
+    <mergeCell ref="H77:J77"/>
+    <mergeCell ref="H71:J71"/>
+    <mergeCell ref="L55:O55"/>
+    <mergeCell ref="H68:J68"/>
+    <mergeCell ref="H56:K57"/>
+    <mergeCell ref="E75:G75"/>
+    <mergeCell ref="G107:I107"/>
+    <mergeCell ref="B92:C92"/>
+    <mergeCell ref="D92:I92"/>
+    <mergeCell ref="J92:L92"/>
+    <mergeCell ref="M92:O92"/>
+    <mergeCell ref="B93:C93"/>
+    <mergeCell ref="D93:I93"/>
+    <mergeCell ref="J93:L93"/>
+    <mergeCell ref="M93:O93"/>
+    <mergeCell ref="B105:O105"/>
+    <mergeCell ref="B67:C70"/>
+    <mergeCell ref="B71:C74"/>
+    <mergeCell ref="H101:M101"/>
+    <mergeCell ref="E56:G57"/>
+    <mergeCell ref="N101:O101"/>
+    <mergeCell ref="E82:G82"/>
+    <mergeCell ref="K123:O123"/>
+    <mergeCell ref="B110:F110"/>
+    <mergeCell ref="B115:O119"/>
+    <mergeCell ref="B104:O104"/>
+    <mergeCell ref="B123:E123"/>
+    <mergeCell ref="N68:O68"/>
+    <mergeCell ref="J106:L106"/>
+    <mergeCell ref="N73:O73"/>
+    <mergeCell ref="E71:G71"/>
+    <mergeCell ref="B100:E100"/>
+    <mergeCell ref="F98:G98"/>
+    <mergeCell ref="N97:O97"/>
+    <mergeCell ref="E72:G72"/>
+    <mergeCell ref="N74:O74"/>
+    <mergeCell ref="E84:G84"/>
+    <mergeCell ref="J108:L108"/>
+    <mergeCell ref="N102:O102"/>
+    <mergeCell ref="F102:G102"/>
+    <mergeCell ref="N69:O69"/>
+    <mergeCell ref="N76:O76"/>
+    <mergeCell ref="B91:C91"/>
+    <mergeCell ref="D91:I91"/>
+    <mergeCell ref="J91:L91"/>
+    <mergeCell ref="M91:O91"/>
+    <mergeCell ref="F124:J124"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="E76:G76"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="G110:I110"/>
+    <mergeCell ref="H81:J81"/>
+    <mergeCell ref="E85:G85"/>
+    <mergeCell ref="G109:I109"/>
+    <mergeCell ref="H66:J66"/>
+    <mergeCell ref="H97:M97"/>
+    <mergeCell ref="H86:J86"/>
+    <mergeCell ref="G106:I106"/>
+    <mergeCell ref="F101:G101"/>
+    <mergeCell ref="F96:G96"/>
+    <mergeCell ref="E78:G78"/>
+    <mergeCell ref="H72:J72"/>
+    <mergeCell ref="H80:J80"/>
+    <mergeCell ref="B49:O49"/>
+    <mergeCell ref="N86:O86"/>
+    <mergeCell ref="H55:K55"/>
+    <mergeCell ref="N80:O80"/>
+    <mergeCell ref="L56:O57"/>
+    <mergeCell ref="E55:G55"/>
+    <mergeCell ref="J107:L107"/>
+    <mergeCell ref="B4:O4"/>
+    <mergeCell ref="H102:M102"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="N81:O81"/>
+    <mergeCell ref="B83:C86"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="L62:O63"/>
+    <mergeCell ref="B58:D58"/>
+    <mergeCell ref="E58:G58"/>
+    <mergeCell ref="H58:K58"/>
+    <mergeCell ref="L58:O58"/>
+    <mergeCell ref="B59:D60"/>
+    <mergeCell ref="E59:G60"/>
+    <mergeCell ref="B20:H20"/>
+    <mergeCell ref="E81:G81"/>
+    <mergeCell ref="E83:G83"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B48:O48"/>
+    <mergeCell ref="I21:O24"/>
+    <mergeCell ref="L6:O6"/>
+    <mergeCell ref="M9:O9"/>
+    <mergeCell ref="D42:E42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="N42:O42"/>
+    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="N35:O35"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="I20:O20"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B10:I10"/>
+    <mergeCell ref="H74:J74"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="I11:O11"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="B108:F108"/>
+    <mergeCell ref="B56:D57"/>
+    <mergeCell ref="E74:G74"/>
+    <mergeCell ref="H85:J85"/>
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="L50:O50"/>
+    <mergeCell ref="H69:J69"/>
+    <mergeCell ref="N96:O96"/>
+    <mergeCell ref="B19:O19"/>
+    <mergeCell ref="H82:J82"/>
+    <mergeCell ref="K45:L45"/>
+    <mergeCell ref="N45:O45"/>
+    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B21:H24"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B51:D52"/>
+    <mergeCell ref="B28:O28"/>
+    <mergeCell ref="I17:O17"/>
+    <mergeCell ref="B124:E124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="B45:C45"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="K124:O124"/>
+    <mergeCell ref="H99:M99"/>
+    <mergeCell ref="F123:J123"/>
+    <mergeCell ref="B113:O113"/>
+    <mergeCell ref="G111:I111"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="K44:L44"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="N72:O72"/>
+    <mergeCell ref="E79:G79"/>
+    <mergeCell ref="H59:K60"/>
+    <mergeCell ref="L59:O60"/>
+    <mergeCell ref="N70:O70"/>
+    <mergeCell ref="B41:C41"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="G41:H41"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="K41:L41"/>
+    <mergeCell ref="N41:O41"/>
+    <mergeCell ref="B125:O125"/>
+    <mergeCell ref="B109:F109"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:M2"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B3:O3"/>
+    <mergeCell ref="B101:E101"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="H50:K50"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="N82:O82"/>
+    <mergeCell ref="N84:O84"/>
+    <mergeCell ref="N78:O78"/>
+    <mergeCell ref="H84:J84"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="J109:L109"/>
+    <mergeCell ref="N31:O31"/>
+    <mergeCell ref="B122:H122"/>
+    <mergeCell ref="B121:H121"/>
+    <mergeCell ref="I121:O121"/>
+    <mergeCell ref="I122:O122"/>
+    <mergeCell ref="B88:O88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:I89"/>
+    <mergeCell ref="J89:L89"/>
+    <mergeCell ref="M89:O89"/>
+    <mergeCell ref="B90:C90"/>
+    <mergeCell ref="D90:I90"/>
+    <mergeCell ref="J90:L90"/>
+    <mergeCell ref="M90:O90"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="F97:G97"/>
+    <mergeCell ref="F99:G99"/>
+    <mergeCell ref="H98:M98"/>
+    <mergeCell ref="H96:M96"/>
+    <mergeCell ref="M106:N106"/>
+    <mergeCell ref="J111:L111"/>
+    <mergeCell ref="M107:N107"/>
+    <mergeCell ref="M108:N108"/>
+    <mergeCell ref="M109:N109"/>
+    <mergeCell ref="M110:N110"/>
+    <mergeCell ref="M111:N111"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="B29:O29"/>
+    <mergeCell ref="B46:C46"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="N46:O46"/>
+    <mergeCell ref="B38:O38"/>
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="K39:O39"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="K30:O30"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="K37:L37"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="N26:O26"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="N25:O25"/>
+    <mergeCell ref="J110:L110"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="N32:O32"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="N66:O66"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="K40:L40"/>
+    <mergeCell ref="N40:O40"/>
+    <mergeCell ref="N98:O98"/>
+    <mergeCell ref="N85:O85"/>
+    <mergeCell ref="H78:J78"/>
+    <mergeCell ref="B54:O54"/>
+    <mergeCell ref="H76:J76"/>
+    <mergeCell ref="E51:G52"/>
+    <mergeCell ref="N83:O83"/>
+    <mergeCell ref="B66:C66"/>
+    <mergeCell ref="H61:K61"/>
+    <mergeCell ref="L61:O61"/>
+    <mergeCell ref="B62:D63"/>
+    <mergeCell ref="E62:G63"/>
     <mergeCell ref="E77:G77"/>
     <mergeCell ref="L51:O52"/>
     <mergeCell ref="H75:J75"/>
@@ -5800,318 +6112,6 @@
     <mergeCell ref="K36:L36"/>
     <mergeCell ref="N71:O71"/>
     <mergeCell ref="B79:C82"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="N25:O25"/>
-    <mergeCell ref="J110:L110"/>
-    <mergeCell ref="N37:O37"/>
-    <mergeCell ref="N32:O32"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="K40:L40"/>
-    <mergeCell ref="N40:O40"/>
-    <mergeCell ref="N98:O98"/>
-    <mergeCell ref="N85:O85"/>
-    <mergeCell ref="H78:J78"/>
-    <mergeCell ref="B54:O54"/>
-    <mergeCell ref="H76:J76"/>
-    <mergeCell ref="E51:G52"/>
-    <mergeCell ref="N83:O83"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="H61:K61"/>
-    <mergeCell ref="L61:O61"/>
-    <mergeCell ref="B62:D63"/>
-    <mergeCell ref="E62:G63"/>
-    <mergeCell ref="M111:N111"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="B29:O29"/>
-    <mergeCell ref="B46:C46"/>
-    <mergeCell ref="D46:E46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="K46:L46"/>
-    <mergeCell ref="N46:O46"/>
-    <mergeCell ref="B38:O38"/>
-    <mergeCell ref="B39:J39"/>
-    <mergeCell ref="K39:O39"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="K30:O30"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="G37:H37"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="K37:L37"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="G26:H26"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="N26:O26"/>
-    <mergeCell ref="B122:H122"/>
-    <mergeCell ref="B121:H121"/>
-    <mergeCell ref="I121:O121"/>
-    <mergeCell ref="I122:O122"/>
-    <mergeCell ref="B88:O88"/>
-    <mergeCell ref="B89:C89"/>
-    <mergeCell ref="D89:I89"/>
-    <mergeCell ref="J89:L89"/>
-    <mergeCell ref="M89:O89"/>
-    <mergeCell ref="B90:C90"/>
-    <mergeCell ref="D90:I90"/>
-    <mergeCell ref="J90:L90"/>
-    <mergeCell ref="M90:O90"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="F97:G97"/>
-    <mergeCell ref="F99:G99"/>
-    <mergeCell ref="H98:M98"/>
-    <mergeCell ref="H96:M96"/>
-    <mergeCell ref="M106:N106"/>
-    <mergeCell ref="J111:L111"/>
-    <mergeCell ref="M107:N107"/>
-    <mergeCell ref="M108:N108"/>
-    <mergeCell ref="M109:N109"/>
-    <mergeCell ref="M110:N110"/>
-    <mergeCell ref="B41:C41"/>
-    <mergeCell ref="D41:E41"/>
-    <mergeCell ref="G41:H41"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="K41:L41"/>
-    <mergeCell ref="N41:O41"/>
-    <mergeCell ref="B125:O125"/>
-    <mergeCell ref="B109:F109"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:M2"/>
-    <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B3:O3"/>
-    <mergeCell ref="B101:E101"/>
-    <mergeCell ref="E68:G68"/>
-    <mergeCell ref="H50:K50"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="G34:H34"/>
-    <mergeCell ref="N82:O82"/>
-    <mergeCell ref="N84:O84"/>
-    <mergeCell ref="N78:O78"/>
-    <mergeCell ref="H84:J84"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="J109:L109"/>
-    <mergeCell ref="N31:O31"/>
-    <mergeCell ref="I17:O17"/>
-    <mergeCell ref="B124:E124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="G36:H36"/>
-    <mergeCell ref="B45:C45"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="K124:O124"/>
-    <mergeCell ref="H99:M99"/>
-    <mergeCell ref="F123:J123"/>
-    <mergeCell ref="B113:O113"/>
-    <mergeCell ref="G111:I111"/>
-    <mergeCell ref="G32:H32"/>
-    <mergeCell ref="B44:C44"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="G44:H44"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="K44:L44"/>
-    <mergeCell ref="N44:O44"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="N72:O72"/>
-    <mergeCell ref="E79:G79"/>
-    <mergeCell ref="H59:K60"/>
-    <mergeCell ref="L59:O60"/>
-    <mergeCell ref="N70:O70"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="H74:J74"/>
-    <mergeCell ref="B11:H11"/>
-    <mergeCell ref="I11:O11"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="E61:G61"/>
-    <mergeCell ref="B108:F108"/>
-    <mergeCell ref="B56:D57"/>
-    <mergeCell ref="E74:G74"/>
-    <mergeCell ref="H85:J85"/>
-    <mergeCell ref="B106:F106"/>
-    <mergeCell ref="L50:O50"/>
-    <mergeCell ref="H69:J69"/>
-    <mergeCell ref="N96:O96"/>
-    <mergeCell ref="B19:O19"/>
-    <mergeCell ref="H82:J82"/>
-    <mergeCell ref="K45:L45"/>
-    <mergeCell ref="N45:O45"/>
-    <mergeCell ref="B42:C42"/>
-    <mergeCell ref="B21:H24"/>
-    <mergeCell ref="G35:H35"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B51:D52"/>
-    <mergeCell ref="B28:O28"/>
-    <mergeCell ref="M9:O9"/>
-    <mergeCell ref="D42:E42"/>
-    <mergeCell ref="G42:H42"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="K42:L42"/>
-    <mergeCell ref="N42:O42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="G43:H43"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="K43:L43"/>
-    <mergeCell ref="B40:C40"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="N35:O35"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="I20:O20"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="B4:O4"/>
-    <mergeCell ref="H102:M102"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="N81:O81"/>
-    <mergeCell ref="B83:C86"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="I5:K5"/>
-    <mergeCell ref="L62:O63"/>
-    <mergeCell ref="B58:D58"/>
-    <mergeCell ref="E58:G58"/>
-    <mergeCell ref="H58:K58"/>
-    <mergeCell ref="L58:O58"/>
-    <mergeCell ref="B59:D60"/>
-    <mergeCell ref="E59:G60"/>
-    <mergeCell ref="B20:H20"/>
-    <mergeCell ref="E81:G81"/>
-    <mergeCell ref="E83:G83"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B48:O48"/>
-    <mergeCell ref="I21:O24"/>
-    <mergeCell ref="L6:O6"/>
-    <mergeCell ref="F124:J124"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="E76:G76"/>
-    <mergeCell ref="E69:G69"/>
-    <mergeCell ref="G110:I110"/>
-    <mergeCell ref="H81:J81"/>
-    <mergeCell ref="E85:G85"/>
-    <mergeCell ref="G109:I109"/>
-    <mergeCell ref="H66:J66"/>
-    <mergeCell ref="H97:M97"/>
-    <mergeCell ref="H86:J86"/>
-    <mergeCell ref="G106:I106"/>
-    <mergeCell ref="F101:G101"/>
-    <mergeCell ref="F96:G96"/>
-    <mergeCell ref="E78:G78"/>
-    <mergeCell ref="H72:J72"/>
-    <mergeCell ref="H80:J80"/>
-    <mergeCell ref="B49:O49"/>
-    <mergeCell ref="N86:O86"/>
-    <mergeCell ref="H55:K55"/>
-    <mergeCell ref="N80:O80"/>
-    <mergeCell ref="L56:O57"/>
-    <mergeCell ref="E55:G55"/>
-    <mergeCell ref="J107:L107"/>
-    <mergeCell ref="K123:O123"/>
-    <mergeCell ref="B110:F110"/>
-    <mergeCell ref="B115:O119"/>
-    <mergeCell ref="B104:O104"/>
-    <mergeCell ref="B123:E123"/>
-    <mergeCell ref="N68:O68"/>
-    <mergeCell ref="J106:L106"/>
-    <mergeCell ref="N73:O73"/>
-    <mergeCell ref="E71:G71"/>
-    <mergeCell ref="B100:E100"/>
-    <mergeCell ref="F98:G98"/>
-    <mergeCell ref="N97:O97"/>
-    <mergeCell ref="E72:G72"/>
-    <mergeCell ref="N74:O74"/>
-    <mergeCell ref="E84:G84"/>
-    <mergeCell ref="J108:L108"/>
-    <mergeCell ref="N102:O102"/>
-    <mergeCell ref="F102:G102"/>
-    <mergeCell ref="N69:O69"/>
-    <mergeCell ref="N76:O76"/>
-    <mergeCell ref="B91:C91"/>
-    <mergeCell ref="D91:I91"/>
-    <mergeCell ref="J91:L91"/>
-    <mergeCell ref="M91:O91"/>
-    <mergeCell ref="B102:E102"/>
-    <mergeCell ref="G108:I108"/>
-    <mergeCell ref="H77:J77"/>
-    <mergeCell ref="H71:J71"/>
-    <mergeCell ref="L55:O55"/>
-    <mergeCell ref="H68:J68"/>
-    <mergeCell ref="H56:K57"/>
-    <mergeCell ref="E75:G75"/>
-    <mergeCell ref="G107:I107"/>
-    <mergeCell ref="B92:C92"/>
-    <mergeCell ref="D92:I92"/>
-    <mergeCell ref="J92:L92"/>
-    <mergeCell ref="M92:O92"/>
-    <mergeCell ref="B93:C93"/>
-    <mergeCell ref="D93:I93"/>
-    <mergeCell ref="J93:L93"/>
-    <mergeCell ref="M93:O93"/>
-    <mergeCell ref="B105:O105"/>
-    <mergeCell ref="B67:C70"/>
-    <mergeCell ref="B71:C74"/>
-    <mergeCell ref="H101:M101"/>
-    <mergeCell ref="E56:G57"/>
-    <mergeCell ref="N101:O101"/>
-    <mergeCell ref="E82:G82"/>
-    <mergeCell ref="L5:O5"/>
-    <mergeCell ref="B114:O114"/>
-    <mergeCell ref="N99:O99"/>
-    <mergeCell ref="B75:C78"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="N75:O75"/>
-    <mergeCell ref="K34:L34"/>
-    <mergeCell ref="H73:J73"/>
-    <mergeCell ref="B111:F111"/>
-    <mergeCell ref="E70:G70"/>
-    <mergeCell ref="H100:M100"/>
-    <mergeCell ref="B95:O95"/>
-    <mergeCell ref="H83:J83"/>
-    <mergeCell ref="E86:G86"/>
-    <mergeCell ref="N34:O34"/>
-    <mergeCell ref="I35:J35"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="J9:L9"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="E80:G80"/>
-    <mergeCell ref="N100:O100"/>
-    <mergeCell ref="F100:G100"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="G31:H31"/>
-    <mergeCell ref="H67:J67"/>
-    <mergeCell ref="H51:K52"/>
-    <mergeCell ref="E66:G66"/>
-    <mergeCell ref="E67:G67"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="I13:O13"/>
-    <mergeCell ref="I14:O14"/>
-    <mergeCell ref="I15:O15"/>
-    <mergeCell ref="I16:O16"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="J8:K8"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="N8:O8"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B12:H17"/>
-    <mergeCell ref="I12:O12"/>
-    <mergeCell ref="F6:H6"/>
-    <mergeCell ref="J10:L10"/>
   </mergeCells>
   <conditionalFormatting sqref="D67:D87">
     <cfRule type="expression" dxfId="3" priority="1">
